--- a/data/Data_Dictionary.xlsx
+++ b/data/Data_Dictionary.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/enrico_toffalini_unipd_it/Documents/Documents/_GRANTS/PRIN-PNRR 2022/Data Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/Toffalini/TimeValidity/measures-validation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_EC4E860EFB524DA529C0F90297F944890C1F12D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4291353-4A41-4B2D-B2D1-961D2DEA8278}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_EC4E860EFB524DA529C0F90297F944890C1F12D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD0CE978-42BB-4CC9-B6EC-168AF2521695}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataDictionary" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DataDictionary!$A$1:$H$587</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -3928,7 +3931,7 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3941,10 +3944,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4145,20 +4144,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.453125" customWidth="1"/>
-    <col min="2" max="2" width="49.54296875" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="26.81640625" customWidth="1"/>
-    <col min="6" max="6" width="11.54296875" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" customWidth="1"/>
-    <col min="8" max="26" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="49.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4202,7 +4202,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -4238,7 +4238,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -4274,7 +4274,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -4310,7 +4310,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -4346,7 +4346,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -4382,7 +4382,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -4418,7 +4418,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
@@ -4490,7 +4490,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
@@ -4562,7 +4562,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>35</v>
       </c>
@@ -4598,7 +4598,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
@@ -4634,7 +4634,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
@@ -4670,7 +4670,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
@@ -4706,7 +4706,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
@@ -4748,7 +4748,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -4790,7 +4790,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
@@ -4832,7 +4832,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>59</v>
       </c>
@@ -4916,7 +4916,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
@@ -4958,7 +4958,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>63</v>
       </c>
@@ -5000,7 +5000,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>65</v>
       </c>
@@ -5042,7 +5042,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>67</v>
       </c>
@@ -5084,7 +5084,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>69</v>
       </c>
@@ -5126,7 +5126,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>71</v>
       </c>
@@ -5168,7 +5168,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>73</v>
       </c>
@@ -5210,7 +5210,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>75</v>
       </c>
@@ -5252,7 +5252,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>77</v>
       </c>
@@ -5294,7 +5294,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>79</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>81</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>83</v>
       </c>
@@ -5420,7 +5420,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>85</v>
       </c>
@@ -5462,7 +5462,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>87</v>
       </c>
@@ -5504,7 +5504,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>89</v>
       </c>
@@ -5546,7 +5546,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>91</v>
       </c>
@@ -5588,7 +5588,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>93</v>
       </c>
@@ -5630,7 +5630,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>95</v>
       </c>
@@ -5672,7 +5672,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>97</v>
       </c>
@@ -5714,7 +5714,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>99</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>101</v>
       </c>
@@ -5798,7 +5798,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>103</v>
       </c>
@@ -5840,7 +5840,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>105</v>
       </c>
@@ -5882,7 +5882,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>107</v>
       </c>
@@ -5924,7 +5924,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>109</v>
       </c>
@@ -5966,7 +5966,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>111</v>
       </c>
@@ -6008,7 +6008,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>113</v>
       </c>
@@ -6050,7 +6050,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>115</v>
       </c>
@@ -6092,7 +6092,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>117</v>
       </c>
@@ -6134,7 +6134,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>119</v>
       </c>
@@ -6176,7 +6176,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>121</v>
       </c>
@@ -6218,7 +6218,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>123</v>
       </c>
@@ -6260,7 +6260,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>125</v>
       </c>
@@ -6302,7 +6302,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>127</v>
       </c>
@@ -6344,7 +6344,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>129</v>
       </c>
@@ -6386,7 +6386,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>131</v>
       </c>
@@ -6428,7 +6428,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>135</v>
       </c>
@@ -6470,7 +6470,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>141</v>
       </c>
@@ -6512,7 +6512,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>143</v>
       </c>
@@ -6554,7 +6554,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>146</v>
       </c>
@@ -6596,7 +6596,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>148</v>
       </c>
@@ -6638,7 +6638,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>150</v>
       </c>
@@ -6680,7 +6680,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>152</v>
       </c>
@@ -6722,7 +6722,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>154</v>
       </c>
@@ -6758,7 +6758,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>156</v>
       </c>
@@ -6794,7 +6794,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>159</v>
       </c>
@@ -6838,7 +6838,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>164</v>
       </c>
@@ -6882,7 +6882,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>166</v>
       </c>
@@ -6926,7 +6926,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>168</v>
       </c>
@@ -6970,7 +6970,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>170</v>
       </c>
@@ -7014,7 +7014,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>172</v>
       </c>
@@ -7058,7 +7058,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>174</v>
       </c>
@@ -7102,7 +7102,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>176</v>
       </c>
@@ -7146,7 +7146,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>178</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>180</v>
       </c>
@@ -7234,7 +7234,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>182</v>
       </c>
@@ -7278,7 +7278,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>185</v>
       </c>
@@ -7314,7 +7314,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>187</v>
       </c>
@@ -7356,7 +7356,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>191</v>
       </c>
@@ -7398,7 +7398,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>193</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>195</v>
       </c>
@@ -7482,7 +7482,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>197</v>
       </c>
@@ -7524,7 +7524,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>199</v>
       </c>
@@ -7564,7 +7564,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>201</v>
       </c>
@@ -7606,7 +7606,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>203</v>
       </c>
@@ -7648,7 +7648,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>205</v>
       </c>
@@ -7690,7 +7690,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>207</v>
       </c>
@@ -7732,7 +7732,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>209</v>
       </c>
@@ -7774,7 +7774,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>211</v>
       </c>
@@ -7814,7 +7814,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>213</v>
       </c>
@@ -7856,7 +7856,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>215</v>
       </c>
@@ -7898,7 +7898,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>217</v>
       </c>
@@ -7940,7 +7940,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>219</v>
       </c>
@@ -7980,7 +7980,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>221</v>
       </c>
@@ -8022,7 +8022,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>223</v>
       </c>
@@ -8064,7 +8064,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>225</v>
       </c>
@@ -8106,7 +8106,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>227</v>
       </c>
@@ -8148,7 +8148,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>229</v>
       </c>
@@ -8190,7 +8190,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>232</v>
       </c>
@@ -8232,7 +8232,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>235</v>
       </c>
@@ -8274,7 +8274,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>238</v>
       </c>
@@ -8316,7 +8316,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>240</v>
       </c>
@@ -8358,7 +8358,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>242</v>
       </c>
@@ -8398,7 +8398,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>244</v>
       </c>
@@ -8440,7 +8440,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>246</v>
       </c>
@@ -8482,7 +8482,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>248</v>
       </c>
@@ -8524,7 +8524,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>250</v>
       </c>
@@ -8566,7 +8566,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>252</v>
       </c>
@@ -8606,7 +8606,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>254</v>
       </c>
@@ -8648,7 +8648,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>256</v>
       </c>
@@ -8690,7 +8690,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>258</v>
       </c>
@@ -8732,7 +8732,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>260</v>
       </c>
@@ -8772,7 +8772,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>262</v>
       </c>
@@ -8812,7 +8812,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>264</v>
       </c>
@@ -8852,7 +8852,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>266</v>
       </c>
@@ -8894,7 +8894,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>268</v>
       </c>
@@ -8936,7 +8936,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>270</v>
       </c>
@@ -8976,7 +8976,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>272</v>
       </c>
@@ -9018,7 +9018,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>274</v>
       </c>
@@ -9058,7 +9058,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>276</v>
       </c>
@@ -9100,7 +9100,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>278</v>
       </c>
@@ -9140,7 +9140,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>280</v>
       </c>
@@ -9182,7 +9182,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>281</v>
       </c>
@@ -9224,7 +9224,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>287</v>
       </c>
@@ -9266,7 +9266,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>290</v>
       </c>
@@ -9308,7 +9308,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>292</v>
       </c>
@@ -9350,7 +9350,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>294</v>
       </c>
@@ -9392,7 +9392,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>296</v>
       </c>
@@ -9434,7 +9434,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>298</v>
       </c>
@@ -9476,7 +9476,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>300</v>
       </c>
@@ -9518,7 +9518,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>302</v>
       </c>
@@ -9560,7 +9560,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>304</v>
       </c>
@@ -9602,7 +9602,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>306</v>
       </c>
@@ -9644,7 +9644,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>308</v>
       </c>
@@ -9686,7 +9686,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>310</v>
       </c>
@@ -9728,7 +9728,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>312</v>
       </c>
@@ -9770,7 +9770,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>314</v>
       </c>
@@ -9812,7 +9812,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>317</v>
       </c>
@@ -9854,7 +9854,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>319</v>
       </c>
@@ -9896,7 +9896,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>322</v>
       </c>
@@ -9938,7 +9938,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>324</v>
       </c>
@@ -9980,7 +9980,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>328</v>
       </c>
@@ -10022,7 +10022,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>330</v>
       </c>
@@ -10064,7 +10064,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>332</v>
       </c>
@@ -10106,7 +10106,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>334</v>
       </c>
@@ -10148,7 +10148,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>336</v>
       </c>
@@ -10190,7 +10190,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>338</v>
       </c>
@@ -10232,7 +10232,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>340</v>
       </c>
@@ -10274,7 +10274,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>342</v>
       </c>
@@ -10316,7 +10316,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>344</v>
       </c>
@@ -10358,7 +10358,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>346</v>
       </c>
@@ -10400,7 +10400,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>348</v>
       </c>
@@ -10442,7 +10442,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>350</v>
       </c>
@@ -10484,7 +10484,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>352</v>
       </c>
@@ -10526,7 +10526,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>354</v>
       </c>
@@ -10568,7 +10568,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>356</v>
       </c>
@@ -10610,7 +10610,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>358</v>
       </c>
@@ -10652,7 +10652,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>360</v>
       </c>
@@ -10694,7 +10694,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>362</v>
       </c>
@@ -10736,7 +10736,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>364</v>
       </c>
@@ -10778,7 +10778,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>366</v>
       </c>
@@ -10820,7 +10820,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>368</v>
       </c>
@@ -10862,7 +10862,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>370</v>
       </c>
@@ -10904,7 +10904,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>372</v>
       </c>
@@ -10946,7 +10946,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>374</v>
       </c>
@@ -10988,7 +10988,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>376</v>
       </c>
@@ -11030,7 +11030,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>378</v>
       </c>
@@ -11072,7 +11072,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>380</v>
       </c>
@@ -11114,7 +11114,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>382</v>
       </c>
@@ -11156,7 +11156,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>384</v>
       </c>
@@ -11198,7 +11198,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>386</v>
       </c>
@@ -11240,7 +11240,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>388</v>
       </c>
@@ -11282,7 +11282,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>390</v>
       </c>
@@ -11324,7 +11324,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>392</v>
       </c>
@@ -11366,7 +11366,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>394</v>
       </c>
@@ -11408,7 +11408,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>396</v>
       </c>
@@ -11450,7 +11450,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>398</v>
       </c>
@@ -11492,7 +11492,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>400</v>
       </c>
@@ -11534,7 +11534,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>402</v>
       </c>
@@ -11576,7 +11576,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>404</v>
       </c>
@@ -11618,7 +11618,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>406</v>
       </c>
@@ -11660,7 +11660,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>408</v>
       </c>
@@ -11702,7 +11702,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>410</v>
       </c>
@@ -11744,7 +11744,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>412</v>
       </c>
@@ -11786,7 +11786,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>414</v>
       </c>
@@ -11828,7 +11828,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>416</v>
       </c>
@@ -11870,7 +11870,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>419</v>
       </c>
@@ -11912,7 +11912,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>422</v>
       </c>
@@ -11954,7 +11954,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>424</v>
       </c>
@@ -11996,7 +11996,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>426</v>
       </c>
@@ -12038,7 +12038,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>428</v>
       </c>
@@ -12080,7 +12080,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>430</v>
       </c>
@@ -12122,7 +12122,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>432</v>
       </c>
@@ -12164,7 +12164,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>434</v>
       </c>
@@ -12206,7 +12206,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>436</v>
       </c>
@@ -12248,7 +12248,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>438</v>
       </c>
@@ -12290,7 +12290,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>440</v>
       </c>
@@ -12332,7 +12332,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>442</v>
       </c>
@@ -12374,7 +12374,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>444</v>
       </c>
@@ -12416,7 +12416,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>446</v>
       </c>
@@ -12458,7 +12458,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>448</v>
       </c>
@@ -12500,7 +12500,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>450</v>
       </c>
@@ -12542,7 +12542,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>452</v>
       </c>
@@ -12584,7 +12584,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>454</v>
       </c>
@@ -12626,7 +12626,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>456</v>
       </c>
@@ -12668,7 +12668,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>458</v>
       </c>
@@ -12710,7 +12710,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>460</v>
       </c>
@@ -12752,7 +12752,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>462</v>
       </c>
@@ -12794,7 +12794,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>464</v>
       </c>
@@ -12836,7 +12836,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>466</v>
       </c>
@@ -12878,7 +12878,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>468</v>
       </c>
@@ -12920,7 +12920,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>470</v>
       </c>
@@ -12962,7 +12962,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>472</v>
       </c>
@@ -13004,7 +13004,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>474</v>
       </c>
@@ -13046,7 +13046,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>476</v>
       </c>
@@ -13088,7 +13088,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>478</v>
       </c>
@@ -13130,7 +13130,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>480</v>
       </c>
@@ -13172,7 +13172,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>482</v>
       </c>
@@ -13214,7 +13214,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>484</v>
       </c>
@@ -13256,7 +13256,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>486</v>
       </c>
@@ -13298,7 +13298,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>488</v>
       </c>
@@ -13340,7 +13340,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="3"/>
     </row>
-    <row r="222" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>490</v>
       </c>
@@ -13382,7 +13382,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="3"/>
     </row>
-    <row r="223" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>492</v>
       </c>
@@ -13424,7 +13424,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="3"/>
     </row>
-    <row r="224" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>494</v>
       </c>
@@ -13466,7 +13466,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
     </row>
-    <row r="225" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>496</v>
       </c>
@@ -13508,7 +13508,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="3"/>
     </row>
-    <row r="226" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>498</v>
       </c>
@@ -13550,7 +13550,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="3"/>
     </row>
-    <row r="227" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>500</v>
       </c>
@@ -13592,7 +13592,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="3"/>
     </row>
-    <row r="228" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>502</v>
       </c>
@@ -13634,7 +13634,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="3"/>
     </row>
-    <row r="229" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>504</v>
       </c>
@@ -13676,7 +13676,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
     </row>
-    <row r="230" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>506</v>
       </c>
@@ -13718,7 +13718,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="3"/>
     </row>
-    <row r="231" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>508</v>
       </c>
@@ -13760,7 +13760,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="3"/>
     </row>
-    <row r="232" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>510</v>
       </c>
@@ -13802,7 +13802,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
     </row>
-    <row r="233" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>512</v>
       </c>
@@ -13844,7 +13844,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
     </row>
-    <row r="234" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>516</v>
       </c>
@@ -13886,7 +13886,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
     </row>
-    <row r="235" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>518</v>
       </c>
@@ -13928,7 +13928,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="3"/>
     </row>
-    <row r="236" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>520</v>
       </c>
@@ -13970,7 +13970,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="3"/>
     </row>
-    <row r="237" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>522</v>
       </c>
@@ -14012,7 +14012,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="3"/>
     </row>
-    <row r="238" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>524</v>
       </c>
@@ -14054,7 +14054,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="3"/>
     </row>
-    <row r="239" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>526</v>
       </c>
@@ -14096,7 +14096,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="3"/>
     </row>
-    <row r="240" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>529</v>
       </c>
@@ -14138,7 +14138,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="3"/>
     </row>
-    <row r="241" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
         <v>531</v>
       </c>
@@ -14180,7 +14180,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="3"/>
     </row>
-    <row r="242" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>534</v>
       </c>
@@ -14222,7 +14222,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
     </row>
-    <row r="243" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>536</v>
       </c>
@@ -14264,7 +14264,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="3"/>
     </row>
-    <row r="244" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>538</v>
       </c>
@@ -14306,7 +14306,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="3"/>
     </row>
-    <row r="245" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>540</v>
       </c>
@@ -14348,7 +14348,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
     </row>
-    <row r="246" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>542</v>
       </c>
@@ -14390,7 +14390,7 @@
       <c r="Y246" s="3"/>
       <c r="Z246" s="3"/>
     </row>
-    <row r="247" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
         <v>544</v>
       </c>
@@ -14432,7 +14432,7 @@
       <c r="Y247" s="3"/>
       <c r="Z247" s="3"/>
     </row>
-    <row r="248" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>546</v>
       </c>
@@ -14474,7 +14474,7 @@
       <c r="Y248" s="3"/>
       <c r="Z248" s="3"/>
     </row>
-    <row r="249" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>548</v>
       </c>
@@ -14516,7 +14516,7 @@
       <c r="Y249" s="3"/>
       <c r="Z249" s="3"/>
     </row>
-    <row r="250" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>550</v>
       </c>
@@ -14558,7 +14558,7 @@
       <c r="Y250" s="3"/>
       <c r="Z250" s="3"/>
     </row>
-    <row r="251" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>552</v>
       </c>
@@ -14600,7 +14600,7 @@
       <c r="Y251" s="3"/>
       <c r="Z251" s="3"/>
     </row>
-    <row r="252" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>554</v>
       </c>
@@ -14642,7 +14642,7 @@
       <c r="Y252" s="3"/>
       <c r="Z252" s="3"/>
     </row>
-    <row r="253" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
         <v>556</v>
       </c>
@@ -14684,7 +14684,7 @@
       <c r="Y253" s="3"/>
       <c r="Z253" s="3"/>
     </row>
-    <row r="254" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>558</v>
       </c>
@@ -14726,7 +14726,7 @@
       <c r="Y254" s="3"/>
       <c r="Z254" s="3"/>
     </row>
-    <row r="255" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>560</v>
       </c>
@@ -14768,7 +14768,7 @@
       <c r="Y255" s="3"/>
       <c r="Z255" s="3"/>
     </row>
-    <row r="256" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>562</v>
       </c>
@@ -14810,7 +14810,7 @@
       <c r="Y256" s="3"/>
       <c r="Z256" s="3"/>
     </row>
-    <row r="257" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>564</v>
       </c>
@@ -14852,7 +14852,7 @@
       <c r="Y257" s="3"/>
       <c r="Z257" s="3"/>
     </row>
-    <row r="258" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>566</v>
       </c>
@@ -14894,7 +14894,7 @@
       <c r="Y258" s="3"/>
       <c r="Z258" s="3"/>
     </row>
-    <row r="259" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
         <v>568</v>
       </c>
@@ -14936,7 +14936,7 @@
       <c r="Y259" s="3"/>
       <c r="Z259" s="3"/>
     </row>
-    <row r="260" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>570</v>
       </c>
@@ -14978,7 +14978,7 @@
       <c r="Y260" s="3"/>
       <c r="Z260" s="3"/>
     </row>
-    <row r="261" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>572</v>
       </c>
@@ -15020,7 +15020,7 @@
       <c r="Y261" s="3"/>
       <c r="Z261" s="3"/>
     </row>
-    <row r="262" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>574</v>
       </c>
@@ -15062,7 +15062,7 @@
       <c r="Y262" s="3"/>
       <c r="Z262" s="3"/>
     </row>
-    <row r="263" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>576</v>
       </c>
@@ -15104,7 +15104,7 @@
       <c r="Y263" s="3"/>
       <c r="Z263" s="3"/>
     </row>
-    <row r="264" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>578</v>
       </c>
@@ -15146,7 +15146,7 @@
       <c r="Y264" s="3"/>
       <c r="Z264" s="3"/>
     </row>
-    <row r="265" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
         <v>580</v>
       </c>
@@ -15188,7 +15188,7 @@
       <c r="Y265" s="3"/>
       <c r="Z265" s="3"/>
     </row>
-    <row r="266" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>582</v>
       </c>
@@ -15230,7 +15230,7 @@
       <c r="Y266" s="3"/>
       <c r="Z266" s="3"/>
     </row>
-    <row r="267" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
         <v>584</v>
       </c>
@@ -15272,7 +15272,7 @@
       <c r="Y267" s="3"/>
       <c r="Z267" s="3"/>
     </row>
-    <row r="268" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>586</v>
       </c>
@@ -15314,7 +15314,7 @@
       <c r="Y268" s="3"/>
       <c r="Z268" s="3"/>
     </row>
-    <row r="269" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>588</v>
       </c>
@@ -15356,7 +15356,7 @@
       <c r="Y269" s="3"/>
       <c r="Z269" s="3"/>
     </row>
-    <row r="270" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>590</v>
       </c>
@@ -15398,7 +15398,7 @@
       <c r="Y270" s="3"/>
       <c r="Z270" s="3"/>
     </row>
-    <row r="271" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
         <v>592</v>
       </c>
@@ -15440,7 +15440,7 @@
       <c r="Y271" s="3"/>
       <c r="Z271" s="3"/>
     </row>
-    <row r="272" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>594</v>
       </c>
@@ -15482,7 +15482,7 @@
       <c r="Y272" s="3"/>
       <c r="Z272" s="3"/>
     </row>
-    <row r="273" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
         <v>596</v>
       </c>
@@ -15524,7 +15524,7 @@
       <c r="Y273" s="3"/>
       <c r="Z273" s="3"/>
     </row>
-    <row r="274" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>598</v>
       </c>
@@ -15566,7 +15566,7 @@
       <c r="Y274" s="3"/>
       <c r="Z274" s="3"/>
     </row>
-    <row r="275" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>600</v>
       </c>
@@ -15608,7 +15608,7 @@
       <c r="Y275" s="3"/>
       <c r="Z275" s="3"/>
     </row>
-    <row r="276" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>602</v>
       </c>
@@ -15650,7 +15650,7 @@
       <c r="Y276" s="3"/>
       <c r="Z276" s="3"/>
     </row>
-    <row r="277" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
         <v>604</v>
       </c>
@@ -15692,7 +15692,7 @@
       <c r="Y277" s="3"/>
       <c r="Z277" s="3"/>
     </row>
-    <row r="278" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>606</v>
       </c>
@@ -15734,7 +15734,7 @@
       <c r="Y278" s="3"/>
       <c r="Z278" s="3"/>
     </row>
-    <row r="279" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>608</v>
       </c>
@@ -15776,7 +15776,7 @@
       <c r="Y279" s="3"/>
       <c r="Z279" s="3"/>
     </row>
-    <row r="280" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>610</v>
       </c>
@@ -15818,7 +15818,7 @@
       <c r="Y280" s="3"/>
       <c r="Z280" s="3"/>
     </row>
-    <row r="281" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>612</v>
       </c>
@@ -15860,7 +15860,7 @@
       <c r="Y281" s="3"/>
       <c r="Z281" s="3"/>
     </row>
-    <row r="282" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>614</v>
       </c>
@@ -15902,7 +15902,7 @@
       <c r="Y282" s="3"/>
       <c r="Z282" s="3"/>
     </row>
-    <row r="283" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>616</v>
       </c>
@@ -15944,7 +15944,7 @@
       <c r="Y283" s="3"/>
       <c r="Z283" s="3"/>
     </row>
-    <row r="284" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>618</v>
       </c>
@@ -15986,7 +15986,7 @@
       <c r="Y284" s="3"/>
       <c r="Z284" s="3"/>
     </row>
-    <row r="285" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>620</v>
       </c>
@@ -16028,7 +16028,7 @@
       <c r="Y285" s="3"/>
       <c r="Z285" s="3"/>
     </row>
-    <row r="286" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>622</v>
       </c>
@@ -16070,7 +16070,7 @@
       <c r="Y286" s="3"/>
       <c r="Z286" s="3"/>
     </row>
-    <row r="287" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>624</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="Y287" s="3"/>
       <c r="Z287" s="3"/>
     </row>
-    <row r="288" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>626</v>
       </c>
@@ -16154,7 +16154,7 @@
       <c r="Y288" s="3"/>
       <c r="Z288" s="3"/>
     </row>
-    <row r="289" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>631</v>
       </c>
@@ -16196,7 +16196,7 @@
       <c r="Y289" s="3"/>
       <c r="Z289" s="3"/>
     </row>
-    <row r="290" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>633</v>
       </c>
@@ -16238,7 +16238,7 @@
       <c r="Y290" s="3"/>
       <c r="Z290" s="3"/>
     </row>
-    <row r="291" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>635</v>
       </c>
@@ -16280,7 +16280,7 @@
       <c r="Y291" s="3"/>
       <c r="Z291" s="3"/>
     </row>
-    <row r="292" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>638</v>
       </c>
@@ -16322,7 +16322,7 @@
       <c r="Y292" s="3"/>
       <c r="Z292" s="3"/>
     </row>
-    <row r="293" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
         <v>640</v>
       </c>
@@ -16364,7 +16364,7 @@
       <c r="Y293" s="3"/>
       <c r="Z293" s="3"/>
     </row>
-    <row r="294" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>642</v>
       </c>
@@ -16406,7 +16406,7 @@
       <c r="Y294" s="3"/>
       <c r="Z294" s="3"/>
     </row>
-    <row r="295" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
         <v>644</v>
       </c>
@@ -16448,7 +16448,7 @@
       <c r="Y295" s="3"/>
       <c r="Z295" s="3"/>
     </row>
-    <row r="296" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>646</v>
       </c>
@@ -16490,7 +16490,7 @@
       <c r="Y296" s="3"/>
       <c r="Z296" s="3"/>
     </row>
-    <row r="297" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>648</v>
       </c>
@@ -16532,7 +16532,7 @@
       <c r="Y297" s="3"/>
       <c r="Z297" s="3"/>
     </row>
-    <row r="298" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>650</v>
       </c>
@@ -16574,7 +16574,7 @@
       <c r="Y298" s="3"/>
       <c r="Z298" s="3"/>
     </row>
-    <row r="299" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
         <v>652</v>
       </c>
@@ -16616,7 +16616,7 @@
       <c r="Y299" s="3"/>
       <c r="Z299" s="3"/>
     </row>
-    <row r="300" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>654</v>
       </c>
@@ -16658,7 +16658,7 @@
       <c r="Y300" s="3"/>
       <c r="Z300" s="3"/>
     </row>
-    <row r="301" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
         <v>656</v>
       </c>
@@ -16700,7 +16700,7 @@
       <c r="Y301" s="3"/>
       <c r="Z301" s="3"/>
     </row>
-    <row r="302" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>658</v>
       </c>
@@ -16742,7 +16742,7 @@
       <c r="Y302" s="3"/>
       <c r="Z302" s="3"/>
     </row>
-    <row r="303" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
         <v>660</v>
       </c>
@@ -16784,7 +16784,7 @@
       <c r="Y303" s="3"/>
       <c r="Z303" s="3"/>
     </row>
-    <row r="304" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>662</v>
       </c>
@@ -16826,7 +16826,7 @@
       <c r="Y304" s="3"/>
       <c r="Z304" s="3"/>
     </row>
-    <row r="305" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>664</v>
       </c>
@@ -16868,7 +16868,7 @@
       <c r="Y305" s="3"/>
       <c r="Z305" s="3"/>
     </row>
-    <row r="306" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>666</v>
       </c>
@@ -16910,7 +16910,7 @@
       <c r="Y306" s="3"/>
       <c r="Z306" s="3"/>
     </row>
-    <row r="307" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>668</v>
       </c>
@@ -16952,7 +16952,7 @@
       <c r="Y307" s="3"/>
       <c r="Z307" s="3"/>
     </row>
-    <row r="308" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>670</v>
       </c>
@@ -16994,7 +16994,7 @@
       <c r="Y308" s="3"/>
       <c r="Z308" s="3"/>
     </row>
-    <row r="309" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
         <v>672</v>
       </c>
@@ -17036,7 +17036,7 @@
       <c r="Y309" s="3"/>
       <c r="Z309" s="3"/>
     </row>
-    <row r="310" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>674</v>
       </c>
@@ -17078,7 +17078,7 @@
       <c r="Y310" s="3"/>
       <c r="Z310" s="3"/>
     </row>
-    <row r="311" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>676</v>
       </c>
@@ -17120,7 +17120,7 @@
       <c r="Y311" s="3"/>
       <c r="Z311" s="3"/>
     </row>
-    <row r="312" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
         <v>678</v>
       </c>
@@ -17161,7 +17161,7 @@
       <c r="Y312" s="3"/>
       <c r="Z312" s="3"/>
     </row>
-    <row r="313" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
         <v>682</v>
       </c>
@@ -17203,7 +17203,7 @@
       <c r="Y313" s="3"/>
       <c r="Z313" s="3"/>
     </row>
-    <row r="314" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>684</v>
       </c>
@@ -17245,7 +17245,7 @@
       <c r="Y314" s="3"/>
       <c r="Z314" s="3"/>
     </row>
-    <row r="315" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>686</v>
       </c>
@@ -17287,7 +17287,7 @@
       <c r="Y315" s="3"/>
       <c r="Z315" s="3"/>
     </row>
-    <row r="316" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
         <v>688</v>
       </c>
@@ -17329,7 +17329,7 @@
       <c r="Y316" s="3"/>
       <c r="Z316" s="3"/>
     </row>
-    <row r="317" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>690</v>
       </c>
@@ -17371,7 +17371,7 @@
       <c r="Y317" s="3"/>
       <c r="Z317" s="3"/>
     </row>
-    <row r="318" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
         <v>692</v>
       </c>
@@ -17413,7 +17413,7 @@
       <c r="Y318" s="3"/>
       <c r="Z318" s="3"/>
     </row>
-    <row r="319" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>694</v>
       </c>
@@ -17455,7 +17455,7 @@
       <c r="Y319" s="3"/>
       <c r="Z319" s="3"/>
     </row>
-    <row r="320" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>696</v>
       </c>
@@ -17497,7 +17497,7 @@
       <c r="Y320" s="3"/>
       <c r="Z320" s="3"/>
     </row>
-    <row r="321" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>698</v>
       </c>
@@ -17539,7 +17539,7 @@
       <c r="Y321" s="3"/>
       <c r="Z321" s="3"/>
     </row>
-    <row r="322" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
         <v>700</v>
       </c>
@@ -17581,7 +17581,7 @@
       <c r="Y322" s="3"/>
       <c r="Z322" s="3"/>
     </row>
-    <row r="323" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>702</v>
       </c>
@@ -17623,7 +17623,7 @@
       <c r="Y323" s="3"/>
       <c r="Z323" s="3"/>
     </row>
-    <row r="324" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>705</v>
       </c>
@@ -17665,7 +17665,7 @@
       <c r="Y324" s="3"/>
       <c r="Z324" s="3"/>
     </row>
-    <row r="325" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
         <v>707</v>
       </c>
@@ -17707,7 +17707,7 @@
       <c r="Y325" s="3"/>
       <c r="Z325" s="3"/>
     </row>
-    <row r="326" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>709</v>
       </c>
@@ -17749,7 +17749,7 @@
       <c r="Y326" s="3"/>
       <c r="Z326" s="3"/>
     </row>
-    <row r="327" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
         <v>711</v>
       </c>
@@ -17791,7 +17791,7 @@
       <c r="Y327" s="3"/>
       <c r="Z327" s="3"/>
     </row>
-    <row r="328" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
         <v>713</v>
       </c>
@@ -17833,7 +17833,7 @@
       <c r="Y328" s="3"/>
       <c r="Z328" s="3"/>
     </row>
-    <row r="329" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>715</v>
       </c>
@@ -17875,7 +17875,7 @@
       <c r="Y329" s="3"/>
       <c r="Z329" s="3"/>
     </row>
-    <row r="330" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>717</v>
       </c>
@@ -17917,7 +17917,7 @@
       <c r="Y330" s="3"/>
       <c r="Z330" s="3"/>
     </row>
-    <row r="331" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
         <v>719</v>
       </c>
@@ -17959,7 +17959,7 @@
       <c r="Y331" s="3"/>
       <c r="Z331" s="3"/>
     </row>
-    <row r="332" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
         <v>721</v>
       </c>
@@ -18001,7 +18001,7 @@
       <c r="Y332" s="3"/>
       <c r="Z332" s="3"/>
     </row>
-    <row r="333" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
         <v>723</v>
       </c>
@@ -18043,7 +18043,7 @@
       <c r="Y333" s="3"/>
       <c r="Z333" s="3"/>
     </row>
-    <row r="334" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>725</v>
       </c>
@@ -18085,7 +18085,7 @@
       <c r="Y334" s="3"/>
       <c r="Z334" s="3"/>
     </row>
-    <row r="335" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>727</v>
       </c>
@@ -18127,7 +18127,7 @@
       <c r="Y335" s="3"/>
       <c r="Z335" s="3"/>
     </row>
-    <row r="336" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>729</v>
       </c>
@@ -18169,7 +18169,7 @@
       <c r="Y336" s="3"/>
       <c r="Z336" s="3"/>
     </row>
-    <row r="337" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
         <v>731</v>
       </c>
@@ -18211,7 +18211,7 @@
       <c r="Y337" s="3"/>
       <c r="Z337" s="3"/>
     </row>
-    <row r="338" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>733</v>
       </c>
@@ -18253,7 +18253,7 @@
       <c r="Y338" s="3"/>
       <c r="Z338" s="3"/>
     </row>
-    <row r="339" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>735</v>
       </c>
@@ -18295,7 +18295,7 @@
       <c r="Y339" s="3"/>
       <c r="Z339" s="3"/>
     </row>
-    <row r="340" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>737</v>
       </c>
@@ -18337,7 +18337,7 @@
       <c r="Y340" s="3"/>
       <c r="Z340" s="3"/>
     </row>
-    <row r="341" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>739</v>
       </c>
@@ -18379,7 +18379,7 @@
       <c r="Y341" s="3"/>
       <c r="Z341" s="3"/>
     </row>
-    <row r="342" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
         <v>741</v>
       </c>
@@ -18421,7 +18421,7 @@
       <c r="Y342" s="3"/>
       <c r="Z342" s="3"/>
     </row>
-    <row r="343" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
         <v>743</v>
       </c>
@@ -18463,7 +18463,7 @@
       <c r="Y343" s="3"/>
       <c r="Z343" s="3"/>
     </row>
-    <row r="344" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>745</v>
       </c>
@@ -18505,7 +18505,7 @@
       <c r="Y344" s="3"/>
       <c r="Z344" s="3"/>
     </row>
-    <row r="345" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>747</v>
       </c>
@@ -18547,7 +18547,7 @@
       <c r="Y345" s="3"/>
       <c r="Z345" s="3"/>
     </row>
-    <row r="346" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>749</v>
       </c>
@@ -18589,7 +18589,7 @@
       <c r="Y346" s="3"/>
       <c r="Z346" s="3"/>
     </row>
-    <row r="347" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
         <v>751</v>
       </c>
@@ -18629,7 +18629,7 @@
       <c r="Y347" s="3"/>
       <c r="Z347" s="3"/>
     </row>
-    <row r="348" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
         <v>756</v>
       </c>
@@ -18671,7 +18671,7 @@
       <c r="Y348" s="3"/>
       <c r="Z348" s="3"/>
     </row>
-    <row r="349" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
         <v>759</v>
       </c>
@@ -18711,7 +18711,7 @@
       <c r="Y349" s="3"/>
       <c r="Z349" s="3"/>
     </row>
-    <row r="350" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
         <v>761</v>
       </c>
@@ -18751,7 +18751,7 @@
       <c r="Y350" s="3"/>
       <c r="Z350" s="3"/>
     </row>
-    <row r="351" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>763</v>
       </c>
@@ -18787,7 +18787,7 @@
       <c r="Y351" s="3"/>
       <c r="Z351" s="3"/>
     </row>
-    <row r="352" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>765</v>
       </c>
@@ -18829,7 +18829,7 @@
       <c r="Y352" s="3"/>
       <c r="Z352" s="3"/>
     </row>
-    <row r="353" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
         <v>769</v>
       </c>
@@ -18871,7 +18871,7 @@
       <c r="Y353" s="3"/>
       <c r="Z353" s="3"/>
     </row>
-    <row r="354" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>771</v>
       </c>
@@ -18913,7 +18913,7 @@
       <c r="Y354" s="3"/>
       <c r="Z354" s="3"/>
     </row>
-    <row r="355" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
         <v>773</v>
       </c>
@@ -18955,7 +18955,7 @@
       <c r="Y355" s="3"/>
       <c r="Z355" s="3"/>
     </row>
-    <row r="356" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>775</v>
       </c>
@@ -18997,7 +18997,7 @@
       <c r="Y356" s="3"/>
       <c r="Z356" s="3"/>
     </row>
-    <row r="357" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
         <v>777</v>
       </c>
@@ -19039,7 +19039,7 @@
       <c r="Y357" s="3"/>
       <c r="Z357" s="3"/>
     </row>
-    <row r="358" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>779</v>
       </c>
@@ -19081,7 +19081,7 @@
       <c r="Y358" s="3"/>
       <c r="Z358" s="3"/>
     </row>
-    <row r="359" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>781</v>
       </c>
@@ -19123,7 +19123,7 @@
       <c r="Y359" s="3"/>
       <c r="Z359" s="3"/>
     </row>
-    <row r="360" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>783</v>
       </c>
@@ -19165,7 +19165,7 @@
       <c r="Y360" s="3"/>
       <c r="Z360" s="3"/>
     </row>
-    <row r="361" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
         <v>785</v>
       </c>
@@ -19207,7 +19207,7 @@
       <c r="Y361" s="3"/>
       <c r="Z361" s="3"/>
     </row>
-    <row r="362" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>787</v>
       </c>
@@ -19249,7 +19249,7 @@
       <c r="Y362" s="3"/>
       <c r="Z362" s="3"/>
     </row>
-    <row r="363" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>790</v>
       </c>
@@ -19291,7 +19291,7 @@
       <c r="Y363" s="3"/>
       <c r="Z363" s="3"/>
     </row>
-    <row r="364" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
         <v>793</v>
       </c>
@@ -19333,7 +19333,7 @@
       <c r="Y364" s="3"/>
       <c r="Z364" s="3"/>
     </row>
-    <row r="365" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>795</v>
       </c>
@@ -19375,7 +19375,7 @@
       <c r="Y365" s="3"/>
       <c r="Z365" s="3"/>
     </row>
-    <row r="366" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>797</v>
       </c>
@@ -19417,7 +19417,7 @@
       <c r="Y366" s="3"/>
       <c r="Z366" s="3"/>
     </row>
-    <row r="367" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
         <v>799</v>
       </c>
@@ -19459,7 +19459,7 @@
       <c r="Y367" s="3"/>
       <c r="Z367" s="3"/>
     </row>
-    <row r="368" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>801</v>
       </c>
@@ -19501,7 +19501,7 @@
       <c r="Y368" s="3"/>
       <c r="Z368" s="3"/>
     </row>
-    <row r="369" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>803</v>
       </c>
@@ -19543,7 +19543,7 @@
       <c r="Y369" s="3"/>
       <c r="Z369" s="3"/>
     </row>
-    <row r="370" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>805</v>
       </c>
@@ -19585,7 +19585,7 @@
       <c r="Y370" s="3"/>
       <c r="Z370" s="3"/>
     </row>
-    <row r="371" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
         <v>807</v>
       </c>
@@ -19627,7 +19627,7 @@
       <c r="Y371" s="3"/>
       <c r="Z371" s="3"/>
     </row>
-    <row r="372" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>809</v>
       </c>
@@ -19669,7 +19669,7 @@
       <c r="Y372" s="3"/>
       <c r="Z372" s="3"/>
     </row>
-    <row r="373" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>811</v>
       </c>
@@ -19711,7 +19711,7 @@
       <c r="Y373" s="3"/>
       <c r="Z373" s="3"/>
     </row>
-    <row r="374" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>813</v>
       </c>
@@ -19753,7 +19753,7 @@
       <c r="Y374" s="3"/>
       <c r="Z374" s="3"/>
     </row>
-    <row r="375" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
         <v>816</v>
       </c>
@@ -19795,7 +19795,7 @@
       <c r="Y375" s="3"/>
       <c r="Z375" s="3"/>
     </row>
-    <row r="376" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>818</v>
       </c>
@@ -19837,7 +19837,7 @@
       <c r="Y376" s="3"/>
       <c r="Z376" s="3"/>
     </row>
-    <row r="377" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>820</v>
       </c>
@@ -19879,7 +19879,7 @@
       <c r="Y377" s="3"/>
       <c r="Z377" s="3"/>
     </row>
-    <row r="378" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>822</v>
       </c>
@@ -19921,7 +19921,7 @@
       <c r="Y378" s="3"/>
       <c r="Z378" s="3"/>
     </row>
-    <row r="379" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
         <v>824</v>
       </c>
@@ -19963,7 +19963,7 @@
       <c r="Y379" s="3"/>
       <c r="Z379" s="3"/>
     </row>
-    <row r="380" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>826</v>
       </c>
@@ -20005,7 +20005,7 @@
       <c r="Y380" s="3"/>
       <c r="Z380" s="3"/>
     </row>
-    <row r="381" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
         <v>828</v>
       </c>
@@ -20047,7 +20047,7 @@
       <c r="Y381" s="3"/>
       <c r="Z381" s="3"/>
     </row>
-    <row r="382" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
         <v>830</v>
       </c>
@@ -20089,7 +20089,7 @@
       <c r="Y382" s="3"/>
       <c r="Z382" s="3"/>
     </row>
-    <row r="383" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
         <v>832</v>
       </c>
@@ -20131,7 +20131,7 @@
       <c r="Y383" s="3"/>
       <c r="Z383" s="3"/>
     </row>
-    <row r="384" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>834</v>
       </c>
@@ -20173,7 +20173,7 @@
       <c r="Y384" s="3"/>
       <c r="Z384" s="3"/>
     </row>
-    <row r="385" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
         <v>836</v>
       </c>
@@ -20215,7 +20215,7 @@
       <c r="Y385" s="3"/>
       <c r="Z385" s="3"/>
     </row>
-    <row r="386" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
         <v>838</v>
       </c>
@@ -20257,7 +20257,7 @@
       <c r="Y386" s="3"/>
       <c r="Z386" s="3"/>
     </row>
-    <row r="387" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
         <v>840</v>
       </c>
@@ -20299,7 +20299,7 @@
       <c r="Y387" s="3"/>
       <c r="Z387" s="3"/>
     </row>
-    <row r="388" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
         <v>842</v>
       </c>
@@ -20341,7 +20341,7 @@
       <c r="Y388" s="3"/>
       <c r="Z388" s="3"/>
     </row>
-    <row r="389" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
         <v>844</v>
       </c>
@@ -20383,7 +20383,7 @@
       <c r="Y389" s="3"/>
       <c r="Z389" s="3"/>
     </row>
-    <row r="390" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
         <v>846</v>
       </c>
@@ -20425,7 +20425,7 @@
       <c r="Y390" s="3"/>
       <c r="Z390" s="3"/>
     </row>
-    <row r="391" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
         <v>848</v>
       </c>
@@ -20467,7 +20467,7 @@
       <c r="Y391" s="3"/>
       <c r="Z391" s="3"/>
     </row>
-    <row r="392" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
         <v>850</v>
       </c>
@@ -20509,7 +20509,7 @@
       <c r="Y392" s="3"/>
       <c r="Z392" s="3"/>
     </row>
-    <row r="393" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
         <v>853</v>
       </c>
@@ -20551,7 +20551,7 @@
       <c r="Y393" s="3"/>
       <c r="Z393" s="3"/>
     </row>
-    <row r="394" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
         <v>855</v>
       </c>
@@ -20593,7 +20593,7 @@
       <c r="Y394" s="3"/>
       <c r="Z394" s="3"/>
     </row>
-    <row r="395" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
         <v>857</v>
       </c>
@@ -20635,7 +20635,7 @@
       <c r="Y395" s="3"/>
       <c r="Z395" s="3"/>
     </row>
-    <row r="396" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>859</v>
       </c>
@@ -20671,7 +20671,7 @@
       <c r="Y396" s="3"/>
       <c r="Z396" s="3"/>
     </row>
-    <row r="397" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
         <v>861</v>
       </c>
@@ -20707,7 +20707,7 @@
       <c r="Y397" s="3"/>
       <c r="Z397" s="3"/>
     </row>
-    <row r="398" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
         <v>864</v>
       </c>
@@ -20743,7 +20743,7 @@
       <c r="Y398" s="3"/>
       <c r="Z398" s="3"/>
     </row>
-    <row r="399" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
         <v>866</v>
       </c>
@@ -20779,7 +20779,7 @@
       <c r="Y399" s="3"/>
       <c r="Z399" s="3"/>
     </row>
-    <row r="400" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
         <v>868</v>
       </c>
@@ -20815,7 +20815,7 @@
       <c r="Y400" s="3"/>
       <c r="Z400" s="3"/>
     </row>
-    <row r="401" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
         <v>870</v>
       </c>
@@ -20851,7 +20851,7 @@
       <c r="Y401" s="3"/>
       <c r="Z401" s="3"/>
     </row>
-    <row r="402" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
         <v>873</v>
       </c>
@@ -20887,7 +20887,7 @@
       <c r="Y402" s="3"/>
       <c r="Z402" s="3"/>
     </row>
-    <row r="403" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
         <v>875</v>
       </c>
@@ -20929,7 +20929,7 @@
       <c r="Y403" s="3"/>
       <c r="Z403" s="3"/>
     </row>
-    <row r="404" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
         <v>878</v>
       </c>
@@ -20971,7 +20971,7 @@
       <c r="Y404" s="3"/>
       <c r="Z404" s="3"/>
     </row>
-    <row r="405" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
         <v>880</v>
       </c>
@@ -21013,7 +21013,7 @@
       <c r="Y405" s="3"/>
       <c r="Z405" s="3"/>
     </row>
-    <row r="406" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
         <v>882</v>
       </c>
@@ -21055,7 +21055,7 @@
       <c r="Y406" s="3"/>
       <c r="Z406" s="3"/>
     </row>
-    <row r="407" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
         <v>884</v>
       </c>
@@ -21097,7 +21097,7 @@
       <c r="Y407" s="3"/>
       <c r="Z407" s="3"/>
     </row>
-    <row r="408" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
         <v>886</v>
       </c>
@@ -21139,7 +21139,7 @@
       <c r="Y408" s="3"/>
       <c r="Z408" s="3"/>
     </row>
-    <row r="409" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
         <v>888</v>
       </c>
@@ -21181,7 +21181,7 @@
       <c r="Y409" s="3"/>
       <c r="Z409" s="3"/>
     </row>
-    <row r="410" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
         <v>890</v>
       </c>
@@ -21223,7 +21223,7 @@
       <c r="Y410" s="3"/>
       <c r="Z410" s="3"/>
     </row>
-    <row r="411" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
         <v>892</v>
       </c>
@@ -21265,7 +21265,7 @@
       <c r="Y411" s="3"/>
       <c r="Z411" s="3"/>
     </row>
-    <row r="412" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
         <v>894</v>
       </c>
@@ -21307,7 +21307,7 @@
       <c r="Y412" s="3"/>
       <c r="Z412" s="3"/>
     </row>
-    <row r="413" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
         <v>896</v>
       </c>
@@ -21349,7 +21349,7 @@
       <c r="Y413" s="3"/>
       <c r="Z413" s="3"/>
     </row>
-    <row r="414" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
         <v>898</v>
       </c>
@@ -21391,7 +21391,7 @@
       <c r="Y414" s="3"/>
       <c r="Z414" s="3"/>
     </row>
-    <row r="415" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
         <v>901</v>
       </c>
@@ -21433,7 +21433,7 @@
       <c r="Y415" s="3"/>
       <c r="Z415" s="3"/>
     </row>
-    <row r="416" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
         <v>903</v>
       </c>
@@ -21475,7 +21475,7 @@
       <c r="Y416" s="3"/>
       <c r="Z416" s="3"/>
     </row>
-    <row r="417" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
         <v>905</v>
       </c>
@@ -21517,7 +21517,7 @@
       <c r="Y417" s="3"/>
       <c r="Z417" s="3"/>
     </row>
-    <row r="418" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
         <v>907</v>
       </c>
@@ -21559,7 +21559,7 @@
       <c r="Y418" s="3"/>
       <c r="Z418" s="3"/>
     </row>
-    <row r="419" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
         <v>909</v>
       </c>
@@ -21601,7 +21601,7 @@
       <c r="Y419" s="3"/>
       <c r="Z419" s="3"/>
     </row>
-    <row r="420" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
         <v>911</v>
       </c>
@@ -21643,7 +21643,7 @@
       <c r="Y420" s="3"/>
       <c r="Z420" s="3"/>
     </row>
-    <row r="421" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
         <v>913</v>
       </c>
@@ -21685,7 +21685,7 @@
       <c r="Y421" s="3"/>
       <c r="Z421" s="3"/>
     </row>
-    <row r="422" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
         <v>915</v>
       </c>
@@ -21727,7 +21727,7 @@
       <c r="Y422" s="3"/>
       <c r="Z422" s="3"/>
     </row>
-    <row r="423" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
         <v>917</v>
       </c>
@@ -21769,7 +21769,7 @@
       <c r="Y423" s="3"/>
       <c r="Z423" s="3"/>
     </row>
-    <row r="424" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
         <v>919</v>
       </c>
@@ -21811,7 +21811,7 @@
       <c r="Y424" s="3"/>
       <c r="Z424" s="3"/>
     </row>
-    <row r="425" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
         <v>921</v>
       </c>
@@ -21853,7 +21853,7 @@
       <c r="Y425" s="3"/>
       <c r="Z425" s="3"/>
     </row>
-    <row r="426" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
         <v>924</v>
       </c>
@@ -21895,7 +21895,7 @@
       <c r="Y426" s="3"/>
       <c r="Z426" s="3"/>
     </row>
-    <row r="427" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
         <v>926</v>
       </c>
@@ -21937,7 +21937,7 @@
       <c r="Y427" s="3"/>
       <c r="Z427" s="3"/>
     </row>
-    <row r="428" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
         <v>928</v>
       </c>
@@ -21979,7 +21979,7 @@
       <c r="Y428" s="3"/>
       <c r="Z428" s="3"/>
     </row>
-    <row r="429" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
         <v>930</v>
       </c>
@@ -22021,7 +22021,7 @@
       <c r="Y429" s="3"/>
       <c r="Z429" s="3"/>
     </row>
-    <row r="430" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
         <v>932</v>
       </c>
@@ -22063,7 +22063,7 @@
       <c r="Y430" s="3"/>
       <c r="Z430" s="3"/>
     </row>
-    <row r="431" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
         <v>934</v>
       </c>
@@ -22105,7 +22105,7 @@
       <c r="Y431" s="3"/>
       <c r="Z431" s="3"/>
     </row>
-    <row r="432" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
         <v>936</v>
       </c>
@@ -22147,7 +22147,7 @@
       <c r="Y432" s="3"/>
       <c r="Z432" s="3"/>
     </row>
-    <row r="433" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
         <v>938</v>
       </c>
@@ -22189,7 +22189,7 @@
       <c r="Y433" s="3"/>
       <c r="Z433" s="3"/>
     </row>
-    <row r="434" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>940</v>
       </c>
@@ -22231,7 +22231,7 @@
       <c r="Y434" s="3"/>
       <c r="Z434" s="3"/>
     </row>
-    <row r="435" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>942</v>
       </c>
@@ -22273,7 +22273,7 @@
       <c r="Y435" s="3"/>
       <c r="Z435" s="3"/>
     </row>
-    <row r="436" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>944</v>
       </c>
@@ -22315,7 +22315,7 @@
       <c r="Y436" s="3"/>
       <c r="Z436" s="3"/>
     </row>
-    <row r="437" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>946</v>
       </c>
@@ -22357,7 +22357,7 @@
       <c r="Y437" s="3"/>
       <c r="Z437" s="3"/>
     </row>
-    <row r="438" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
         <v>948</v>
       </c>
@@ -22399,7 +22399,7 @@
       <c r="Y438" s="3"/>
       <c r="Z438" s="3"/>
     </row>
-    <row r="439" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
         <v>950</v>
       </c>
@@ -22441,7 +22441,7 @@
       <c r="Y439" s="3"/>
       <c r="Z439" s="3"/>
     </row>
-    <row r="440" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
         <v>952</v>
       </c>
@@ -22483,7 +22483,7 @@
       <c r="Y440" s="3"/>
       <c r="Z440" s="3"/>
     </row>
-    <row r="441" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
         <v>954</v>
       </c>
@@ -22525,7 +22525,7 @@
       <c r="Y441" s="3"/>
       <c r="Z441" s="3"/>
     </row>
-    <row r="442" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
         <v>956</v>
       </c>
@@ -22567,7 +22567,7 @@
       <c r="Y442" s="3"/>
       <c r="Z442" s="3"/>
     </row>
-    <row r="443" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
         <v>958</v>
       </c>
@@ -22609,7 +22609,7 @@
       <c r="Y443" s="3"/>
       <c r="Z443" s="3"/>
     </row>
-    <row r="444" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
         <v>960</v>
       </c>
@@ -22651,7 +22651,7 @@
       <c r="Y444" s="3"/>
       <c r="Z444" s="3"/>
     </row>
-    <row r="445" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
         <v>962</v>
       </c>
@@ -22693,7 +22693,7 @@
       <c r="Y445" s="3"/>
       <c r="Z445" s="3"/>
     </row>
-    <row r="446" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
         <v>964</v>
       </c>
@@ -22735,7 +22735,7 @@
       <c r="Y446" s="3"/>
       <c r="Z446" s="3"/>
     </row>
-    <row r="447" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
         <v>966</v>
       </c>
@@ -22771,7 +22771,7 @@
       <c r="Y447" s="3"/>
       <c r="Z447" s="3"/>
     </row>
-    <row r="448" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
         <v>968</v>
       </c>
@@ -22807,7 +22807,7 @@
       <c r="Y448" s="3"/>
       <c r="Z448" s="3"/>
     </row>
-    <row r="449" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
         <v>970</v>
       </c>
@@ -22843,7 +22843,7 @@
       <c r="Y449" s="3"/>
       <c r="Z449" s="3"/>
     </row>
-    <row r="450" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
         <v>972</v>
       </c>
@@ -22879,7 +22879,7 @@
       <c r="Y450" s="3"/>
       <c r="Z450" s="3"/>
     </row>
-    <row r="451" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="3" t="s">
         <v>974</v>
       </c>
@@ -22915,7 +22915,7 @@
       <c r="Y451" s="3"/>
       <c r="Z451" s="3"/>
     </row>
-    <row r="452" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
         <v>976</v>
       </c>
@@ -22951,7 +22951,7 @@
       <c r="Y452" s="3"/>
       <c r="Z452" s="3"/>
     </row>
-    <row r="453" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
         <v>978</v>
       </c>
@@ -22987,7 +22987,7 @@
       <c r="Y453" s="3"/>
       <c r="Z453" s="3"/>
     </row>
-    <row r="454" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
         <v>980</v>
       </c>
@@ -23023,7 +23023,7 @@
       <c r="Y454" s="3"/>
       <c r="Z454" s="3"/>
     </row>
-    <row r="455" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
         <v>982</v>
       </c>
@@ -23059,7 +23059,7 @@
       <c r="Y455" s="3"/>
       <c r="Z455" s="3"/>
     </row>
-    <row r="456" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
         <v>984</v>
       </c>
@@ -23095,7 +23095,7 @@
       <c r="Y456" s="3"/>
       <c r="Z456" s="3"/>
     </row>
-    <row r="457" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
         <v>986</v>
       </c>
@@ -23131,7 +23131,7 @@
       <c r="Y457" s="3"/>
       <c r="Z457" s="3"/>
     </row>
-    <row r="458" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
         <v>988</v>
       </c>
@@ -23173,7 +23173,7 @@
       <c r="Y458" s="3"/>
       <c r="Z458" s="3"/>
     </row>
-    <row r="459" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
         <v>993</v>
       </c>
@@ -23215,7 +23215,7 @@
       <c r="Y459" s="3"/>
       <c r="Z459" s="3"/>
     </row>
-    <row r="460" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
         <v>995</v>
       </c>
@@ -23257,7 +23257,7 @@
       <c r="Y460" s="3"/>
       <c r="Z460" s="3"/>
     </row>
-    <row r="461" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
         <v>997</v>
       </c>
@@ -23299,7 +23299,7 @@
       <c r="Y461" s="3"/>
       <c r="Z461" s="3"/>
     </row>
-    <row r="462" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
         <v>999</v>
       </c>
@@ -23341,7 +23341,7 @@
       <c r="Y462" s="3"/>
       <c r="Z462" s="3"/>
     </row>
-    <row r="463" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
         <v>1003</v>
       </c>
@@ -23383,7 +23383,7 @@
       <c r="Y463" s="3"/>
       <c r="Z463" s="3"/>
     </row>
-    <row r="464" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
         <v>1005</v>
       </c>
@@ -23425,7 +23425,7 @@
       <c r="Y464" s="3"/>
       <c r="Z464" s="3"/>
     </row>
-    <row r="465" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
         <v>1007</v>
       </c>
@@ -23467,7 +23467,7 @@
       <c r="Y465" s="3"/>
       <c r="Z465" s="3"/>
     </row>
-    <row r="466" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
         <v>1009</v>
       </c>
@@ -23509,7 +23509,7 @@
       <c r="Y466" s="3"/>
       <c r="Z466" s="3"/>
     </row>
-    <row r="467" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
         <v>1011</v>
       </c>
@@ -23551,7 +23551,7 @@
       <c r="Y467" s="3"/>
       <c r="Z467" s="3"/>
     </row>
-    <row r="468" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
         <v>1013</v>
       </c>
@@ -23593,7 +23593,7 @@
       <c r="Y468" s="3"/>
       <c r="Z468" s="3"/>
     </row>
-    <row r="469" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
         <v>1015</v>
       </c>
@@ -23635,7 +23635,7 @@
       <c r="Y469" s="3"/>
       <c r="Z469" s="3"/>
     </row>
-    <row r="470" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
         <v>1017</v>
       </c>
@@ -23677,7 +23677,7 @@
       <c r="Y470" s="3"/>
       <c r="Z470" s="3"/>
     </row>
-    <row r="471" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
         <v>1019</v>
       </c>
@@ -23719,7 +23719,7 @@
       <c r="Y471" s="3"/>
       <c r="Z471" s="3"/>
     </row>
-    <row r="472" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
         <v>1021</v>
       </c>
@@ -23761,7 +23761,7 @@
       <c r="Y472" s="3"/>
       <c r="Z472" s="3"/>
     </row>
-    <row r="473" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
         <v>1023</v>
       </c>
@@ -23803,7 +23803,7 @@
       <c r="Y473" s="3"/>
       <c r="Z473" s="3"/>
     </row>
-    <row r="474" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
         <v>1025</v>
       </c>
@@ -23845,7 +23845,7 @@
       <c r="Y474" s="3"/>
       <c r="Z474" s="3"/>
     </row>
-    <row r="475" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
         <v>1027</v>
       </c>
@@ -23887,7 +23887,7 @@
       <c r="Y475" s="3"/>
       <c r="Z475" s="3"/>
     </row>
-    <row r="476" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
         <v>1029</v>
       </c>
@@ -23929,7 +23929,7 @@
       <c r="Y476" s="3"/>
       <c r="Z476" s="3"/>
     </row>
-    <row r="477" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
         <v>1031</v>
       </c>
@@ -23971,7 +23971,7 @@
       <c r="Y477" s="3"/>
       <c r="Z477" s="3"/>
     </row>
-    <row r="478" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
         <v>1033</v>
       </c>
@@ -24013,7 +24013,7 @@
       <c r="Y478" s="3"/>
       <c r="Z478" s="3"/>
     </row>
-    <row r="479" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
         <v>1035</v>
       </c>
@@ -24055,7 +24055,7 @@
       <c r="Y479" s="3"/>
       <c r="Z479" s="3"/>
     </row>
-    <row r="480" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
         <v>1037</v>
       </c>
@@ -24097,7 +24097,7 @@
       <c r="Y480" s="3"/>
       <c r="Z480" s="3"/>
     </row>
-    <row r="481" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="3" t="s">
         <v>1039</v>
       </c>
@@ -24139,7 +24139,7 @@
       <c r="Y481" s="3"/>
       <c r="Z481" s="3"/>
     </row>
-    <row r="482" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
         <v>1041</v>
       </c>
@@ -24181,7 +24181,7 @@
       <c r="Y482" s="3"/>
       <c r="Z482" s="3"/>
     </row>
-    <row r="483" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
         <v>1045</v>
       </c>
@@ -24223,7 +24223,7 @@
       <c r="Y483" s="3"/>
       <c r="Z483" s="3"/>
     </row>
-    <row r="484" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
         <v>1047</v>
       </c>
@@ -24265,7 +24265,7 @@
       <c r="Y484" s="3"/>
       <c r="Z484" s="3"/>
     </row>
-    <row r="485" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
         <v>1049</v>
       </c>
@@ -24307,7 +24307,7 @@
       <c r="Y485" s="3"/>
       <c r="Z485" s="3"/>
     </row>
-    <row r="486" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
         <v>1051</v>
       </c>
@@ -24349,7 +24349,7 @@
       <c r="Y486" s="3"/>
       <c r="Z486" s="3"/>
     </row>
-    <row r="487" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
         <v>1053</v>
       </c>
@@ -24391,7 +24391,7 @@
       <c r="Y487" s="3"/>
       <c r="Z487" s="3"/>
     </row>
-    <row r="488" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
         <v>1055</v>
       </c>
@@ -24433,7 +24433,7 @@
       <c r="Y488" s="3"/>
       <c r="Z488" s="3"/>
     </row>
-    <row r="489" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
         <v>1057</v>
       </c>
@@ -24475,7 +24475,7 @@
       <c r="Y489" s="3"/>
       <c r="Z489" s="3"/>
     </row>
-    <row r="490" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
         <v>1059</v>
       </c>
@@ -24517,7 +24517,7 @@
       <c r="Y490" s="3"/>
       <c r="Z490" s="3"/>
     </row>
-    <row r="491" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
         <v>1061</v>
       </c>
@@ -24559,7 +24559,7 @@
       <c r="Y491" s="3"/>
       <c r="Z491" s="3"/>
     </row>
-    <row r="492" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
         <v>1063</v>
       </c>
@@ -24601,7 +24601,7 @@
       <c r="Y492" s="3"/>
       <c r="Z492" s="3"/>
     </row>
-    <row r="493" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
         <v>1065</v>
       </c>
@@ -24643,7 +24643,7 @@
       <c r="Y493" s="3"/>
       <c r="Z493" s="3"/>
     </row>
-    <row r="494" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
         <v>1067</v>
       </c>
@@ -24685,7 +24685,7 @@
       <c r="Y494" s="3"/>
       <c r="Z494" s="3"/>
     </row>
-    <row r="495" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
         <v>1070</v>
       </c>
@@ -24727,7 +24727,7 @@
       <c r="Y495" s="3"/>
       <c r="Z495" s="3"/>
     </row>
-    <row r="496" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
         <v>1072</v>
       </c>
@@ -24769,7 +24769,7 @@
       <c r="Y496" s="3"/>
       <c r="Z496" s="3"/>
     </row>
-    <row r="497" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
         <v>1074</v>
       </c>
@@ -24811,7 +24811,7 @@
       <c r="Y497" s="3"/>
       <c r="Z497" s="3"/>
     </row>
-    <row r="498" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
         <v>1078</v>
       </c>
@@ -24853,7 +24853,7 @@
       <c r="Y498" s="3"/>
       <c r="Z498" s="3"/>
     </row>
-    <row r="499" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="3" t="s">
         <v>1080</v>
       </c>
@@ -24895,7 +24895,7 @@
       <c r="Y499" s="3"/>
       <c r="Z499" s="3"/>
     </row>
-    <row r="500" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
         <v>1082</v>
       </c>
@@ -24937,7 +24937,7 @@
       <c r="Y500" s="3"/>
       <c r="Z500" s="3"/>
     </row>
-    <row r="501" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
         <v>1084</v>
       </c>
@@ -24979,7 +24979,7 @@
       <c r="Y501" s="3"/>
       <c r="Z501" s="3"/>
     </row>
-    <row r="502" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
         <v>1086</v>
       </c>
@@ -25021,7 +25021,7 @@
       <c r="Y502" s="3"/>
       <c r="Z502" s="3"/>
     </row>
-    <row r="503" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
         <v>1088</v>
       </c>
@@ -25063,7 +25063,7 @@
       <c r="Y503" s="3"/>
       <c r="Z503" s="3"/>
     </row>
-    <row r="504" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
         <v>1090</v>
       </c>
@@ -25105,7 +25105,7 @@
       <c r="Y504" s="3"/>
       <c r="Z504" s="3"/>
     </row>
-    <row r="505" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
         <v>1092</v>
       </c>
@@ -25147,7 +25147,7 @@
       <c r="Y505" s="3"/>
       <c r="Z505" s="3"/>
     </row>
-    <row r="506" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
         <v>1094</v>
       </c>
@@ -25189,7 +25189,7 @@
       <c r="Y506" s="3"/>
       <c r="Z506" s="3"/>
     </row>
-    <row r="507" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
         <v>1096</v>
       </c>
@@ -25231,7 +25231,7 @@
       <c r="Y507" s="3"/>
       <c r="Z507" s="3"/>
     </row>
-    <row r="508" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
         <v>1098</v>
       </c>
@@ -25273,7 +25273,7 @@
       <c r="Y508" s="3"/>
       <c r="Z508" s="3"/>
     </row>
-    <row r="509" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
         <v>1100</v>
       </c>
@@ -25315,7 +25315,7 @@
       <c r="Y509" s="3"/>
       <c r="Z509" s="3"/>
     </row>
-    <row r="510" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
         <v>1102</v>
       </c>
@@ -25357,7 +25357,7 @@
       <c r="Y510" s="3"/>
       <c r="Z510" s="3"/>
     </row>
-    <row r="511" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="3" t="s">
         <v>1104</v>
       </c>
@@ -25399,7 +25399,7 @@
       <c r="Y511" s="3"/>
       <c r="Z511" s="3"/>
     </row>
-    <row r="512" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
         <v>1106</v>
       </c>
@@ -25441,7 +25441,7 @@
       <c r="Y512" s="3"/>
       <c r="Z512" s="3"/>
     </row>
-    <row r="513" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
         <v>1108</v>
       </c>
@@ -25483,7 +25483,7 @@
       <c r="Y513" s="3"/>
       <c r="Z513" s="3"/>
     </row>
-    <row r="514" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
         <v>1110</v>
       </c>
@@ -25525,7 +25525,7 @@
       <c r="Y514" s="3"/>
       <c r="Z514" s="3"/>
     </row>
-    <row r="515" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
         <v>1112</v>
       </c>
@@ -25567,7 +25567,7 @@
       <c r="Y515" s="3"/>
       <c r="Z515" s="3"/>
     </row>
-    <row r="516" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
         <v>1114</v>
       </c>
@@ -25609,7 +25609,7 @@
       <c r="Y516" s="3"/>
       <c r="Z516" s="3"/>
     </row>
-    <row r="517" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="3" t="s">
         <v>1116</v>
       </c>
@@ -25651,7 +25651,7 @@
       <c r="Y517" s="3"/>
       <c r="Z517" s="3"/>
     </row>
-    <row r="518" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
         <v>1120</v>
       </c>
@@ -25693,7 +25693,7 @@
       <c r="Y518" s="3"/>
       <c r="Z518" s="3"/>
     </row>
-    <row r="519" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
         <v>1122</v>
       </c>
@@ -25735,7 +25735,7 @@
       <c r="Y519" s="3"/>
       <c r="Z519" s="3"/>
     </row>
-    <row r="520" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
         <v>1124</v>
       </c>
@@ -25777,7 +25777,7 @@
       <c r="Y520" s="3"/>
       <c r="Z520" s="3"/>
     </row>
-    <row r="521" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
         <v>1126</v>
       </c>
@@ -25819,7 +25819,7 @@
       <c r="Y521" s="3"/>
       <c r="Z521" s="3"/>
     </row>
-    <row r="522" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
         <v>1128</v>
       </c>
@@ -25861,7 +25861,7 @@
       <c r="Y522" s="3"/>
       <c r="Z522" s="3"/>
     </row>
-    <row r="523" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
         <v>1130</v>
       </c>
@@ -25903,7 +25903,7 @@
       <c r="Y523" s="3"/>
       <c r="Z523" s="3"/>
     </row>
-    <row r="524" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
         <v>1132</v>
       </c>
@@ -25945,7 +25945,7 @@
       <c r="Y524" s="3"/>
       <c r="Z524" s="3"/>
     </row>
-    <row r="525" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
         <v>1134</v>
       </c>
@@ -25987,7 +25987,7 @@
       <c r="Y525" s="3"/>
       <c r="Z525" s="3"/>
     </row>
-    <row r="526" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
         <v>1136</v>
       </c>
@@ -26029,7 +26029,7 @@
       <c r="Y526" s="3"/>
       <c r="Z526" s="3"/>
     </row>
-    <row r="527" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
         <v>1138</v>
       </c>
@@ -26071,7 +26071,7 @@
       <c r="Y527" s="3"/>
       <c r="Z527" s="3"/>
     </row>
-    <row r="528" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
         <v>1140</v>
       </c>
@@ -26113,7 +26113,7 @@
       <c r="Y528" s="3"/>
       <c r="Z528" s="3"/>
     </row>
-    <row r="529" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
         <v>1142</v>
       </c>
@@ -26155,7 +26155,7 @@
       <c r="Y529" s="3"/>
       <c r="Z529" s="3"/>
     </row>
-    <row r="530" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
         <v>1144</v>
       </c>
@@ -26197,7 +26197,7 @@
       <c r="Y530" s="3"/>
       <c r="Z530" s="3"/>
     </row>
-    <row r="531" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
         <v>1146</v>
       </c>
@@ -26239,7 +26239,7 @@
       <c r="Y531" s="3"/>
       <c r="Z531" s="3"/>
     </row>
-    <row r="532" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
         <v>1148</v>
       </c>
@@ -26281,7 +26281,7 @@
       <c r="Y532" s="3"/>
       <c r="Z532" s="3"/>
     </row>
-    <row r="533" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
         <v>1150</v>
       </c>
@@ -26323,7 +26323,7 @@
       <c r="Y533" s="3"/>
       <c r="Z533" s="3"/>
     </row>
-    <row r="534" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
         <v>1152</v>
       </c>
@@ -26365,7 +26365,7 @@
       <c r="Y534" s="3"/>
       <c r="Z534" s="3"/>
     </row>
-    <row r="535" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="3" t="s">
         <v>1154</v>
       </c>
@@ -26407,7 +26407,7 @@
       <c r="Y535" s="3"/>
       <c r="Z535" s="3"/>
     </row>
-    <row r="536" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
         <v>1156</v>
       </c>
@@ -26449,7 +26449,7 @@
       <c r="Y536" s="3"/>
       <c r="Z536" s="3"/>
     </row>
-    <row r="537" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
         <v>1158</v>
       </c>
@@ -26485,7 +26485,7 @@
       <c r="Y537" s="3"/>
       <c r="Z537" s="3"/>
     </row>
-    <row r="538" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
         <v>1160</v>
       </c>
@@ -26521,7 +26521,7 @@
       <c r="Y538" s="3"/>
       <c r="Z538" s="3"/>
     </row>
-    <row r="539" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="3" t="s">
         <v>1162</v>
       </c>
@@ -26565,7 +26565,7 @@
       <c r="Y539" s="3"/>
       <c r="Z539" s="3"/>
     </row>
-    <row r="540" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
         <v>1168</v>
       </c>
@@ -26609,7 +26609,7 @@
       <c r="Y540" s="3"/>
       <c r="Z540" s="3"/>
     </row>
-    <row r="541" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3" t="s">
         <v>1170</v>
       </c>
@@ -26653,7 +26653,7 @@
       <c r="Y541" s="3"/>
       <c r="Z541" s="3"/>
     </row>
-    <row r="542" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
         <v>1172</v>
       </c>
@@ -26697,7 +26697,7 @@
       <c r="Y542" s="3"/>
       <c r="Z542" s="3"/>
     </row>
-    <row r="543" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="3" t="s">
         <v>1174</v>
       </c>
@@ -26741,7 +26741,7 @@
       <c r="Y543" s="3"/>
       <c r="Z543" s="3"/>
     </row>
-    <row r="544" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="3" t="s">
         <v>1176</v>
       </c>
@@ -26785,7 +26785,7 @@
       <c r="Y544" s="3"/>
       <c r="Z544" s="3"/>
     </row>
-    <row r="545" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
         <v>1178</v>
       </c>
@@ -26829,7 +26829,7 @@
       <c r="Y545" s="3"/>
       <c r="Z545" s="3"/>
     </row>
-    <row r="546" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
         <v>1180</v>
       </c>
@@ -26873,7 +26873,7 @@
       <c r="Y546" s="3"/>
       <c r="Z546" s="3"/>
     </row>
-    <row r="547" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="3" t="s">
         <v>1182</v>
       </c>
@@ -26917,7 +26917,7 @@
       <c r="Y547" s="3"/>
       <c r="Z547" s="3"/>
     </row>
-    <row r="548" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
         <v>1184</v>
       </c>
@@ -26961,7 +26961,7 @@
       <c r="Y548" s="3"/>
       <c r="Z548" s="3"/>
     </row>
-    <row r="549" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="3" t="s">
         <v>1186</v>
       </c>
@@ -27005,7 +27005,7 @@
       <c r="Y549" s="3"/>
       <c r="Z549" s="3"/>
     </row>
-    <row r="550" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
         <v>1188</v>
       </c>
@@ -27049,7 +27049,7 @@
       <c r="Y550" s="3"/>
       <c r="Z550" s="3"/>
     </row>
-    <row r="551" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="3" t="s">
         <v>1190</v>
       </c>
@@ -27093,7 +27093,7 @@
       <c r="Y551" s="3"/>
       <c r="Z551" s="3"/>
     </row>
-    <row r="552" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
         <v>1192</v>
       </c>
@@ -27137,7 +27137,7 @@
       <c r="Y552" s="3"/>
       <c r="Z552" s="3"/>
     </row>
-    <row r="553" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="3" t="s">
         <v>1194</v>
       </c>
@@ -27181,7 +27181,7 @@
       <c r="Y553" s="3"/>
       <c r="Z553" s="3"/>
     </row>
-    <row r="554" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
         <v>1197</v>
       </c>
@@ -27225,7 +27225,7 @@
       <c r="Y554" s="3"/>
       <c r="Z554" s="3"/>
     </row>
-    <row r="555" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="3" t="s">
         <v>1199</v>
       </c>
@@ -27269,7 +27269,7 @@
       <c r="Y555" s="3"/>
       <c r="Z555" s="3"/>
     </row>
-    <row r="556" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="3" t="s">
         <v>1201</v>
       </c>
@@ -27313,7 +27313,7 @@
       <c r="Y556" s="3"/>
       <c r="Z556" s="3"/>
     </row>
-    <row r="557" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="3" t="s">
         <v>1203</v>
       </c>
@@ -27357,7 +27357,7 @@
       <c r="Y557" s="3"/>
       <c r="Z557" s="3"/>
     </row>
-    <row r="558" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
         <v>1205</v>
       </c>
@@ -27401,7 +27401,7 @@
       <c r="Y558" s="3"/>
       <c r="Z558" s="3"/>
     </row>
-    <row r="559" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="3" t="s">
         <v>1207</v>
       </c>
@@ -27445,7 +27445,7 @@
       <c r="Y559" s="3"/>
       <c r="Z559" s="3"/>
     </row>
-    <row r="560" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
         <v>1209</v>
       </c>
@@ -27489,7 +27489,7 @@
       <c r="Y560" s="3"/>
       <c r="Z560" s="3"/>
     </row>
-    <row r="561" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="3" t="s">
         <v>1211</v>
       </c>
@@ -27533,7 +27533,7 @@
       <c r="Y561" s="3"/>
       <c r="Z561" s="3"/>
     </row>
-    <row r="562" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="3" t="s">
         <v>1213</v>
       </c>
@@ -27577,7 +27577,7 @@
       <c r="Y562" s="3"/>
       <c r="Z562" s="3"/>
     </row>
-    <row r="563" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="3" t="s">
         <v>1215</v>
       </c>
@@ -27621,7 +27621,7 @@
       <c r="Y563" s="3"/>
       <c r="Z563" s="3"/>
     </row>
-    <row r="564" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="3" t="s">
         <v>1217</v>
       </c>
@@ -27665,7 +27665,7 @@
       <c r="Y564" s="3"/>
       <c r="Z564" s="3"/>
     </row>
-    <row r="565" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="3" t="s">
         <v>1219</v>
       </c>
@@ -27709,7 +27709,7 @@
       <c r="Y565" s="3"/>
       <c r="Z565" s="3"/>
     </row>
-    <row r="566" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="3" t="s">
         <v>1221</v>
       </c>
@@ -27753,7 +27753,7 @@
       <c r="Y566" s="3"/>
       <c r="Z566" s="3"/>
     </row>
-    <row r="567" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="3" t="s">
         <v>1223</v>
       </c>
@@ -27797,7 +27797,7 @@
       <c r="Y567" s="3"/>
       <c r="Z567" s="3"/>
     </row>
-    <row r="568" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="3" t="s">
         <v>1225</v>
       </c>
@@ -27841,7 +27841,7 @@
       <c r="Y568" s="3"/>
       <c r="Z568" s="3"/>
     </row>
-    <row r="569" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
         <v>1227</v>
       </c>
@@ -27885,7 +27885,7 @@
       <c r="Y569" s="3"/>
       <c r="Z569" s="3"/>
     </row>
-    <row r="570" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
         <v>1229</v>
       </c>
@@ -27929,7 +27929,7 @@
       <c r="Y570" s="3"/>
       <c r="Z570" s="3"/>
     </row>
-    <row r="571" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="3" t="s">
         <v>1231</v>
       </c>
@@ -27973,7 +27973,7 @@
       <c r="Y571" s="3"/>
       <c r="Z571" s="3"/>
     </row>
-    <row r="572" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
         <v>1236</v>
       </c>
@@ -28017,7 +28017,7 @@
       <c r="Y572" s="3"/>
       <c r="Z572" s="3"/>
     </row>
-    <row r="573" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
         <v>1238</v>
       </c>
@@ -28061,7 +28061,7 @@
       <c r="Y573" s="3"/>
       <c r="Z573" s="3"/>
     </row>
-    <row r="574" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="3" t="s">
         <v>1240</v>
       </c>
@@ -28105,7 +28105,7 @@
       <c r="Y574" s="3"/>
       <c r="Z574" s="3"/>
     </row>
-    <row r="575" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
         <v>1242</v>
       </c>
@@ -28149,7 +28149,7 @@
       <c r="Y575" s="3"/>
       <c r="Z575" s="3"/>
     </row>
-    <row r="576" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
         <v>1245</v>
       </c>
@@ -28193,7 +28193,7 @@
       <c r="Y576" s="3"/>
       <c r="Z576" s="3"/>
     </row>
-    <row r="577" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="3" t="s">
         <v>1247</v>
       </c>
@@ -28237,7 +28237,7 @@
       <c r="Y577" s="3"/>
       <c r="Z577" s="3"/>
     </row>
-    <row r="578" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
         <v>1249</v>
       </c>
@@ -28281,7 +28281,7 @@
       <c r="Y578" s="3"/>
       <c r="Z578" s="3"/>
     </row>
-    <row r="579" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="3" t="s">
         <v>1251</v>
       </c>
@@ -28325,7 +28325,7 @@
       <c r="Y579" s="3"/>
       <c r="Z579" s="3"/>
     </row>
-    <row r="580" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="3" t="s">
         <v>1253</v>
       </c>
@@ -28369,7 +28369,7 @@
       <c r="Y580" s="3"/>
       <c r="Z580" s="3"/>
     </row>
-    <row r="581" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
         <v>1255</v>
       </c>
@@ -28413,7 +28413,7 @@
       <c r="Y581" s="3"/>
       <c r="Z581" s="3"/>
     </row>
-    <row r="582" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
         <v>1257</v>
       </c>
@@ -28457,7 +28457,7 @@
       <c r="Y582" s="3"/>
       <c r="Z582" s="3"/>
     </row>
-    <row r="583" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="3" t="s">
         <v>1259</v>
       </c>
@@ -28501,7 +28501,7 @@
       <c r="Y583" s="3"/>
       <c r="Z583" s="3"/>
     </row>
-    <row r="584" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
         <v>1262</v>
       </c>
@@ -28545,7 +28545,7 @@
       <c r="Y584" s="3"/>
       <c r="Z584" s="3"/>
     </row>
-    <row r="585" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
         <v>1264</v>
       </c>
@@ -28589,7 +28589,7 @@
       <c r="Y585" s="3"/>
       <c r="Z585" s="3"/>
     </row>
-    <row r="586" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
         <v>1266</v>
       </c>
@@ -28633,7 +28633,7 @@
       <c r="Y586" s="3"/>
       <c r="Z586" s="3"/>
     </row>
-    <row r="587" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="3" t="s">
         <v>1268</v>
       </c>
@@ -28677,7 +28677,7 @@
       <c r="Y587" s="3"/>
       <c r="Z587" s="3"/>
     </row>
-    <row r="588" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -28705,7 +28705,7 @@
       <c r="Y588" s="3"/>
       <c r="Z588" s="3"/>
     </row>
-    <row r="589" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -28733,7 +28733,7 @@
       <c r="Y589" s="3"/>
       <c r="Z589" s="3"/>
     </row>
-    <row r="590" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -28761,7 +28761,7 @@
       <c r="Y590" s="3"/>
       <c r="Z590" s="3"/>
     </row>
-    <row r="591" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -28789,7 +28789,7 @@
       <c r="Y591" s="3"/>
       <c r="Z591" s="3"/>
     </row>
-    <row r="592" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -28817,7 +28817,7 @@
       <c r="Y592" s="3"/>
       <c r="Z592" s="3"/>
     </row>
-    <row r="593" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -28845,7 +28845,7 @@
       <c r="Y593" s="3"/>
       <c r="Z593" s="3"/>
     </row>
-    <row r="594" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -28873,7 +28873,7 @@
       <c r="Y594" s="3"/>
       <c r="Z594" s="3"/>
     </row>
-    <row r="595" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -28901,7 +28901,7 @@
       <c r="Y595" s="3"/>
       <c r="Z595" s="3"/>
     </row>
-    <row r="596" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -28929,7 +28929,7 @@
       <c r="Y596" s="3"/>
       <c r="Z596" s="3"/>
     </row>
-    <row r="597" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -28957,7 +28957,7 @@
       <c r="Y597" s="3"/>
       <c r="Z597" s="3"/>
     </row>
-    <row r="598" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -28985,7 +28985,7 @@
       <c r="Y598" s="3"/>
       <c r="Z598" s="3"/>
     </row>
-    <row r="599" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -29013,7 +29013,7 @@
       <c r="Y599" s="3"/>
       <c r="Z599" s="3"/>
     </row>
-    <row r="600" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -29041,7 +29041,7 @@
       <c r="Y600" s="3"/>
       <c r="Z600" s="3"/>
     </row>
-    <row r="601" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -29069,7 +29069,7 @@
       <c r="Y601" s="3"/>
       <c r="Z601" s="3"/>
     </row>
-    <row r="602" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -29097,7 +29097,7 @@
       <c r="Y602" s="3"/>
       <c r="Z602" s="3"/>
     </row>
-    <row r="603" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -29125,7 +29125,7 @@
       <c r="Y603" s="3"/>
       <c r="Z603" s="3"/>
     </row>
-    <row r="604" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -29153,7 +29153,7 @@
       <c r="Y604" s="3"/>
       <c r="Z604" s="3"/>
     </row>
-    <row r="605" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -29181,7 +29181,7 @@
       <c r="Y605" s="3"/>
       <c r="Z605" s="3"/>
     </row>
-    <row r="606" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -29209,7 +29209,7 @@
       <c r="Y606" s="3"/>
       <c r="Z606" s="3"/>
     </row>
-    <row r="607" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -29237,7 +29237,7 @@
       <c r="Y607" s="3"/>
       <c r="Z607" s="3"/>
     </row>
-    <row r="608" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -29265,7 +29265,7 @@
       <c r="Y608" s="3"/>
       <c r="Z608" s="3"/>
     </row>
-    <row r="609" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -29293,7 +29293,7 @@
       <c r="Y609" s="3"/>
       <c r="Z609" s="3"/>
     </row>
-    <row r="610" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -29321,7 +29321,7 @@
       <c r="Y610" s="3"/>
       <c r="Z610" s="3"/>
     </row>
-    <row r="611" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -29349,7 +29349,7 @@
       <c r="Y611" s="3"/>
       <c r="Z611" s="3"/>
     </row>
-    <row r="612" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -29377,7 +29377,7 @@
       <c r="Y612" s="3"/>
       <c r="Z612" s="3"/>
     </row>
-    <row r="613" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -29405,7 +29405,7 @@
       <c r="Y613" s="3"/>
       <c r="Z613" s="3"/>
     </row>
-    <row r="614" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -29433,7 +29433,7 @@
       <c r="Y614" s="3"/>
       <c r="Z614" s="3"/>
     </row>
-    <row r="615" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -29461,7 +29461,7 @@
       <c r="Y615" s="3"/>
       <c r="Z615" s="3"/>
     </row>
-    <row r="616" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -29489,7 +29489,7 @@
       <c r="Y616" s="3"/>
       <c r="Z616" s="3"/>
     </row>
-    <row r="617" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -29517,7 +29517,7 @@
       <c r="Y617" s="3"/>
       <c r="Z617" s="3"/>
     </row>
-    <row r="618" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -29545,7 +29545,7 @@
       <c r="Y618" s="3"/>
       <c r="Z618" s="3"/>
     </row>
-    <row r="619" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -29573,7 +29573,7 @@
       <c r="Y619" s="3"/>
       <c r="Z619" s="3"/>
     </row>
-    <row r="620" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -29601,7 +29601,7 @@
       <c r="Y620" s="3"/>
       <c r="Z620" s="3"/>
     </row>
-    <row r="621" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -29629,7 +29629,7 @@
       <c r="Y621" s="3"/>
       <c r="Z621" s="3"/>
     </row>
-    <row r="622" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -29657,7 +29657,7 @@
       <c r="Y622" s="3"/>
       <c r="Z622" s="3"/>
     </row>
-    <row r="623" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -29685,7 +29685,7 @@
       <c r="Y623" s="3"/>
       <c r="Z623" s="3"/>
     </row>
-    <row r="624" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -29713,7 +29713,7 @@
       <c r="Y624" s="3"/>
       <c r="Z624" s="3"/>
     </row>
-    <row r="625" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -29741,7 +29741,7 @@
       <c r="Y625" s="3"/>
       <c r="Z625" s="3"/>
     </row>
-    <row r="626" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -29769,7 +29769,7 @@
       <c r="Y626" s="3"/>
       <c r="Z626" s="3"/>
     </row>
-    <row r="627" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -29797,7 +29797,7 @@
       <c r="Y627" s="3"/>
       <c r="Z627" s="3"/>
     </row>
-    <row r="628" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -29825,7 +29825,7 @@
       <c r="Y628" s="3"/>
       <c r="Z628" s="3"/>
     </row>
-    <row r="629" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -29853,7 +29853,7 @@
       <c r="Y629" s="3"/>
       <c r="Z629" s="3"/>
     </row>
-    <row r="630" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -29881,7 +29881,7 @@
       <c r="Y630" s="3"/>
       <c r="Z630" s="3"/>
     </row>
-    <row r="631" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -29909,7 +29909,7 @@
       <c r="Y631" s="3"/>
       <c r="Z631" s="3"/>
     </row>
-    <row r="632" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -29937,7 +29937,7 @@
       <c r="Y632" s="3"/>
       <c r="Z632" s="3"/>
     </row>
-    <row r="633" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -29965,7 +29965,7 @@
       <c r="Y633" s="3"/>
       <c r="Z633" s="3"/>
     </row>
-    <row r="634" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -29993,7 +29993,7 @@
       <c r="Y634" s="3"/>
       <c r="Z634" s="3"/>
     </row>
-    <row r="635" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -30021,7 +30021,7 @@
       <c r="Y635" s="3"/>
       <c r="Z635" s="3"/>
     </row>
-    <row r="636" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -30049,7 +30049,7 @@
       <c r="Y636" s="3"/>
       <c r="Z636" s="3"/>
     </row>
-    <row r="637" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -30077,7 +30077,7 @@
       <c r="Y637" s="3"/>
       <c r="Z637" s="3"/>
     </row>
-    <row r="638" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -30105,7 +30105,7 @@
       <c r="Y638" s="3"/>
       <c r="Z638" s="3"/>
     </row>
-    <row r="639" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -30133,7 +30133,7 @@
       <c r="Y639" s="3"/>
       <c r="Z639" s="3"/>
     </row>
-    <row r="640" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -30161,7 +30161,7 @@
       <c r="Y640" s="3"/>
       <c r="Z640" s="3"/>
     </row>
-    <row r="641" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -30189,7 +30189,7 @@
       <c r="Y641" s="3"/>
       <c r="Z641" s="3"/>
     </row>
-    <row r="642" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -30217,7 +30217,7 @@
       <c r="Y642" s="3"/>
       <c r="Z642" s="3"/>
     </row>
-    <row r="643" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -30245,7 +30245,7 @@
       <c r="Y643" s="3"/>
       <c r="Z643" s="3"/>
     </row>
-    <row r="644" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -30273,7 +30273,7 @@
       <c r="Y644" s="3"/>
       <c r="Z644" s="3"/>
     </row>
-    <row r="645" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -30301,7 +30301,7 @@
       <c r="Y645" s="3"/>
       <c r="Z645" s="3"/>
     </row>
-    <row r="646" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -30329,7 +30329,7 @@
       <c r="Y646" s="3"/>
       <c r="Z646" s="3"/>
     </row>
-    <row r="647" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -30357,7 +30357,7 @@
       <c r="Y647" s="3"/>
       <c r="Z647" s="3"/>
     </row>
-    <row r="648" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -30385,7 +30385,7 @@
       <c r="Y648" s="3"/>
       <c r="Z648" s="3"/>
     </row>
-    <row r="649" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -30413,7 +30413,7 @@
       <c r="Y649" s="3"/>
       <c r="Z649" s="3"/>
     </row>
-    <row r="650" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -30441,7 +30441,7 @@
       <c r="Y650" s="3"/>
       <c r="Z650" s="3"/>
     </row>
-    <row r="651" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -30469,7 +30469,7 @@
       <c r="Y651" s="3"/>
       <c r="Z651" s="3"/>
     </row>
-    <row r="652" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -30497,7 +30497,7 @@
       <c r="Y652" s="3"/>
       <c r="Z652" s="3"/>
     </row>
-    <row r="653" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -30525,7 +30525,7 @@
       <c r="Y653" s="3"/>
       <c r="Z653" s="3"/>
     </row>
-    <row r="654" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -30553,7 +30553,7 @@
       <c r="Y654" s="3"/>
       <c r="Z654" s="3"/>
     </row>
-    <row r="655" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -30581,7 +30581,7 @@
       <c r="Y655" s="3"/>
       <c r="Z655" s="3"/>
     </row>
-    <row r="656" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -30609,7 +30609,7 @@
       <c r="Y656" s="3"/>
       <c r="Z656" s="3"/>
     </row>
-    <row r="657" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -30637,7 +30637,7 @@
       <c r="Y657" s="3"/>
       <c r="Z657" s="3"/>
     </row>
-    <row r="658" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -30665,7 +30665,7 @@
       <c r="Y658" s="3"/>
       <c r="Z658" s="3"/>
     </row>
-    <row r="659" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -30693,7 +30693,7 @@
       <c r="Y659" s="3"/>
       <c r="Z659" s="3"/>
     </row>
-    <row r="660" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -30721,7 +30721,7 @@
       <c r="Y660" s="3"/>
       <c r="Z660" s="3"/>
     </row>
-    <row r="661" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -30749,7 +30749,7 @@
       <c r="Y661" s="3"/>
       <c r="Z661" s="3"/>
     </row>
-    <row r="662" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -30777,7 +30777,7 @@
       <c r="Y662" s="3"/>
       <c r="Z662" s="3"/>
     </row>
-    <row r="663" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -30805,7 +30805,7 @@
       <c r="Y663" s="3"/>
       <c r="Z663" s="3"/>
     </row>
-    <row r="664" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -30833,7 +30833,7 @@
       <c r="Y664" s="3"/>
       <c r="Z664" s="3"/>
     </row>
-    <row r="665" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -30861,7 +30861,7 @@
       <c r="Y665" s="3"/>
       <c r="Z665" s="3"/>
     </row>
-    <row r="666" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -30889,7 +30889,7 @@
       <c r="Y666" s="3"/>
       <c r="Z666" s="3"/>
     </row>
-    <row r="667" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -30917,7 +30917,7 @@
       <c r="Y667" s="3"/>
       <c r="Z667" s="3"/>
     </row>
-    <row r="668" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -30945,7 +30945,7 @@
       <c r="Y668" s="3"/>
       <c r="Z668" s="3"/>
     </row>
-    <row r="669" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -30973,7 +30973,7 @@
       <c r="Y669" s="3"/>
       <c r="Z669" s="3"/>
     </row>
-    <row r="670" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -31001,7 +31001,7 @@
       <c r="Y670" s="3"/>
       <c r="Z670" s="3"/>
     </row>
-    <row r="671" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -31029,7 +31029,7 @@
       <c r="Y671" s="3"/>
       <c r="Z671" s="3"/>
     </row>
-    <row r="672" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -31057,7 +31057,7 @@
       <c r="Y672" s="3"/>
       <c r="Z672" s="3"/>
     </row>
-    <row r="673" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -31085,7 +31085,7 @@
       <c r="Y673" s="3"/>
       <c r="Z673" s="3"/>
     </row>
-    <row r="674" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -31113,7 +31113,7 @@
       <c r="Y674" s="3"/>
       <c r="Z674" s="3"/>
     </row>
-    <row r="675" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -31141,7 +31141,7 @@
       <c r="Y675" s="3"/>
       <c r="Z675" s="3"/>
     </row>
-    <row r="676" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -31169,7 +31169,7 @@
       <c r="Y676" s="3"/>
       <c r="Z676" s="3"/>
     </row>
-    <row r="677" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -31197,7 +31197,7 @@
       <c r="Y677" s="3"/>
       <c r="Z677" s="3"/>
     </row>
-    <row r="678" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -31225,7 +31225,7 @@
       <c r="Y678" s="3"/>
       <c r="Z678" s="3"/>
     </row>
-    <row r="679" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -31253,7 +31253,7 @@
       <c r="Y679" s="3"/>
       <c r="Z679" s="3"/>
     </row>
-    <row r="680" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -31281,7 +31281,7 @@
       <c r="Y680" s="3"/>
       <c r="Z680" s="3"/>
     </row>
-    <row r="681" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -31309,7 +31309,7 @@
       <c r="Y681" s="3"/>
       <c r="Z681" s="3"/>
     </row>
-    <row r="682" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -31337,7 +31337,7 @@
       <c r="Y682" s="3"/>
       <c r="Z682" s="3"/>
     </row>
-    <row r="683" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -31365,7 +31365,7 @@
       <c r="Y683" s="3"/>
       <c r="Z683" s="3"/>
     </row>
-    <row r="684" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -31393,7 +31393,7 @@
       <c r="Y684" s="3"/>
       <c r="Z684" s="3"/>
     </row>
-    <row r="685" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -31421,7 +31421,7 @@
       <c r="Y685" s="3"/>
       <c r="Z685" s="3"/>
     </row>
-    <row r="686" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -31449,7 +31449,7 @@
       <c r="Y686" s="3"/>
       <c r="Z686" s="3"/>
     </row>
-    <row r="687" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -31477,7 +31477,7 @@
       <c r="Y687" s="3"/>
       <c r="Z687" s="3"/>
     </row>
-    <row r="688" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -31505,7 +31505,7 @@
       <c r="Y688" s="3"/>
       <c r="Z688" s="3"/>
     </row>
-    <row r="689" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -31533,7 +31533,7 @@
       <c r="Y689" s="3"/>
       <c r="Z689" s="3"/>
     </row>
-    <row r="690" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -31561,7 +31561,7 @@
       <c r="Y690" s="3"/>
       <c r="Z690" s="3"/>
     </row>
-    <row r="691" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -31589,7 +31589,7 @@
       <c r="Y691" s="3"/>
       <c r="Z691" s="3"/>
     </row>
-    <row r="692" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -31617,7 +31617,7 @@
       <c r="Y692" s="3"/>
       <c r="Z692" s="3"/>
     </row>
-    <row r="693" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -31645,7 +31645,7 @@
       <c r="Y693" s="3"/>
       <c r="Z693" s="3"/>
     </row>
-    <row r="694" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -31673,7 +31673,7 @@
       <c r="Y694" s="3"/>
       <c r="Z694" s="3"/>
     </row>
-    <row r="695" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -31701,7 +31701,7 @@
       <c r="Y695" s="3"/>
       <c r="Z695" s="3"/>
     </row>
-    <row r="696" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -31729,7 +31729,7 @@
       <c r="Y696" s="3"/>
       <c r="Z696" s="3"/>
     </row>
-    <row r="697" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -31757,7 +31757,7 @@
       <c r="Y697" s="3"/>
       <c r="Z697" s="3"/>
     </row>
-    <row r="698" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -31785,7 +31785,7 @@
       <c r="Y698" s="3"/>
       <c r="Z698" s="3"/>
     </row>
-    <row r="699" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -31813,7 +31813,7 @@
       <c r="Y699" s="3"/>
       <c r="Z699" s="3"/>
     </row>
-    <row r="700" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -31841,7 +31841,7 @@
       <c r="Y700" s="3"/>
       <c r="Z700" s="3"/>
     </row>
-    <row r="701" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -31869,7 +31869,7 @@
       <c r="Y701" s="3"/>
       <c r="Z701" s="3"/>
     </row>
-    <row r="702" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -31897,7 +31897,7 @@
       <c r="Y702" s="3"/>
       <c r="Z702" s="3"/>
     </row>
-    <row r="703" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -31925,7 +31925,7 @@
       <c r="Y703" s="3"/>
       <c r="Z703" s="3"/>
     </row>
-    <row r="704" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -31953,7 +31953,7 @@
       <c r="Y704" s="3"/>
       <c r="Z704" s="3"/>
     </row>
-    <row r="705" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -31981,7 +31981,7 @@
       <c r="Y705" s="3"/>
       <c r="Z705" s="3"/>
     </row>
-    <row r="706" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -32009,7 +32009,7 @@
       <c r="Y706" s="3"/>
       <c r="Z706" s="3"/>
     </row>
-    <row r="707" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -32037,7 +32037,7 @@
       <c r="Y707" s="3"/>
       <c r="Z707" s="3"/>
     </row>
-    <row r="708" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -32065,7 +32065,7 @@
       <c r="Y708" s="3"/>
       <c r="Z708" s="3"/>
     </row>
-    <row r="709" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -32093,7 +32093,7 @@
       <c r="Y709" s="3"/>
       <c r="Z709" s="3"/>
     </row>
-    <row r="710" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -32121,7 +32121,7 @@
       <c r="Y710" s="3"/>
       <c r="Z710" s="3"/>
     </row>
-    <row r="711" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -32149,7 +32149,7 @@
       <c r="Y711" s="3"/>
       <c r="Z711" s="3"/>
     </row>
-    <row r="712" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -32177,7 +32177,7 @@
       <c r="Y712" s="3"/>
       <c r="Z712" s="3"/>
     </row>
-    <row r="713" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -32205,7 +32205,7 @@
       <c r="Y713" s="3"/>
       <c r="Z713" s="3"/>
     </row>
-    <row r="714" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -32233,7 +32233,7 @@
       <c r="Y714" s="3"/>
       <c r="Z714" s="3"/>
     </row>
-    <row r="715" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -32261,7 +32261,7 @@
       <c r="Y715" s="3"/>
       <c r="Z715" s="3"/>
     </row>
-    <row r="716" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -32289,7 +32289,7 @@
       <c r="Y716" s="3"/>
       <c r="Z716" s="3"/>
     </row>
-    <row r="717" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -32317,7 +32317,7 @@
       <c r="Y717" s="3"/>
       <c r="Z717" s="3"/>
     </row>
-    <row r="718" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -32345,7 +32345,7 @@
       <c r="Y718" s="3"/>
       <c r="Z718" s="3"/>
     </row>
-    <row r="719" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -32373,7 +32373,7 @@
       <c r="Y719" s="3"/>
       <c r="Z719" s="3"/>
     </row>
-    <row r="720" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -32401,7 +32401,7 @@
       <c r="Y720" s="3"/>
       <c r="Z720" s="3"/>
     </row>
-    <row r="721" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -32429,7 +32429,7 @@
       <c r="Y721" s="3"/>
       <c r="Z721" s="3"/>
     </row>
-    <row r="722" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -32457,7 +32457,7 @@
       <c r="Y722" s="3"/>
       <c r="Z722" s="3"/>
     </row>
-    <row r="723" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -32485,7 +32485,7 @@
       <c r="Y723" s="3"/>
       <c r="Z723" s="3"/>
     </row>
-    <row r="724" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -32513,7 +32513,7 @@
       <c r="Y724" s="3"/>
       <c r="Z724" s="3"/>
     </row>
-    <row r="725" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -32541,7 +32541,7 @@
       <c r="Y725" s="3"/>
       <c r="Z725" s="3"/>
     </row>
-    <row r="726" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -32569,7 +32569,7 @@
       <c r="Y726" s="3"/>
       <c r="Z726" s="3"/>
     </row>
-    <row r="727" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -32597,7 +32597,7 @@
       <c r="Y727" s="3"/>
       <c r="Z727" s="3"/>
     </row>
-    <row r="728" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -32625,7 +32625,7 @@
       <c r="Y728" s="3"/>
       <c r="Z728" s="3"/>
     </row>
-    <row r="729" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -32653,7 +32653,7 @@
       <c r="Y729" s="3"/>
       <c r="Z729" s="3"/>
     </row>
-    <row r="730" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -32681,7 +32681,7 @@
       <c r="Y730" s="3"/>
       <c r="Z730" s="3"/>
     </row>
-    <row r="731" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -32709,7 +32709,7 @@
       <c r="Y731" s="3"/>
       <c r="Z731" s="3"/>
     </row>
-    <row r="732" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -32737,7 +32737,7 @@
       <c r="Y732" s="3"/>
       <c r="Z732" s="3"/>
     </row>
-    <row r="733" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -32765,7 +32765,7 @@
       <c r="Y733" s="3"/>
       <c r="Z733" s="3"/>
     </row>
-    <row r="734" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -32793,7 +32793,7 @@
       <c r="Y734" s="3"/>
       <c r="Z734" s="3"/>
     </row>
-    <row r="735" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -32821,7 +32821,7 @@
       <c r="Y735" s="3"/>
       <c r="Z735" s="3"/>
     </row>
-    <row r="736" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -32849,7 +32849,7 @@
       <c r="Y736" s="3"/>
       <c r="Z736" s="3"/>
     </row>
-    <row r="737" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -32877,7 +32877,7 @@
       <c r="Y737" s="3"/>
       <c r="Z737" s="3"/>
     </row>
-    <row r="738" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -32905,7 +32905,7 @@
       <c r="Y738" s="3"/>
       <c r="Z738" s="3"/>
     </row>
-    <row r="739" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -32933,7 +32933,7 @@
       <c r="Y739" s="3"/>
       <c r="Z739" s="3"/>
     </row>
-    <row r="740" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -32961,7 +32961,7 @@
       <c r="Y740" s="3"/>
       <c r="Z740" s="3"/>
     </row>
-    <row r="741" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -32989,7 +32989,7 @@
       <c r="Y741" s="3"/>
       <c r="Z741" s="3"/>
     </row>
-    <row r="742" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -33017,7 +33017,7 @@
       <c r="Y742" s="3"/>
       <c r="Z742" s="3"/>
     </row>
-    <row r="743" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -33045,7 +33045,7 @@
       <c r="Y743" s="3"/>
       <c r="Z743" s="3"/>
     </row>
-    <row r="744" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -33073,7 +33073,7 @@
       <c r="Y744" s="3"/>
       <c r="Z744" s="3"/>
     </row>
-    <row r="745" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -33101,7 +33101,7 @@
       <c r="Y745" s="3"/>
       <c r="Z745" s="3"/>
     </row>
-    <row r="746" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -33129,7 +33129,7 @@
       <c r="Y746" s="3"/>
       <c r="Z746" s="3"/>
     </row>
-    <row r="747" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -33157,7 +33157,7 @@
       <c r="Y747" s="3"/>
       <c r="Z747" s="3"/>
     </row>
-    <row r="748" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -33185,7 +33185,7 @@
       <c r="Y748" s="3"/>
       <c r="Z748" s="3"/>
     </row>
-    <row r="749" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -33213,7 +33213,7 @@
       <c r="Y749" s="3"/>
       <c r="Z749" s="3"/>
     </row>
-    <row r="750" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -33241,7 +33241,7 @@
       <c r="Y750" s="3"/>
       <c r="Z750" s="3"/>
     </row>
-    <row r="751" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -33269,7 +33269,7 @@
       <c r="Y751" s="3"/>
       <c r="Z751" s="3"/>
     </row>
-    <row r="752" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -33297,7 +33297,7 @@
       <c r="Y752" s="3"/>
       <c r="Z752" s="3"/>
     </row>
-    <row r="753" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -33325,7 +33325,7 @@
       <c r="Y753" s="3"/>
       <c r="Z753" s="3"/>
     </row>
-    <row r="754" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -33353,7 +33353,7 @@
       <c r="Y754" s="3"/>
       <c r="Z754" s="3"/>
     </row>
-    <row r="755" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -33381,7 +33381,7 @@
       <c r="Y755" s="3"/>
       <c r="Z755" s="3"/>
     </row>
-    <row r="756" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -33409,7 +33409,7 @@
       <c r="Y756" s="3"/>
       <c r="Z756" s="3"/>
     </row>
-    <row r="757" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -33437,7 +33437,7 @@
       <c r="Y757" s="3"/>
       <c r="Z757" s="3"/>
     </row>
-    <row r="758" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -33465,7 +33465,7 @@
       <c r="Y758" s="3"/>
       <c r="Z758" s="3"/>
     </row>
-    <row r="759" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -33493,7 +33493,7 @@
       <c r="Y759" s="3"/>
       <c r="Z759" s="3"/>
     </row>
-    <row r="760" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -33521,7 +33521,7 @@
       <c r="Y760" s="3"/>
       <c r="Z760" s="3"/>
     </row>
-    <row r="761" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -33549,7 +33549,7 @@
       <c r="Y761" s="3"/>
       <c r="Z761" s="3"/>
     </row>
-    <row r="762" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -33577,7 +33577,7 @@
       <c r="Y762" s="3"/>
       <c r="Z762" s="3"/>
     </row>
-    <row r="763" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -33605,7 +33605,7 @@
       <c r="Y763" s="3"/>
       <c r="Z763" s="3"/>
     </row>
-    <row r="764" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -33633,7 +33633,7 @@
       <c r="Y764" s="3"/>
       <c r="Z764" s="3"/>
     </row>
-    <row r="765" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -33661,7 +33661,7 @@
       <c r="Y765" s="3"/>
       <c r="Z765" s="3"/>
     </row>
-    <row r="766" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -33689,7 +33689,7 @@
       <c r="Y766" s="3"/>
       <c r="Z766" s="3"/>
     </row>
-    <row r="767" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -33717,7 +33717,7 @@
       <c r="Y767" s="3"/>
       <c r="Z767" s="3"/>
     </row>
-    <row r="768" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -33745,7 +33745,7 @@
       <c r="Y768" s="3"/>
       <c r="Z768" s="3"/>
     </row>
-    <row r="769" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -33773,7 +33773,7 @@
       <c r="Y769" s="3"/>
       <c r="Z769" s="3"/>
     </row>
-    <row r="770" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -33801,7 +33801,7 @@
       <c r="Y770" s="3"/>
       <c r="Z770" s="3"/>
     </row>
-    <row r="771" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -33829,7 +33829,7 @@
       <c r="Y771" s="3"/>
       <c r="Z771" s="3"/>
     </row>
-    <row r="772" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -33857,7 +33857,7 @@
       <c r="Y772" s="3"/>
       <c r="Z772" s="3"/>
     </row>
-    <row r="773" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -33885,7 +33885,7 @@
       <c r="Y773" s="3"/>
       <c r="Z773" s="3"/>
     </row>
-    <row r="774" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -33913,7 +33913,7 @@
       <c r="Y774" s="3"/>
       <c r="Z774" s="3"/>
     </row>
-    <row r="775" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -33941,7 +33941,7 @@
       <c r="Y775" s="3"/>
       <c r="Z775" s="3"/>
     </row>
-    <row r="776" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -33969,7 +33969,7 @@
       <c r="Y776" s="3"/>
       <c r="Z776" s="3"/>
     </row>
-    <row r="777" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -33997,7 +33997,7 @@
       <c r="Y777" s="3"/>
       <c r="Z777" s="3"/>
     </row>
-    <row r="778" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -34025,7 +34025,7 @@
       <c r="Y778" s="3"/>
       <c r="Z778" s="3"/>
     </row>
-    <row r="779" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -34053,7 +34053,7 @@
       <c r="Y779" s="3"/>
       <c r="Z779" s="3"/>
     </row>
-    <row r="780" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -34081,7 +34081,7 @@
       <c r="Y780" s="3"/>
       <c r="Z780" s="3"/>
     </row>
-    <row r="781" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -34109,7 +34109,7 @@
       <c r="Y781" s="3"/>
       <c r="Z781" s="3"/>
     </row>
-    <row r="782" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -34137,7 +34137,7 @@
       <c r="Y782" s="3"/>
       <c r="Z782" s="3"/>
     </row>
-    <row r="783" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -34165,7 +34165,7 @@
       <c r="Y783" s="3"/>
       <c r="Z783" s="3"/>
     </row>
-    <row r="784" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -34193,7 +34193,7 @@
       <c r="Y784" s="3"/>
       <c r="Z784" s="3"/>
     </row>
-    <row r="785" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -34221,7 +34221,7 @@
       <c r="Y785" s="3"/>
       <c r="Z785" s="3"/>
     </row>
-    <row r="786" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -34249,7 +34249,7 @@
       <c r="Y786" s="3"/>
       <c r="Z786" s="3"/>
     </row>
-    <row r="787" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -34277,7 +34277,7 @@
       <c r="Y787" s="3"/>
       <c r="Z787" s="3"/>
     </row>
-    <row r="788" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -34305,7 +34305,7 @@
       <c r="Y788" s="3"/>
       <c r="Z788" s="3"/>
     </row>
-    <row r="789" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -34333,7 +34333,7 @@
       <c r="Y789" s="3"/>
       <c r="Z789" s="3"/>
     </row>
-    <row r="790" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -34361,7 +34361,7 @@
       <c r="Y790" s="3"/>
       <c r="Z790" s="3"/>
     </row>
-    <row r="791" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -34389,7 +34389,7 @@
       <c r="Y791" s="3"/>
       <c r="Z791" s="3"/>
     </row>
-    <row r="792" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -34417,7 +34417,7 @@
       <c r="Y792" s="3"/>
       <c r="Z792" s="3"/>
     </row>
-    <row r="793" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -34445,7 +34445,7 @@
       <c r="Y793" s="3"/>
       <c r="Z793" s="3"/>
     </row>
-    <row r="794" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -34473,7 +34473,7 @@
       <c r="Y794" s="3"/>
       <c r="Z794" s="3"/>
     </row>
-    <row r="795" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -34501,7 +34501,7 @@
       <c r="Y795" s="3"/>
       <c r="Z795" s="3"/>
     </row>
-    <row r="796" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -34529,7 +34529,7 @@
       <c r="Y796" s="3"/>
       <c r="Z796" s="3"/>
     </row>
-    <row r="797" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -34557,7 +34557,7 @@
       <c r="Y797" s="3"/>
       <c r="Z797" s="3"/>
     </row>
-    <row r="798" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -34585,7 +34585,7 @@
       <c r="Y798" s="3"/>
       <c r="Z798" s="3"/>
     </row>
-    <row r="799" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -34613,7 +34613,7 @@
       <c r="Y799" s="3"/>
       <c r="Z799" s="3"/>
     </row>
-    <row r="800" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -34641,7 +34641,7 @@
       <c r="Y800" s="3"/>
       <c r="Z800" s="3"/>
     </row>
-    <row r="801" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -34669,7 +34669,7 @@
       <c r="Y801" s="3"/>
       <c r="Z801" s="3"/>
     </row>
-    <row r="802" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -34697,7 +34697,7 @@
       <c r="Y802" s="3"/>
       <c r="Z802" s="3"/>
     </row>
-    <row r="803" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -34725,7 +34725,7 @@
       <c r="Y803" s="3"/>
       <c r="Z803" s="3"/>
     </row>
-    <row r="804" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -34753,7 +34753,7 @@
       <c r="Y804" s="3"/>
       <c r="Z804" s="3"/>
     </row>
-    <row r="805" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -34781,7 +34781,7 @@
       <c r="Y805" s="3"/>
       <c r="Z805" s="3"/>
     </row>
-    <row r="806" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -34809,7 +34809,7 @@
       <c r="Y806" s="3"/>
       <c r="Z806" s="3"/>
     </row>
-    <row r="807" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -34837,7 +34837,7 @@
       <c r="Y807" s="3"/>
       <c r="Z807" s="3"/>
     </row>
-    <row r="808" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -34865,7 +34865,7 @@
       <c r="Y808" s="3"/>
       <c r="Z808" s="3"/>
     </row>
-    <row r="809" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -34893,7 +34893,7 @@
       <c r="Y809" s="3"/>
       <c r="Z809" s="3"/>
     </row>
-    <row r="810" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -34921,7 +34921,7 @@
       <c r="Y810" s="3"/>
       <c r="Z810" s="3"/>
     </row>
-    <row r="811" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -34949,7 +34949,7 @@
       <c r="Y811" s="3"/>
       <c r="Z811" s="3"/>
     </row>
-    <row r="812" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -34977,7 +34977,7 @@
       <c r="Y812" s="3"/>
       <c r="Z812" s="3"/>
     </row>
-    <row r="813" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -35005,7 +35005,7 @@
       <c r="Y813" s="3"/>
       <c r="Z813" s="3"/>
     </row>
-    <row r="814" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -35033,7 +35033,7 @@
       <c r="Y814" s="3"/>
       <c r="Z814" s="3"/>
     </row>
-    <row r="815" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -35061,7 +35061,7 @@
       <c r="Y815" s="3"/>
       <c r="Z815" s="3"/>
     </row>
-    <row r="816" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -35089,7 +35089,7 @@
       <c r="Y816" s="3"/>
       <c r="Z816" s="3"/>
     </row>
-    <row r="817" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -35117,7 +35117,7 @@
       <c r="Y817" s="3"/>
       <c r="Z817" s="3"/>
     </row>
-    <row r="818" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -35145,7 +35145,7 @@
       <c r="Y818" s="3"/>
       <c r="Z818" s="3"/>
     </row>
-    <row r="819" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -35173,7 +35173,7 @@
       <c r="Y819" s="3"/>
       <c r="Z819" s="3"/>
     </row>
-    <row r="820" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -35201,7 +35201,7 @@
       <c r="Y820" s="3"/>
       <c r="Z820" s="3"/>
     </row>
-    <row r="821" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -35229,7 +35229,7 @@
       <c r="Y821" s="3"/>
       <c r="Z821" s="3"/>
     </row>
-    <row r="822" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -35257,7 +35257,7 @@
       <c r="Y822" s="3"/>
       <c r="Z822" s="3"/>
     </row>
-    <row r="823" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -35285,7 +35285,7 @@
       <c r="Y823" s="3"/>
       <c r="Z823" s="3"/>
     </row>
-    <row r="824" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -35313,7 +35313,7 @@
       <c r="Y824" s="3"/>
       <c r="Z824" s="3"/>
     </row>
-    <row r="825" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -35341,7 +35341,7 @@
       <c r="Y825" s="3"/>
       <c r="Z825" s="3"/>
     </row>
-    <row r="826" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -35369,7 +35369,7 @@
       <c r="Y826" s="3"/>
       <c r="Z826" s="3"/>
     </row>
-    <row r="827" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -35397,7 +35397,7 @@
       <c r="Y827" s="3"/>
       <c r="Z827" s="3"/>
     </row>
-    <row r="828" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -35425,7 +35425,7 @@
       <c r="Y828" s="3"/>
       <c r="Z828" s="3"/>
     </row>
-    <row r="829" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -35453,7 +35453,7 @@
       <c r="Y829" s="3"/>
       <c r="Z829" s="3"/>
     </row>
-    <row r="830" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -35481,7 +35481,7 @@
       <c r="Y830" s="3"/>
       <c r="Z830" s="3"/>
     </row>
-    <row r="831" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -35509,7 +35509,7 @@
       <c r="Y831" s="3"/>
       <c r="Z831" s="3"/>
     </row>
-    <row r="832" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -35537,7 +35537,7 @@
       <c r="Y832" s="3"/>
       <c r="Z832" s="3"/>
     </row>
-    <row r="833" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -35565,7 +35565,7 @@
       <c r="Y833" s="3"/>
       <c r="Z833" s="3"/>
     </row>
-    <row r="834" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -35593,7 +35593,7 @@
       <c r="Y834" s="3"/>
       <c r="Z834" s="3"/>
     </row>
-    <row r="835" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -35621,7 +35621,7 @@
       <c r="Y835" s="3"/>
       <c r="Z835" s="3"/>
     </row>
-    <row r="836" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -35649,7 +35649,7 @@
       <c r="Y836" s="3"/>
       <c r="Z836" s="3"/>
     </row>
-    <row r="837" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -35677,7 +35677,7 @@
       <c r="Y837" s="3"/>
       <c r="Z837" s="3"/>
     </row>
-    <row r="838" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -35705,7 +35705,7 @@
       <c r="Y838" s="3"/>
       <c r="Z838" s="3"/>
     </row>
-    <row r="839" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -35733,7 +35733,7 @@
       <c r="Y839" s="3"/>
       <c r="Z839" s="3"/>
     </row>
-    <row r="840" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -35761,7 +35761,7 @@
       <c r="Y840" s="3"/>
       <c r="Z840" s="3"/>
     </row>
-    <row r="841" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -35789,7 +35789,7 @@
       <c r="Y841" s="3"/>
       <c r="Z841" s="3"/>
     </row>
-    <row r="842" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -35817,7 +35817,7 @@
       <c r="Y842" s="3"/>
       <c r="Z842" s="3"/>
     </row>
-    <row r="843" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -35845,7 +35845,7 @@
       <c r="Y843" s="3"/>
       <c r="Z843" s="3"/>
     </row>
-    <row r="844" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -35873,7 +35873,7 @@
       <c r="Y844" s="3"/>
       <c r="Z844" s="3"/>
     </row>
-    <row r="845" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -35901,7 +35901,7 @@
       <c r="Y845" s="3"/>
       <c r="Z845" s="3"/>
     </row>
-    <row r="846" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -35929,7 +35929,7 @@
       <c r="Y846" s="3"/>
       <c r="Z846" s="3"/>
     </row>
-    <row r="847" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -35957,7 +35957,7 @@
       <c r="Y847" s="3"/>
       <c r="Z847" s="3"/>
     </row>
-    <row r="848" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -35985,7 +35985,7 @@
       <c r="Y848" s="3"/>
       <c r="Z848" s="3"/>
     </row>
-    <row r="849" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -36013,7 +36013,7 @@
       <c r="Y849" s="3"/>
       <c r="Z849" s="3"/>
     </row>
-    <row r="850" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -36041,7 +36041,7 @@
       <c r="Y850" s="3"/>
       <c r="Z850" s="3"/>
     </row>
-    <row r="851" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -36069,7 +36069,7 @@
       <c r="Y851" s="3"/>
       <c r="Z851" s="3"/>
     </row>
-    <row r="852" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -36097,7 +36097,7 @@
       <c r="Y852" s="3"/>
       <c r="Z852" s="3"/>
     </row>
-    <row r="853" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -36125,7 +36125,7 @@
       <c r="Y853" s="3"/>
       <c r="Z853" s="3"/>
     </row>
-    <row r="854" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -36153,7 +36153,7 @@
       <c r="Y854" s="3"/>
       <c r="Z854" s="3"/>
     </row>
-    <row r="855" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -36181,7 +36181,7 @@
       <c r="Y855" s="3"/>
       <c r="Z855" s="3"/>
     </row>
-    <row r="856" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -36209,7 +36209,7 @@
       <c r="Y856" s="3"/>
       <c r="Z856" s="3"/>
     </row>
-    <row r="857" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -36237,7 +36237,7 @@
       <c r="Y857" s="3"/>
       <c r="Z857" s="3"/>
     </row>
-    <row r="858" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -36265,7 +36265,7 @@
       <c r="Y858" s="3"/>
       <c r="Z858" s="3"/>
     </row>
-    <row r="859" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -36293,7 +36293,7 @@
       <c r="Y859" s="3"/>
       <c r="Z859" s="3"/>
     </row>
-    <row r="860" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -36321,7 +36321,7 @@
       <c r="Y860" s="3"/>
       <c r="Z860" s="3"/>
     </row>
-    <row r="861" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -36349,7 +36349,7 @@
       <c r="Y861" s="3"/>
       <c r="Z861" s="3"/>
     </row>
-    <row r="862" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -36377,7 +36377,7 @@
       <c r="Y862" s="3"/>
       <c r="Z862" s="3"/>
     </row>
-    <row r="863" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -36405,7 +36405,7 @@
       <c r="Y863" s="3"/>
       <c r="Z863" s="3"/>
     </row>
-    <row r="864" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -36433,7 +36433,7 @@
       <c r="Y864" s="3"/>
       <c r="Z864" s="3"/>
     </row>
-    <row r="865" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -36461,7 +36461,7 @@
       <c r="Y865" s="3"/>
       <c r="Z865" s="3"/>
     </row>
-    <row r="866" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -36489,7 +36489,7 @@
       <c r="Y866" s="3"/>
       <c r="Z866" s="3"/>
     </row>
-    <row r="867" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -36517,7 +36517,7 @@
       <c r="Y867" s="3"/>
       <c r="Z867" s="3"/>
     </row>
-    <row r="868" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -36545,7 +36545,7 @@
       <c r="Y868" s="3"/>
       <c r="Z868" s="3"/>
     </row>
-    <row r="869" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -36573,7 +36573,7 @@
       <c r="Y869" s="3"/>
       <c r="Z869" s="3"/>
     </row>
-    <row r="870" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -36601,7 +36601,7 @@
       <c r="Y870" s="3"/>
       <c r="Z870" s="3"/>
     </row>
-    <row r="871" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -36629,7 +36629,7 @@
       <c r="Y871" s="3"/>
       <c r="Z871" s="3"/>
     </row>
-    <row r="872" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -36657,7 +36657,7 @@
       <c r="Y872" s="3"/>
       <c r="Z872" s="3"/>
     </row>
-    <row r="873" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -36685,7 +36685,7 @@
       <c r="Y873" s="3"/>
       <c r="Z873" s="3"/>
     </row>
-    <row r="874" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -36713,7 +36713,7 @@
       <c r="Y874" s="3"/>
       <c r="Z874" s="3"/>
     </row>
-    <row r="875" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -36741,7 +36741,7 @@
       <c r="Y875" s="3"/>
       <c r="Z875" s="3"/>
     </row>
-    <row r="876" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -36769,7 +36769,7 @@
       <c r="Y876" s="3"/>
       <c r="Z876" s="3"/>
     </row>
-    <row r="877" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -36797,7 +36797,7 @@
       <c r="Y877" s="3"/>
       <c r="Z877" s="3"/>
     </row>
-    <row r="878" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -36825,7 +36825,7 @@
       <c r="Y878" s="3"/>
       <c r="Z878" s="3"/>
     </row>
-    <row r="879" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -36853,7 +36853,7 @@
       <c r="Y879" s="3"/>
       <c r="Z879" s="3"/>
     </row>
-    <row r="880" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -36881,7 +36881,7 @@
       <c r="Y880" s="3"/>
       <c r="Z880" s="3"/>
     </row>
-    <row r="881" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -36909,7 +36909,7 @@
       <c r="Y881" s="3"/>
       <c r="Z881" s="3"/>
     </row>
-    <row r="882" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -36937,7 +36937,7 @@
       <c r="Y882" s="3"/>
       <c r="Z882" s="3"/>
     </row>
-    <row r="883" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -36965,7 +36965,7 @@
       <c r="Y883" s="3"/>
       <c r="Z883" s="3"/>
     </row>
-    <row r="884" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -36993,7 +36993,7 @@
       <c r="Y884" s="3"/>
       <c r="Z884" s="3"/>
     </row>
-    <row r="885" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -37021,7 +37021,7 @@
       <c r="Y885" s="3"/>
       <c r="Z885" s="3"/>
     </row>
-    <row r="886" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -37049,7 +37049,7 @@
       <c r="Y886" s="3"/>
       <c r="Z886" s="3"/>
     </row>
-    <row r="887" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -37077,7 +37077,7 @@
       <c r="Y887" s="3"/>
       <c r="Z887" s="3"/>
     </row>
-    <row r="888" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -37105,7 +37105,7 @@
       <c r="Y888" s="3"/>
       <c r="Z888" s="3"/>
     </row>
-    <row r="889" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -37133,7 +37133,7 @@
       <c r="Y889" s="3"/>
       <c r="Z889" s="3"/>
     </row>
-    <row r="890" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -37161,7 +37161,7 @@
       <c r="Y890" s="3"/>
       <c r="Z890" s="3"/>
     </row>
-    <row r="891" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -37189,7 +37189,7 @@
       <c r="Y891" s="3"/>
       <c r="Z891" s="3"/>
     </row>
-    <row r="892" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -37217,7 +37217,7 @@
       <c r="Y892" s="3"/>
       <c r="Z892" s="3"/>
     </row>
-    <row r="893" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -37245,7 +37245,7 @@
       <c r="Y893" s="3"/>
       <c r="Z893" s="3"/>
     </row>
-    <row r="894" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -37273,7 +37273,7 @@
       <c r="Y894" s="3"/>
       <c r="Z894" s="3"/>
     </row>
-    <row r="895" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -37301,7 +37301,7 @@
       <c r="Y895" s="3"/>
       <c r="Z895" s="3"/>
     </row>
-    <row r="896" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -37329,7 +37329,7 @@
       <c r="Y896" s="3"/>
       <c r="Z896" s="3"/>
     </row>
-    <row r="897" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -37357,7 +37357,7 @@
       <c r="Y897" s="3"/>
       <c r="Z897" s="3"/>
     </row>
-    <row r="898" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -37385,7 +37385,7 @@
       <c r="Y898" s="3"/>
       <c r="Z898" s="3"/>
     </row>
-    <row r="899" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -37413,7 +37413,7 @@
       <c r="Y899" s="3"/>
       <c r="Z899" s="3"/>
     </row>
-    <row r="900" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -37441,7 +37441,7 @@
       <c r="Y900" s="3"/>
       <c r="Z900" s="3"/>
     </row>
-    <row r="901" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -37469,7 +37469,7 @@
       <c r="Y901" s="3"/>
       <c r="Z901" s="3"/>
     </row>
-    <row r="902" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -37497,7 +37497,7 @@
       <c r="Y902" s="3"/>
       <c r="Z902" s="3"/>
     </row>
-    <row r="903" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -37525,7 +37525,7 @@
       <c r="Y903" s="3"/>
       <c r="Z903" s="3"/>
     </row>
-    <row r="904" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -37553,7 +37553,7 @@
       <c r="Y904" s="3"/>
       <c r="Z904" s="3"/>
     </row>
-    <row r="905" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -37581,7 +37581,7 @@
       <c r="Y905" s="3"/>
       <c r="Z905" s="3"/>
     </row>
-    <row r="906" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -37609,7 +37609,7 @@
       <c r="Y906" s="3"/>
       <c r="Z906" s="3"/>
     </row>
-    <row r="907" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -37637,7 +37637,7 @@
       <c r="Y907" s="3"/>
       <c r="Z907" s="3"/>
     </row>
-    <row r="908" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -37665,7 +37665,7 @@
       <c r="Y908" s="3"/>
       <c r="Z908" s="3"/>
     </row>
-    <row r="909" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -37693,7 +37693,7 @@
       <c r="Y909" s="3"/>
       <c r="Z909" s="3"/>
     </row>
-    <row r="910" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -37721,7 +37721,7 @@
       <c r="Y910" s="3"/>
       <c r="Z910" s="3"/>
     </row>
-    <row r="911" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -37749,7 +37749,7 @@
       <c r="Y911" s="3"/>
       <c r="Z911" s="3"/>
     </row>
-    <row r="912" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -37777,7 +37777,7 @@
       <c r="Y912" s="3"/>
       <c r="Z912" s="3"/>
     </row>
-    <row r="913" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -37805,7 +37805,7 @@
       <c r="Y913" s="3"/>
       <c r="Z913" s="3"/>
     </row>
-    <row r="914" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -37833,7 +37833,7 @@
       <c r="Y914" s="3"/>
       <c r="Z914" s="3"/>
     </row>
-    <row r="915" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -37861,7 +37861,7 @@
       <c r="Y915" s="3"/>
       <c r="Z915" s="3"/>
     </row>
-    <row r="916" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -37889,7 +37889,7 @@
       <c r="Y916" s="3"/>
       <c r="Z916" s="3"/>
     </row>
-    <row r="917" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -37917,7 +37917,7 @@
       <c r="Y917" s="3"/>
       <c r="Z917" s="3"/>
     </row>
-    <row r="918" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -37945,7 +37945,7 @@
       <c r="Y918" s="3"/>
       <c r="Z918" s="3"/>
     </row>
-    <row r="919" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -37973,7 +37973,7 @@
       <c r="Y919" s="3"/>
       <c r="Z919" s="3"/>
     </row>
-    <row r="920" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -38001,7 +38001,7 @@
       <c r="Y920" s="3"/>
       <c r="Z920" s="3"/>
     </row>
-    <row r="921" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -38029,7 +38029,7 @@
       <c r="Y921" s="3"/>
       <c r="Z921" s="3"/>
     </row>
-    <row r="922" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -38057,7 +38057,7 @@
       <c r="Y922" s="3"/>
       <c r="Z922" s="3"/>
     </row>
-    <row r="923" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -38085,7 +38085,7 @@
       <c r="Y923" s="3"/>
       <c r="Z923" s="3"/>
     </row>
-    <row r="924" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -38113,7 +38113,7 @@
       <c r="Y924" s="3"/>
       <c r="Z924" s="3"/>
     </row>
-    <row r="925" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -38141,7 +38141,7 @@
       <c r="Y925" s="3"/>
       <c r="Z925" s="3"/>
     </row>
-    <row r="926" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -38169,7 +38169,7 @@
       <c r="Y926" s="3"/>
       <c r="Z926" s="3"/>
     </row>
-    <row r="927" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -38197,7 +38197,7 @@
       <c r="Y927" s="3"/>
       <c r="Z927" s="3"/>
     </row>
-    <row r="928" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -38225,7 +38225,7 @@
       <c r="Y928" s="3"/>
       <c r="Z928" s="3"/>
     </row>
-    <row r="929" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -38253,7 +38253,7 @@
       <c r="Y929" s="3"/>
       <c r="Z929" s="3"/>
     </row>
-    <row r="930" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -38281,7 +38281,7 @@
       <c r="Y930" s="3"/>
       <c r="Z930" s="3"/>
     </row>
-    <row r="931" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -38309,7 +38309,7 @@
       <c r="Y931" s="3"/>
       <c r="Z931" s="3"/>
     </row>
-    <row r="932" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -38337,7 +38337,7 @@
       <c r="Y932" s="3"/>
       <c r="Z932" s="3"/>
     </row>
-    <row r="933" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -38365,7 +38365,7 @@
       <c r="Y933" s="3"/>
       <c r="Z933" s="3"/>
     </row>
-    <row r="934" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -38393,7 +38393,7 @@
       <c r="Y934" s="3"/>
       <c r="Z934" s="3"/>
     </row>
-    <row r="935" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -38421,7 +38421,7 @@
       <c r="Y935" s="3"/>
       <c r="Z935" s="3"/>
     </row>
-    <row r="936" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -38449,7 +38449,7 @@
       <c r="Y936" s="3"/>
       <c r="Z936" s="3"/>
     </row>
-    <row r="937" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -38477,7 +38477,7 @@
       <c r="Y937" s="3"/>
       <c r="Z937" s="3"/>
     </row>
-    <row r="938" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -38505,7 +38505,7 @@
       <c r="Y938" s="3"/>
       <c r="Z938" s="3"/>
     </row>
-    <row r="939" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -38533,7 +38533,7 @@
       <c r="Y939" s="3"/>
       <c r="Z939" s="3"/>
     </row>
-    <row r="940" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -38561,7 +38561,7 @@
       <c r="Y940" s="3"/>
       <c r="Z940" s="3"/>
     </row>
-    <row r="941" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -38589,7 +38589,7 @@
       <c r="Y941" s="3"/>
       <c r="Z941" s="3"/>
     </row>
-    <row r="942" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -38617,7 +38617,7 @@
       <c r="Y942" s="3"/>
       <c r="Z942" s="3"/>
     </row>
-    <row r="943" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -38645,7 +38645,7 @@
       <c r="Y943" s="3"/>
       <c r="Z943" s="3"/>
     </row>
-    <row r="944" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -38673,7 +38673,7 @@
       <c r="Y944" s="3"/>
       <c r="Z944" s="3"/>
     </row>
-    <row r="945" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -38701,7 +38701,7 @@
       <c r="Y945" s="3"/>
       <c r="Z945" s="3"/>
     </row>
-    <row r="946" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -38729,7 +38729,7 @@
       <c r="Y946" s="3"/>
       <c r="Z946" s="3"/>
     </row>
-    <row r="947" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -38757,7 +38757,7 @@
       <c r="Y947" s="3"/>
       <c r="Z947" s="3"/>
     </row>
-    <row r="948" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -38785,7 +38785,7 @@
       <c r="Y948" s="3"/>
       <c r="Z948" s="3"/>
     </row>
-    <row r="949" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -38813,7 +38813,7 @@
       <c r="Y949" s="3"/>
       <c r="Z949" s="3"/>
     </row>
-    <row r="950" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -38841,7 +38841,7 @@
       <c r="Y950" s="3"/>
       <c r="Z950" s="3"/>
     </row>
-    <row r="951" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -38869,7 +38869,7 @@
       <c r="Y951" s="3"/>
       <c r="Z951" s="3"/>
     </row>
-    <row r="952" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -38897,7 +38897,7 @@
       <c r="Y952" s="3"/>
       <c r="Z952" s="3"/>
     </row>
-    <row r="953" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -38925,7 +38925,7 @@
       <c r="Y953" s="3"/>
       <c r="Z953" s="3"/>
     </row>
-    <row r="954" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -38953,7 +38953,7 @@
       <c r="Y954" s="3"/>
       <c r="Z954" s="3"/>
     </row>
-    <row r="955" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -38981,7 +38981,7 @@
       <c r="Y955" s="3"/>
       <c r="Z955" s="3"/>
     </row>
-    <row r="956" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -39009,7 +39009,7 @@
       <c r="Y956" s="3"/>
       <c r="Z956" s="3"/>
     </row>
-    <row r="957" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -39037,7 +39037,7 @@
       <c r="Y957" s="3"/>
       <c r="Z957" s="3"/>
     </row>
-    <row r="958" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -39065,7 +39065,7 @@
       <c r="Y958" s="3"/>
       <c r="Z958" s="3"/>
     </row>
-    <row r="959" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="3"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
@@ -39093,7 +39093,7 @@
       <c r="Y959" s="3"/>
       <c r="Z959" s="3"/>
     </row>
-    <row r="960" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="3"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
@@ -39121,7 +39121,7 @@
       <c r="Y960" s="3"/>
       <c r="Z960" s="3"/>
     </row>
-    <row r="961" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="3"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
@@ -39149,7 +39149,7 @@
       <c r="Y961" s="3"/>
       <c r="Z961" s="3"/>
     </row>
-    <row r="962" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="3"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
@@ -39177,7 +39177,7 @@
       <c r="Y962" s="3"/>
       <c r="Z962" s="3"/>
     </row>
-    <row r="963" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="3"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
@@ -39205,7 +39205,7 @@
       <c r="Y963" s="3"/>
       <c r="Z963" s="3"/>
     </row>
-    <row r="964" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="3"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
@@ -39233,7 +39233,7 @@
       <c r="Y964" s="3"/>
       <c r="Z964" s="3"/>
     </row>
-    <row r="965" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="3"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
@@ -39261,7 +39261,7 @@
       <c r="Y965" s="3"/>
       <c r="Z965" s="3"/>
     </row>
-    <row r="966" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="3"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
@@ -39289,7 +39289,7 @@
       <c r="Y966" s="3"/>
       <c r="Z966" s="3"/>
     </row>
-    <row r="967" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="3"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
@@ -39317,7 +39317,7 @@
       <c r="Y967" s="3"/>
       <c r="Z967" s="3"/>
     </row>
-    <row r="968" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="3"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
@@ -39345,7 +39345,7 @@
       <c r="Y968" s="3"/>
       <c r="Z968" s="3"/>
     </row>
-    <row r="969" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="3"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
@@ -39373,7 +39373,7 @@
       <c r="Y969" s="3"/>
       <c r="Z969" s="3"/>
     </row>
-    <row r="970" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="3"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
@@ -39401,7 +39401,7 @@
       <c r="Y970" s="3"/>
       <c r="Z970" s="3"/>
     </row>
-    <row r="971" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="3"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
@@ -39429,7 +39429,7 @@
       <c r="Y971" s="3"/>
       <c r="Z971" s="3"/>
     </row>
-    <row r="972" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="3"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
@@ -39457,7 +39457,7 @@
       <c r="Y972" s="3"/>
       <c r="Z972" s="3"/>
     </row>
-    <row r="973" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="3"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
@@ -39485,7 +39485,7 @@
       <c r="Y973" s="3"/>
       <c r="Z973" s="3"/>
     </row>
-    <row r="974" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -39513,7 +39513,7 @@
       <c r="Y974" s="3"/>
       <c r="Z974" s="3"/>
     </row>
-    <row r="975" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="3"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
@@ -39541,7 +39541,7 @@
       <c r="Y975" s="3"/>
       <c r="Z975" s="3"/>
     </row>
-    <row r="976" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
@@ -39569,7 +39569,7 @@
       <c r="Y976" s="3"/>
       <c r="Z976" s="3"/>
     </row>
-    <row r="977" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -39597,7 +39597,7 @@
       <c r="Y977" s="3"/>
       <c r="Z977" s="3"/>
     </row>
-    <row r="978" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="3"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
@@ -39625,7 +39625,7 @@
       <c r="Y978" s="3"/>
       <c r="Z978" s="3"/>
     </row>
-    <row r="979" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="3"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
@@ -39653,7 +39653,7 @@
       <c r="Y979" s="3"/>
       <c r="Z979" s="3"/>
     </row>
-    <row r="980" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="3"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
@@ -39681,7 +39681,7 @@
       <c r="Y980" s="3"/>
       <c r="Z980" s="3"/>
     </row>
-    <row r="981" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="3"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
@@ -39709,7 +39709,7 @@
       <c r="Y981" s="3"/>
       <c r="Z981" s="3"/>
     </row>
-    <row r="982" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="3"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
@@ -39737,7 +39737,7 @@
       <c r="Y982" s="3"/>
       <c r="Z982" s="3"/>
     </row>
-    <row r="983" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="3"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
@@ -39765,7 +39765,7 @@
       <c r="Y983" s="3"/>
       <c r="Z983" s="3"/>
     </row>
-    <row r="984" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="3"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
@@ -39793,7 +39793,7 @@
       <c r="Y984" s="3"/>
       <c r="Z984" s="3"/>
     </row>
-    <row r="985" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="3"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
@@ -39821,7 +39821,7 @@
       <c r="Y985" s="3"/>
       <c r="Z985" s="3"/>
     </row>
-    <row r="986" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="3"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
@@ -39849,7 +39849,7 @@
       <c r="Y986" s="3"/>
       <c r="Z986" s="3"/>
     </row>
-    <row r="987" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="3"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
@@ -39877,7 +39877,7 @@
       <c r="Y987" s="3"/>
       <c r="Z987" s="3"/>
     </row>
-    <row r="988" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="3"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
@@ -39905,7 +39905,7 @@
       <c r="Y988" s="3"/>
       <c r="Z988" s="3"/>
     </row>
-    <row r="989" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
@@ -39933,7 +39933,7 @@
       <c r="Y989" s="3"/>
       <c r="Z989" s="3"/>
     </row>
-    <row r="990" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="3"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
@@ -39961,7 +39961,7 @@
       <c r="Y990" s="3"/>
       <c r="Z990" s="3"/>
     </row>
-    <row r="991" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="3"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
@@ -39989,7 +39989,7 @@
       <c r="Y991" s="3"/>
       <c r="Z991" s="3"/>
     </row>
-    <row r="992" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="3"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
@@ -40017,7 +40017,7 @@
       <c r="Y992" s="3"/>
       <c r="Z992" s="3"/>
     </row>
-    <row r="993" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -40045,7 +40045,7 @@
       <c r="Y993" s="3"/>
       <c r="Z993" s="3"/>
     </row>
-    <row r="994" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -40073,7 +40073,7 @@
       <c r="Y994" s="3"/>
       <c r="Z994" s="3"/>
     </row>
-    <row r="995" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -40101,7 +40101,7 @@
       <c r="Y995" s="3"/>
       <c r="Z995" s="3"/>
     </row>
-    <row r="996" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="3"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
@@ -40129,7 +40129,7 @@
       <c r="Y996" s="3"/>
       <c r="Z996" s="3"/>
     </row>
-    <row r="997" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="3"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
@@ -40157,7 +40157,7 @@
       <c r="Y997" s="3"/>
       <c r="Z997" s="3"/>
     </row>
-    <row r="998" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="3"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
@@ -40185,7 +40185,7 @@
       <c r="Y998" s="3"/>
       <c r="Z998" s="3"/>
     </row>
-    <row r="999" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="3"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
@@ -40213,7 +40213,7 @@
       <c r="Y999" s="3"/>
       <c r="Z999" s="3"/>
     </row>
-    <row r="1000" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="3"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
@@ -40242,6 +40242,13 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H587" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="Time Discrimination"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/data/Data_Dictionary.xlsx
+++ b/data/Data_Dictionary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/Toffalini/TimeValidity/measures-validation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_EC4E860EFB524DA529C0F90297F944890C1F12D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD0CE978-42BB-4CC9-B6EC-168AF2521695}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_EC4E860EFB524DA529C0F90297F944890C1F12D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8A747DC-B538-451B-B45C-3A133670ADB8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3045" yWindow="1170" windowWidth="14985" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DataDictionary" sheetId="1" r:id="rId1"/>
@@ -4144,7 +4144,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4202,7 +4201,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -4238,7 +4237,7 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -4274,7 +4273,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -4310,7 +4309,7 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -4346,7 +4345,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -4382,7 +4381,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>22</v>
       </c>
@@ -4418,7 +4417,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -4454,7 +4453,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
@@ -4490,7 +4489,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -4526,7 +4525,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>33</v>
       </c>
@@ -4562,7 +4561,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>35</v>
       </c>
@@ -4598,7 +4597,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
@@ -4634,7 +4633,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
@@ -4670,7 +4669,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>44</v>
       </c>
@@ -4706,7 +4705,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
@@ -4748,7 +4747,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>
@@ -4790,7 +4789,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>55</v>
       </c>
@@ -4832,7 +4831,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
@@ -4874,7 +4873,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>59</v>
       </c>
@@ -4916,7 +4915,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
@@ -4958,7 +4957,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>63</v>
       </c>
@@ -5000,7 +4999,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>65</v>
       </c>
@@ -5042,7 +5041,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>67</v>
       </c>
@@ -5084,7 +5083,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>69</v>
       </c>
@@ -5126,7 +5125,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>71</v>
       </c>
@@ -5168,7 +5167,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>73</v>
       </c>
@@ -5210,7 +5209,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>75</v>
       </c>
@@ -5252,7 +5251,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>77</v>
       </c>
@@ -5294,7 +5293,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>79</v>
       </c>
@@ -5336,7 +5335,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>81</v>
       </c>
@@ -5378,7 +5377,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>83</v>
       </c>
@@ -5420,7 +5419,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>85</v>
       </c>
@@ -5462,7 +5461,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>87</v>
       </c>
@@ -5504,7 +5503,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>89</v>
       </c>
@@ -5546,7 +5545,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>91</v>
       </c>
@@ -5588,7 +5587,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>93</v>
       </c>
@@ -5630,7 +5629,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>95</v>
       </c>
@@ -5672,7 +5671,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>97</v>
       </c>
@@ -5714,7 +5713,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>99</v>
       </c>
@@ -5756,7 +5755,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>101</v>
       </c>
@@ -5798,7 +5797,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>103</v>
       </c>
@@ -5840,7 +5839,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>105</v>
       </c>
@@ -5882,7 +5881,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>107</v>
       </c>
@@ -5924,7 +5923,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>109</v>
       </c>
@@ -5966,7 +5965,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>111</v>
       </c>
@@ -6008,7 +6007,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>113</v>
       </c>
@@ -6050,7 +6049,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>115</v>
       </c>
@@ -6092,7 +6091,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>117</v>
       </c>
@@ -6134,7 +6133,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>119</v>
       </c>
@@ -6176,7 +6175,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>121</v>
       </c>
@@ -6218,7 +6217,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>123</v>
       </c>
@@ -6260,7 +6259,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>125</v>
       </c>
@@ -6302,7 +6301,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>127</v>
       </c>
@@ -6344,7 +6343,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>129</v>
       </c>
@@ -6386,7 +6385,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>131</v>
       </c>
@@ -6428,7 +6427,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>135</v>
       </c>
@@ -6470,7 +6469,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>141</v>
       </c>
@@ -6512,7 +6511,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>143</v>
       </c>
@@ -6554,7 +6553,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>146</v>
       </c>
@@ -6596,7 +6595,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>148</v>
       </c>
@@ -6638,7 +6637,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>150</v>
       </c>
@@ -6680,7 +6679,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>152</v>
       </c>
@@ -6722,7 +6721,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>154</v>
       </c>
@@ -6758,7 +6757,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>156</v>
       </c>
@@ -6794,7 +6793,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>159</v>
       </c>
@@ -6838,7 +6837,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>164</v>
       </c>
@@ -6882,7 +6881,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>166</v>
       </c>
@@ -6926,7 +6925,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>168</v>
       </c>
@@ -6970,7 +6969,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>170</v>
       </c>
@@ -7014,7 +7013,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>172</v>
       </c>
@@ -7058,7 +7057,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>174</v>
       </c>
@@ -7102,7 +7101,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>176</v>
       </c>
@@ -7146,7 +7145,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>178</v>
       </c>
@@ -7190,7 +7189,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>180</v>
       </c>
@@ -7234,7 +7233,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>182</v>
       </c>
@@ -7278,7 +7277,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>185</v>
       </c>
@@ -7314,7 +7313,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>187</v>
       </c>
@@ -7356,7 +7355,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>191</v>
       </c>
@@ -7398,7 +7397,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>193</v>
       </c>
@@ -7440,7 +7439,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>195</v>
       </c>
@@ -7482,7 +7481,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>197</v>
       </c>
@@ -7524,7 +7523,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>199</v>
       </c>
@@ -7564,7 +7563,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>201</v>
       </c>
@@ -7606,7 +7605,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>203</v>
       </c>
@@ -7648,7 +7647,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>205</v>
       </c>
@@ -7690,7 +7689,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>207</v>
       </c>
@@ -7732,7 +7731,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>209</v>
       </c>
@@ -7774,7 +7773,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>211</v>
       </c>
@@ -7814,7 +7813,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>213</v>
       </c>
@@ -7856,7 +7855,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>215</v>
       </c>
@@ -7898,7 +7897,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>217</v>
       </c>
@@ -7940,7 +7939,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>219</v>
       </c>
@@ -7980,7 +7979,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>221</v>
       </c>
@@ -8022,7 +8021,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>223</v>
       </c>
@@ -8064,7 +8063,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>225</v>
       </c>
@@ -8106,7 +8105,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>227</v>
       </c>
@@ -8148,7 +8147,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>229</v>
       </c>
@@ -8190,7 +8189,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>232</v>
       </c>
@@ -8232,7 +8231,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>235</v>
       </c>
@@ -8274,7 +8273,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>238</v>
       </c>
@@ -8316,7 +8315,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>240</v>
       </c>
@@ -8358,7 +8357,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>242</v>
       </c>
@@ -8398,7 +8397,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>244</v>
       </c>
@@ -8440,7 +8439,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>246</v>
       </c>
@@ -8482,7 +8481,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>248</v>
       </c>
@@ -8524,7 +8523,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
         <v>250</v>
       </c>
@@ -8566,7 +8565,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>252</v>
       </c>
@@ -8606,7 +8605,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>254</v>
       </c>
@@ -8648,7 +8647,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>256</v>
       </c>
@@ -8690,7 +8689,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>258</v>
       </c>
@@ -8732,7 +8731,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>260</v>
       </c>
@@ -8772,7 +8771,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>262</v>
       </c>
@@ -8812,7 +8811,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>264</v>
       </c>
@@ -8852,7 +8851,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>266</v>
       </c>
@@ -8894,7 +8893,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>268</v>
       </c>
@@ -8936,7 +8935,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>270</v>
       </c>
@@ -8976,7 +8975,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>272</v>
       </c>
@@ -9018,7 +9017,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>274</v>
       </c>
@@ -9058,7 +9057,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>276</v>
       </c>
@@ -9100,7 +9099,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
         <v>278</v>
       </c>
@@ -9140,7 +9139,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
         <v>280</v>
       </c>
@@ -9182,7 +9181,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
         <v>281</v>
       </c>
@@ -9224,7 +9223,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
         <v>287</v>
       </c>
@@ -9266,7 +9265,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
         <v>290</v>
       </c>
@@ -9308,7 +9307,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>292</v>
       </c>
@@ -9350,7 +9349,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
         <v>294</v>
       </c>
@@ -9392,7 +9391,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
         <v>296</v>
       </c>
@@ -9434,7 +9433,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
         <v>298</v>
       </c>
@@ -9476,7 +9475,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>300</v>
       </c>
@@ -9518,7 +9517,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>302</v>
       </c>
@@ -9560,7 +9559,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>304</v>
       </c>
@@ -9602,7 +9601,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>306</v>
       </c>
@@ -9644,7 +9643,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>308</v>
       </c>
@@ -9686,7 +9685,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>310</v>
       </c>
@@ -9728,7 +9727,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>312</v>
       </c>
@@ -9770,7 +9769,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>314</v>
       </c>
@@ -9812,7 +9811,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>317</v>
       </c>
@@ -9854,7 +9853,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>319</v>
       </c>
@@ -9896,7 +9895,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>322</v>
       </c>
@@ -9938,7 +9937,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>324</v>
       </c>
@@ -9980,7 +9979,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>328</v>
       </c>
@@ -10022,7 +10021,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>330</v>
       </c>
@@ -10064,7 +10063,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>332</v>
       </c>
@@ -10106,7 +10105,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>334</v>
       </c>
@@ -10148,7 +10147,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
         <v>336</v>
       </c>
@@ -10190,7 +10189,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
         <v>338</v>
       </c>
@@ -10232,7 +10231,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
         <v>340</v>
       </c>
@@ -10274,7 +10273,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
         <v>342</v>
       </c>
@@ -10316,7 +10315,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>344</v>
       </c>
@@ -10358,7 +10357,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
         <v>346</v>
       </c>
@@ -10400,7 +10399,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
         <v>348</v>
       </c>
@@ -10442,7 +10441,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
         <v>350</v>
       </c>
@@ -10484,7 +10483,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
         <v>352</v>
       </c>
@@ -10526,7 +10525,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
         <v>354</v>
       </c>
@@ -10568,7 +10567,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>356</v>
       </c>
@@ -10610,7 +10609,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
         <v>358</v>
       </c>
@@ -10652,7 +10651,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
         <v>360</v>
       </c>
@@ -10694,7 +10693,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
         <v>362</v>
       </c>
@@ -10736,7 +10735,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
         <v>364</v>
       </c>
@@ -10778,7 +10777,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
         <v>366</v>
       </c>
@@ -10820,7 +10819,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
         <v>368</v>
       </c>
@@ -10862,7 +10861,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
         <v>370</v>
       </c>
@@ -10904,7 +10903,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>372</v>
       </c>
@@ -10946,7 +10945,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
         <v>374</v>
       </c>
@@ -10988,7 +10987,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
         <v>376</v>
       </c>
@@ -11030,7 +11029,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
         <v>378</v>
       </c>
@@ -11072,7 +11071,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
         <v>380</v>
       </c>
@@ -11114,7 +11113,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
         <v>382</v>
       </c>
@@ -11156,7 +11155,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
         <v>384</v>
       </c>
@@ -11198,7 +11197,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
         <v>386</v>
       </c>
@@ -11240,7 +11239,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
         <v>388</v>
       </c>
@@ -11282,7 +11281,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
         <v>390</v>
       </c>
@@ -11324,7 +11323,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
         <v>392</v>
       </c>
@@ -11366,7 +11365,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
         <v>394</v>
       </c>
@@ -11408,7 +11407,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
         <v>396</v>
       </c>
@@ -11450,7 +11449,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>398</v>
       </c>
@@ -11492,7 +11491,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>400</v>
       </c>
@@ -11534,7 +11533,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>402</v>
       </c>
@@ -11576,7 +11575,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>404</v>
       </c>
@@ -11618,7 +11617,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>406</v>
       </c>
@@ -11660,7 +11659,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>408</v>
       </c>
@@ -11702,7 +11701,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>410</v>
       </c>
@@ -11744,7 +11743,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>412</v>
       </c>
@@ -11786,7 +11785,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>414</v>
       </c>
@@ -11828,7 +11827,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>416</v>
       </c>
@@ -11870,7 +11869,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>419</v>
       </c>
@@ -11912,7 +11911,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>422</v>
       </c>
@@ -11954,7 +11953,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>424</v>
       </c>
@@ -11996,7 +11995,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>426</v>
       </c>
@@ -12038,7 +12037,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>428</v>
       </c>
@@ -12080,7 +12079,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>430</v>
       </c>
@@ -12122,7 +12121,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
         <v>432</v>
       </c>
@@ -12164,7 +12163,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
         <v>434</v>
       </c>
@@ -12206,7 +12205,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
         <v>436</v>
       </c>
@@ -12248,7 +12247,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
         <v>438</v>
       </c>
@@ -12290,7 +12289,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
         <v>440</v>
       </c>
@@ -12332,7 +12331,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
         <v>442</v>
       </c>
@@ -12374,7 +12373,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
         <v>444</v>
       </c>
@@ -12416,7 +12415,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
         <v>446</v>
       </c>
@@ -12458,7 +12457,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
         <v>448</v>
       </c>
@@ -12500,7 +12499,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
         <v>450</v>
       </c>
@@ -12542,7 +12541,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
         <v>452</v>
       </c>
@@ -12584,7 +12583,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
         <v>454</v>
       </c>
@@ -12626,7 +12625,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
         <v>456</v>
       </c>
@@ -12668,7 +12667,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
         <v>458</v>
       </c>
@@ -12710,7 +12709,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
         <v>460</v>
       </c>
@@ -12752,7 +12751,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
         <v>462</v>
       </c>
@@ -12794,7 +12793,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
         <v>464</v>
       </c>
@@ -12836,7 +12835,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
         <v>466</v>
       </c>
@@ -12878,7 +12877,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
         <v>468</v>
       </c>
@@ -12920,7 +12919,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
         <v>470</v>
       </c>
@@ -12962,7 +12961,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
         <v>472</v>
       </c>
@@ -13004,7 +13003,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
         <v>474</v>
       </c>
@@ -13046,7 +13045,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
         <v>476</v>
       </c>
@@ -13088,7 +13087,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
         <v>478</v>
       </c>
@@ -13130,7 +13129,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
         <v>480</v>
       </c>
@@ -13172,7 +13171,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
         <v>482</v>
       </c>
@@ -13214,7 +13213,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
         <v>484</v>
       </c>
@@ -13256,7 +13255,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
         <v>486</v>
       </c>
@@ -13298,7 +13297,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
         <v>488</v>
       </c>
@@ -13340,7 +13339,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="3"/>
     </row>
-    <row r="222" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
         <v>490</v>
       </c>
@@ -13382,7 +13381,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="3"/>
     </row>
-    <row r="223" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
         <v>492</v>
       </c>
@@ -13424,7 +13423,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="3"/>
     </row>
-    <row r="224" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
         <v>494</v>
       </c>
@@ -13466,7 +13465,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
     </row>
-    <row r="225" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
         <v>496</v>
       </c>
@@ -13508,7 +13507,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="3"/>
     </row>
-    <row r="226" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
         <v>498</v>
       </c>
@@ -13550,7 +13549,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="3"/>
     </row>
-    <row r="227" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
         <v>500</v>
       </c>
@@ -13592,7 +13591,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="3"/>
     </row>
-    <row r="228" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
         <v>502</v>
       </c>
@@ -13634,7 +13633,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="3"/>
     </row>
-    <row r="229" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>504</v>
       </c>
@@ -13676,7 +13675,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
     </row>
-    <row r="230" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
         <v>506</v>
       </c>
@@ -13718,7 +13717,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="3"/>
     </row>
-    <row r="231" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
         <v>508</v>
       </c>
@@ -13760,7 +13759,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="3"/>
     </row>
-    <row r="232" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
         <v>510</v>
       </c>
@@ -13802,7 +13801,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
     </row>
-    <row r="233" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
         <v>512</v>
       </c>
@@ -13844,7 +13843,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
     </row>
-    <row r="234" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
         <v>516</v>
       </c>
@@ -13886,7 +13885,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
     </row>
-    <row r="235" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
         <v>518</v>
       </c>
@@ -13928,7 +13927,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="3"/>
     </row>
-    <row r="236" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
         <v>520</v>
       </c>
@@ -13970,7 +13969,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="3"/>
     </row>
-    <row r="237" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
         <v>522</v>
       </c>
@@ -14012,7 +14011,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="3"/>
     </row>
-    <row r="238" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
         <v>524</v>
       </c>
@@ -14054,7 +14053,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="3"/>
     </row>
-    <row r="239" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
         <v>526</v>
       </c>
@@ -14096,7 +14095,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="3"/>
     </row>
-    <row r="240" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
         <v>529</v>
       </c>
@@ -14138,7 +14137,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="3"/>
     </row>
-    <row r="241" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
         <v>531</v>
       </c>
@@ -14180,7 +14179,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="3"/>
     </row>
-    <row r="242" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
         <v>534</v>
       </c>
@@ -14222,7 +14221,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
     </row>
-    <row r="243" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
         <v>536</v>
       </c>
@@ -14264,7 +14263,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="3"/>
     </row>
-    <row r="244" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
         <v>538</v>
       </c>
@@ -14306,7 +14305,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="3"/>
     </row>
-    <row r="245" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
         <v>540</v>
       </c>
@@ -14348,7 +14347,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
     </row>
-    <row r="246" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
         <v>542</v>
       </c>
@@ -14390,7 +14389,7 @@
       <c r="Y246" s="3"/>
       <c r="Z246" s="3"/>
     </row>
-    <row r="247" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
         <v>544</v>
       </c>
@@ -14432,7 +14431,7 @@
       <c r="Y247" s="3"/>
       <c r="Z247" s="3"/>
     </row>
-    <row r="248" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
         <v>546</v>
       </c>
@@ -14474,7 +14473,7 @@
       <c r="Y248" s="3"/>
       <c r="Z248" s="3"/>
     </row>
-    <row r="249" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
         <v>548</v>
       </c>
@@ -14516,7 +14515,7 @@
       <c r="Y249" s="3"/>
       <c r="Z249" s="3"/>
     </row>
-    <row r="250" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
         <v>550</v>
       </c>
@@ -14558,7 +14557,7 @@
       <c r="Y250" s="3"/>
       <c r="Z250" s="3"/>
     </row>
-    <row r="251" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
         <v>552</v>
       </c>
@@ -14600,7 +14599,7 @@
       <c r="Y251" s="3"/>
       <c r="Z251" s="3"/>
     </row>
-    <row r="252" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
         <v>554</v>
       </c>
@@ -14642,7 +14641,7 @@
       <c r="Y252" s="3"/>
       <c r="Z252" s="3"/>
     </row>
-    <row r="253" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
         <v>556</v>
       </c>
@@ -14684,7 +14683,7 @@
       <c r="Y253" s="3"/>
       <c r="Z253" s="3"/>
     </row>
-    <row r="254" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
         <v>558</v>
       </c>
@@ -14726,7 +14725,7 @@
       <c r="Y254" s="3"/>
       <c r="Z254" s="3"/>
     </row>
-    <row r="255" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
         <v>560</v>
       </c>
@@ -14768,7 +14767,7 @@
       <c r="Y255" s="3"/>
       <c r="Z255" s="3"/>
     </row>
-    <row r="256" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
         <v>562</v>
       </c>
@@ -14810,7 +14809,7 @@
       <c r="Y256" s="3"/>
       <c r="Z256" s="3"/>
     </row>
-    <row r="257" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
         <v>564</v>
       </c>
@@ -14852,7 +14851,7 @@
       <c r="Y257" s="3"/>
       <c r="Z257" s="3"/>
     </row>
-    <row r="258" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
         <v>566</v>
       </c>
@@ -14894,7 +14893,7 @@
       <c r="Y258" s="3"/>
       <c r="Z258" s="3"/>
     </row>
-    <row r="259" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
         <v>568</v>
       </c>
@@ -14936,7 +14935,7 @@
       <c r="Y259" s="3"/>
       <c r="Z259" s="3"/>
     </row>
-    <row r="260" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
         <v>570</v>
       </c>
@@ -14978,7 +14977,7 @@
       <c r="Y260" s="3"/>
       <c r="Z260" s="3"/>
     </row>
-    <row r="261" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
         <v>572</v>
       </c>
@@ -15020,7 +15019,7 @@
       <c r="Y261" s="3"/>
       <c r="Z261" s="3"/>
     </row>
-    <row r="262" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
         <v>574</v>
       </c>
@@ -15062,7 +15061,7 @@
       <c r="Y262" s="3"/>
       <c r="Z262" s="3"/>
     </row>
-    <row r="263" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
         <v>576</v>
       </c>
@@ -15104,7 +15103,7 @@
       <c r="Y263" s="3"/>
       <c r="Z263" s="3"/>
     </row>
-    <row r="264" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
         <v>578</v>
       </c>
@@ -15146,7 +15145,7 @@
       <c r="Y264" s="3"/>
       <c r="Z264" s="3"/>
     </row>
-    <row r="265" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
         <v>580</v>
       </c>
@@ -15188,7 +15187,7 @@
       <c r="Y265" s="3"/>
       <c r="Z265" s="3"/>
     </row>
-    <row r="266" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
         <v>582</v>
       </c>
@@ -15230,7 +15229,7 @@
       <c r="Y266" s="3"/>
       <c r="Z266" s="3"/>
     </row>
-    <row r="267" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
         <v>584</v>
       </c>
@@ -15272,7 +15271,7 @@
       <c r="Y267" s="3"/>
       <c r="Z267" s="3"/>
     </row>
-    <row r="268" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
         <v>586</v>
       </c>
@@ -15314,7 +15313,7 @@
       <c r="Y268" s="3"/>
       <c r="Z268" s="3"/>
     </row>
-    <row r="269" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
         <v>588</v>
       </c>
@@ -15356,7 +15355,7 @@
       <c r="Y269" s="3"/>
       <c r="Z269" s="3"/>
     </row>
-    <row r="270" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
         <v>590</v>
       </c>
@@ -15398,7 +15397,7 @@
       <c r="Y270" s="3"/>
       <c r="Z270" s="3"/>
     </row>
-    <row r="271" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
         <v>592</v>
       </c>
@@ -15440,7 +15439,7 @@
       <c r="Y271" s="3"/>
       <c r="Z271" s="3"/>
     </row>
-    <row r="272" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
         <v>594</v>
       </c>
@@ -15482,7 +15481,7 @@
       <c r="Y272" s="3"/>
       <c r="Z272" s="3"/>
     </row>
-    <row r="273" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="3" t="s">
         <v>596</v>
       </c>
@@ -15524,7 +15523,7 @@
       <c r="Y273" s="3"/>
       <c r="Z273" s="3"/>
     </row>
-    <row r="274" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="3" t="s">
         <v>598</v>
       </c>
@@ -15566,7 +15565,7 @@
       <c r="Y274" s="3"/>
       <c r="Z274" s="3"/>
     </row>
-    <row r="275" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="3" t="s">
         <v>600</v>
       </c>
@@ -15608,7 +15607,7 @@
       <c r="Y275" s="3"/>
       <c r="Z275" s="3"/>
     </row>
-    <row r="276" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
         <v>602</v>
       </c>
@@ -15650,7 +15649,7 @@
       <c r="Y276" s="3"/>
       <c r="Z276" s="3"/>
     </row>
-    <row r="277" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="3" t="s">
         <v>604</v>
       </c>
@@ -15692,7 +15691,7 @@
       <c r="Y277" s="3"/>
       <c r="Z277" s="3"/>
     </row>
-    <row r="278" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
         <v>606</v>
       </c>
@@ -15734,7 +15733,7 @@
       <c r="Y278" s="3"/>
       <c r="Z278" s="3"/>
     </row>
-    <row r="279" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="3" t="s">
         <v>608</v>
       </c>
@@ -15776,7 +15775,7 @@
       <c r="Y279" s="3"/>
       <c r="Z279" s="3"/>
     </row>
-    <row r="280" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
         <v>610</v>
       </c>
@@ -15818,7 +15817,7 @@
       <c r="Y280" s="3"/>
       <c r="Z280" s="3"/>
     </row>
-    <row r="281" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
         <v>612</v>
       </c>
@@ -15860,7 +15859,7 @@
       <c r="Y281" s="3"/>
       <c r="Z281" s="3"/>
     </row>
-    <row r="282" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="3" t="s">
         <v>614</v>
       </c>
@@ -15902,7 +15901,7 @@
       <c r="Y282" s="3"/>
       <c r="Z282" s="3"/>
     </row>
-    <row r="283" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
         <v>616</v>
       </c>
@@ -15944,7 +15943,7 @@
       <c r="Y283" s="3"/>
       <c r="Z283" s="3"/>
     </row>
-    <row r="284" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
         <v>618</v>
       </c>
@@ -15986,7 +15985,7 @@
       <c r="Y284" s="3"/>
       <c r="Z284" s="3"/>
     </row>
-    <row r="285" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
         <v>620</v>
       </c>
@@ -16028,7 +16027,7 @@
       <c r="Y285" s="3"/>
       <c r="Z285" s="3"/>
     </row>
-    <row r="286" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
         <v>622</v>
       </c>
@@ -16070,7 +16069,7 @@
       <c r="Y286" s="3"/>
       <c r="Z286" s="3"/>
     </row>
-    <row r="287" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
         <v>624</v>
       </c>
@@ -16112,7 +16111,7 @@
       <c r="Y287" s="3"/>
       <c r="Z287" s="3"/>
     </row>
-    <row r="288" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="3" t="s">
         <v>626</v>
       </c>
@@ -16154,7 +16153,7 @@
       <c r="Y288" s="3"/>
       <c r="Z288" s="3"/>
     </row>
-    <row r="289" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
         <v>631</v>
       </c>
@@ -16196,7 +16195,7 @@
       <c r="Y289" s="3"/>
       <c r="Z289" s="3"/>
     </row>
-    <row r="290" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="3" t="s">
         <v>633</v>
       </c>
@@ -16238,7 +16237,7 @@
       <c r="Y290" s="3"/>
       <c r="Z290" s="3"/>
     </row>
-    <row r="291" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
         <v>635</v>
       </c>
@@ -16280,7 +16279,7 @@
       <c r="Y291" s="3"/>
       <c r="Z291" s="3"/>
     </row>
-    <row r="292" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="3" t="s">
         <v>638</v>
       </c>
@@ -16322,7 +16321,7 @@
       <c r="Y292" s="3"/>
       <c r="Z292" s="3"/>
     </row>
-    <row r="293" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
         <v>640</v>
       </c>
@@ -16364,7 +16363,7 @@
       <c r="Y293" s="3"/>
       <c r="Z293" s="3"/>
     </row>
-    <row r="294" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
         <v>642</v>
       </c>
@@ -16406,7 +16405,7 @@
       <c r="Y294" s="3"/>
       <c r="Z294" s="3"/>
     </row>
-    <row r="295" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="3" t="s">
         <v>644</v>
       </c>
@@ -16448,7 +16447,7 @@
       <c r="Y295" s="3"/>
       <c r="Z295" s="3"/>
     </row>
-    <row r="296" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
         <v>646</v>
       </c>
@@ -16490,7 +16489,7 @@
       <c r="Y296" s="3"/>
       <c r="Z296" s="3"/>
     </row>
-    <row r="297" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="3" t="s">
         <v>648</v>
       </c>
@@ -16532,7 +16531,7 @@
       <c r="Y297" s="3"/>
       <c r="Z297" s="3"/>
     </row>
-    <row r="298" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
         <v>650</v>
       </c>
@@ -16574,7 +16573,7 @@
       <c r="Y298" s="3"/>
       <c r="Z298" s="3"/>
     </row>
-    <row r="299" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
         <v>652</v>
       </c>
@@ -16616,7 +16615,7 @@
       <c r="Y299" s="3"/>
       <c r="Z299" s="3"/>
     </row>
-    <row r="300" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
         <v>654</v>
       </c>
@@ -16658,7 +16657,7 @@
       <c r="Y300" s="3"/>
       <c r="Z300" s="3"/>
     </row>
-    <row r="301" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
         <v>656</v>
       </c>
@@ -16700,7 +16699,7 @@
       <c r="Y301" s="3"/>
       <c r="Z301" s="3"/>
     </row>
-    <row r="302" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
         <v>658</v>
       </c>
@@ -16742,7 +16741,7 @@
       <c r="Y302" s="3"/>
       <c r="Z302" s="3"/>
     </row>
-    <row r="303" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
         <v>660</v>
       </c>
@@ -16784,7 +16783,7 @@
       <c r="Y303" s="3"/>
       <c r="Z303" s="3"/>
     </row>
-    <row r="304" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
         <v>662</v>
       </c>
@@ -16826,7 +16825,7 @@
       <c r="Y304" s="3"/>
       <c r="Z304" s="3"/>
     </row>
-    <row r="305" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
         <v>664</v>
       </c>
@@ -16868,7 +16867,7 @@
       <c r="Y305" s="3"/>
       <c r="Z305" s="3"/>
     </row>
-    <row r="306" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
         <v>666</v>
       </c>
@@ -16910,7 +16909,7 @@
       <c r="Y306" s="3"/>
       <c r="Z306" s="3"/>
     </row>
-    <row r="307" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
         <v>668</v>
       </c>
@@ -16952,7 +16951,7 @@
       <c r="Y307" s="3"/>
       <c r="Z307" s="3"/>
     </row>
-    <row r="308" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
         <v>670</v>
       </c>
@@ -16994,7 +16993,7 @@
       <c r="Y308" s="3"/>
       <c r="Z308" s="3"/>
     </row>
-    <row r="309" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
         <v>672</v>
       </c>
@@ -17036,7 +17035,7 @@
       <c r="Y309" s="3"/>
       <c r="Z309" s="3"/>
     </row>
-    <row r="310" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
         <v>674</v>
       </c>
@@ -17078,7 +17077,7 @@
       <c r="Y310" s="3"/>
       <c r="Z310" s="3"/>
     </row>
-    <row r="311" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
         <v>676</v>
       </c>
@@ -17120,7 +17119,7 @@
       <c r="Y311" s="3"/>
       <c r="Z311" s="3"/>
     </row>
-    <row r="312" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
         <v>678</v>
       </c>
@@ -17161,7 +17160,7 @@
       <c r="Y312" s="3"/>
       <c r="Z312" s="3"/>
     </row>
-    <row r="313" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
         <v>682</v>
       </c>
@@ -17203,7 +17202,7 @@
       <c r="Y313" s="3"/>
       <c r="Z313" s="3"/>
     </row>
-    <row r="314" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
         <v>684</v>
       </c>
@@ -17245,7 +17244,7 @@
       <c r="Y314" s="3"/>
       <c r="Z314" s="3"/>
     </row>
-    <row r="315" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
         <v>686</v>
       </c>
@@ -17287,7 +17286,7 @@
       <c r="Y315" s="3"/>
       <c r="Z315" s="3"/>
     </row>
-    <row r="316" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
         <v>688</v>
       </c>
@@ -17329,7 +17328,7 @@
       <c r="Y316" s="3"/>
       <c r="Z316" s="3"/>
     </row>
-    <row r="317" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
         <v>690</v>
       </c>
@@ -17371,7 +17370,7 @@
       <c r="Y317" s="3"/>
       <c r="Z317" s="3"/>
     </row>
-    <row r="318" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
         <v>692</v>
       </c>
@@ -17413,7 +17412,7 @@
       <c r="Y318" s="3"/>
       <c r="Z318" s="3"/>
     </row>
-    <row r="319" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
         <v>694</v>
       </c>
@@ -17455,7 +17454,7 @@
       <c r="Y319" s="3"/>
       <c r="Z319" s="3"/>
     </row>
-    <row r="320" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
         <v>696</v>
       </c>
@@ -17497,7 +17496,7 @@
       <c r="Y320" s="3"/>
       <c r="Z320" s="3"/>
     </row>
-    <row r="321" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
         <v>698</v>
       </c>
@@ -17539,7 +17538,7 @@
       <c r="Y321" s="3"/>
       <c r="Z321" s="3"/>
     </row>
-    <row r="322" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
         <v>700</v>
       </c>
@@ -17581,7 +17580,7 @@
       <c r="Y322" s="3"/>
       <c r="Z322" s="3"/>
     </row>
-    <row r="323" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
         <v>702</v>
       </c>
@@ -17623,7 +17622,7 @@
       <c r="Y323" s="3"/>
       <c r="Z323" s="3"/>
     </row>
-    <row r="324" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
         <v>705</v>
       </c>
@@ -17665,7 +17664,7 @@
       <c r="Y324" s="3"/>
       <c r="Z324" s="3"/>
     </row>
-    <row r="325" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
         <v>707</v>
       </c>
@@ -17707,7 +17706,7 @@
       <c r="Y325" s="3"/>
       <c r="Z325" s="3"/>
     </row>
-    <row r="326" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
         <v>709</v>
       </c>
@@ -17749,7 +17748,7 @@
       <c r="Y326" s="3"/>
       <c r="Z326" s="3"/>
     </row>
-    <row r="327" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
         <v>711</v>
       </c>
@@ -17791,7 +17790,7 @@
       <c r="Y327" s="3"/>
       <c r="Z327" s="3"/>
     </row>
-    <row r="328" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
         <v>713</v>
       </c>
@@ -17833,7 +17832,7 @@
       <c r="Y328" s="3"/>
       <c r="Z328" s="3"/>
     </row>
-    <row r="329" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
         <v>715</v>
       </c>
@@ -17875,7 +17874,7 @@
       <c r="Y329" s="3"/>
       <c r="Z329" s="3"/>
     </row>
-    <row r="330" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
         <v>717</v>
       </c>
@@ -17917,7 +17916,7 @@
       <c r="Y330" s="3"/>
       <c r="Z330" s="3"/>
     </row>
-    <row r="331" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
         <v>719</v>
       </c>
@@ -17959,7 +17958,7 @@
       <c r="Y331" s="3"/>
       <c r="Z331" s="3"/>
     </row>
-    <row r="332" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
         <v>721</v>
       </c>
@@ -18001,7 +18000,7 @@
       <c r="Y332" s="3"/>
       <c r="Z332" s="3"/>
     </row>
-    <row r="333" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
         <v>723</v>
       </c>
@@ -18043,7 +18042,7 @@
       <c r="Y333" s="3"/>
       <c r="Z333" s="3"/>
     </row>
-    <row r="334" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
         <v>725</v>
       </c>
@@ -18085,7 +18084,7 @@
       <c r="Y334" s="3"/>
       <c r="Z334" s="3"/>
     </row>
-    <row r="335" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
         <v>727</v>
       </c>
@@ -18127,7 +18126,7 @@
       <c r="Y335" s="3"/>
       <c r="Z335" s="3"/>
     </row>
-    <row r="336" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
         <v>729</v>
       </c>
@@ -18169,7 +18168,7 @@
       <c r="Y336" s="3"/>
       <c r="Z336" s="3"/>
     </row>
-    <row r="337" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
         <v>731</v>
       </c>
@@ -18211,7 +18210,7 @@
       <c r="Y337" s="3"/>
       <c r="Z337" s="3"/>
     </row>
-    <row r="338" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
         <v>733</v>
       </c>
@@ -18253,7 +18252,7 @@
       <c r="Y338" s="3"/>
       <c r="Z338" s="3"/>
     </row>
-    <row r="339" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
         <v>735</v>
       </c>
@@ -18295,7 +18294,7 @@
       <c r="Y339" s="3"/>
       <c r="Z339" s="3"/>
     </row>
-    <row r="340" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
         <v>737</v>
       </c>
@@ -18337,7 +18336,7 @@
       <c r="Y340" s="3"/>
       <c r="Z340" s="3"/>
     </row>
-    <row r="341" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
         <v>739</v>
       </c>
@@ -18379,7 +18378,7 @@
       <c r="Y341" s="3"/>
       <c r="Z341" s="3"/>
     </row>
-    <row r="342" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
         <v>741</v>
       </c>
@@ -18421,7 +18420,7 @@
       <c r="Y342" s="3"/>
       <c r="Z342" s="3"/>
     </row>
-    <row r="343" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
         <v>743</v>
       </c>
@@ -18463,7 +18462,7 @@
       <c r="Y343" s="3"/>
       <c r="Z343" s="3"/>
     </row>
-    <row r="344" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
         <v>745</v>
       </c>
@@ -18505,7 +18504,7 @@
       <c r="Y344" s="3"/>
       <c r="Z344" s="3"/>
     </row>
-    <row r="345" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
         <v>747</v>
       </c>
@@ -18547,7 +18546,7 @@
       <c r="Y345" s="3"/>
       <c r="Z345" s="3"/>
     </row>
-    <row r="346" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:26" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
         <v>749</v>
       </c>
@@ -18671,7 +18670,7 @@
       <c r="Y348" s="3"/>
       <c r="Z348" s="3"/>
     </row>
-    <row r="349" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
         <v>759</v>
       </c>
@@ -18751,7 +18750,7 @@
       <c r="Y350" s="3"/>
       <c r="Z350" s="3"/>
     </row>
-    <row r="351" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
         <v>763</v>
       </c>
@@ -18787,7 +18786,7 @@
       <c r="Y351" s="3"/>
       <c r="Z351" s="3"/>
     </row>
-    <row r="352" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
         <v>765</v>
       </c>
@@ -18829,7 +18828,7 @@
       <c r="Y352" s="3"/>
       <c r="Z352" s="3"/>
     </row>
-    <row r="353" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
         <v>769</v>
       </c>
@@ -18871,7 +18870,7 @@
       <c r="Y353" s="3"/>
       <c r="Z353" s="3"/>
     </row>
-    <row r="354" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
         <v>771</v>
       </c>
@@ -18913,7 +18912,7 @@
       <c r="Y354" s="3"/>
       <c r="Z354" s="3"/>
     </row>
-    <row r="355" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
         <v>773</v>
       </c>
@@ -18955,7 +18954,7 @@
       <c r="Y355" s="3"/>
       <c r="Z355" s="3"/>
     </row>
-    <row r="356" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
         <v>775</v>
       </c>
@@ -18997,7 +18996,7 @@
       <c r="Y356" s="3"/>
       <c r="Z356" s="3"/>
     </row>
-    <row r="357" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
         <v>777</v>
       </c>
@@ -19039,7 +19038,7 @@
       <c r="Y357" s="3"/>
       <c r="Z357" s="3"/>
     </row>
-    <row r="358" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
         <v>779</v>
       </c>
@@ -19081,7 +19080,7 @@
       <c r="Y358" s="3"/>
       <c r="Z358" s="3"/>
     </row>
-    <row r="359" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
         <v>781</v>
       </c>
@@ -19123,7 +19122,7 @@
       <c r="Y359" s="3"/>
       <c r="Z359" s="3"/>
     </row>
-    <row r="360" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
         <v>783</v>
       </c>
@@ -19165,7 +19164,7 @@
       <c r="Y360" s="3"/>
       <c r="Z360" s="3"/>
     </row>
-    <row r="361" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
         <v>785</v>
       </c>
@@ -19207,7 +19206,7 @@
       <c r="Y361" s="3"/>
       <c r="Z361" s="3"/>
     </row>
-    <row r="362" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
         <v>787</v>
       </c>
@@ -19249,7 +19248,7 @@
       <c r="Y362" s="3"/>
       <c r="Z362" s="3"/>
     </row>
-    <row r="363" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
         <v>790</v>
       </c>
@@ -19291,7 +19290,7 @@
       <c r="Y363" s="3"/>
       <c r="Z363" s="3"/>
     </row>
-    <row r="364" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
         <v>793</v>
       </c>
@@ -19333,7 +19332,7 @@
       <c r="Y364" s="3"/>
       <c r="Z364" s="3"/>
     </row>
-    <row r="365" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
         <v>795</v>
       </c>
@@ -19375,7 +19374,7 @@
       <c r="Y365" s="3"/>
       <c r="Z365" s="3"/>
     </row>
-    <row r="366" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
         <v>797</v>
       </c>
@@ -19417,7 +19416,7 @@
       <c r="Y366" s="3"/>
       <c r="Z366" s="3"/>
     </row>
-    <row r="367" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
         <v>799</v>
       </c>
@@ -19459,7 +19458,7 @@
       <c r="Y367" s="3"/>
       <c r="Z367" s="3"/>
     </row>
-    <row r="368" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
         <v>801</v>
       </c>
@@ -19501,7 +19500,7 @@
       <c r="Y368" s="3"/>
       <c r="Z368" s="3"/>
     </row>
-    <row r="369" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
         <v>803</v>
       </c>
@@ -19543,7 +19542,7 @@
       <c r="Y369" s="3"/>
       <c r="Z369" s="3"/>
     </row>
-    <row r="370" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
         <v>805</v>
       </c>
@@ -19585,7 +19584,7 @@
       <c r="Y370" s="3"/>
       <c r="Z370" s="3"/>
     </row>
-    <row r="371" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
         <v>807</v>
       </c>
@@ -19627,7 +19626,7 @@
       <c r="Y371" s="3"/>
       <c r="Z371" s="3"/>
     </row>
-    <row r="372" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
         <v>809</v>
       </c>
@@ -19669,7 +19668,7 @@
       <c r="Y372" s="3"/>
       <c r="Z372" s="3"/>
     </row>
-    <row r="373" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
         <v>811</v>
       </c>
@@ -19711,7 +19710,7 @@
       <c r="Y373" s="3"/>
       <c r="Z373" s="3"/>
     </row>
-    <row r="374" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
         <v>813</v>
       </c>
@@ -19753,7 +19752,7 @@
       <c r="Y374" s="3"/>
       <c r="Z374" s="3"/>
     </row>
-    <row r="375" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
         <v>816</v>
       </c>
@@ -19795,7 +19794,7 @@
       <c r="Y375" s="3"/>
       <c r="Z375" s="3"/>
     </row>
-    <row r="376" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
         <v>818</v>
       </c>
@@ -19837,7 +19836,7 @@
       <c r="Y376" s="3"/>
       <c r="Z376" s="3"/>
     </row>
-    <row r="377" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
         <v>820</v>
       </c>
@@ -19879,7 +19878,7 @@
       <c r="Y377" s="3"/>
       <c r="Z377" s="3"/>
     </row>
-    <row r="378" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
         <v>822</v>
       </c>
@@ -19921,7 +19920,7 @@
       <c r="Y378" s="3"/>
       <c r="Z378" s="3"/>
     </row>
-    <row r="379" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
         <v>824</v>
       </c>
@@ -19963,7 +19962,7 @@
       <c r="Y379" s="3"/>
       <c r="Z379" s="3"/>
     </row>
-    <row r="380" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
         <v>826</v>
       </c>
@@ -20005,7 +20004,7 @@
       <c r="Y380" s="3"/>
       <c r="Z380" s="3"/>
     </row>
-    <row r="381" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
         <v>828</v>
       </c>
@@ -20047,7 +20046,7 @@
       <c r="Y381" s="3"/>
       <c r="Z381" s="3"/>
     </row>
-    <row r="382" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
         <v>830</v>
       </c>
@@ -20089,7 +20088,7 @@
       <c r="Y382" s="3"/>
       <c r="Z382" s="3"/>
     </row>
-    <row r="383" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
         <v>832</v>
       </c>
@@ -20131,7 +20130,7 @@
       <c r="Y383" s="3"/>
       <c r="Z383" s="3"/>
     </row>
-    <row r="384" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
         <v>834</v>
       </c>
@@ -20173,7 +20172,7 @@
       <c r="Y384" s="3"/>
       <c r="Z384" s="3"/>
     </row>
-    <row r="385" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
         <v>836</v>
       </c>
@@ -20215,7 +20214,7 @@
       <c r="Y385" s="3"/>
       <c r="Z385" s="3"/>
     </row>
-    <row r="386" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
         <v>838</v>
       </c>
@@ -20257,7 +20256,7 @@
       <c r="Y386" s="3"/>
       <c r="Z386" s="3"/>
     </row>
-    <row r="387" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
         <v>840</v>
       </c>
@@ -20299,7 +20298,7 @@
       <c r="Y387" s="3"/>
       <c r="Z387" s="3"/>
     </row>
-    <row r="388" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
         <v>842</v>
       </c>
@@ -20341,7 +20340,7 @@
       <c r="Y388" s="3"/>
       <c r="Z388" s="3"/>
     </row>
-    <row r="389" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
         <v>844</v>
       </c>
@@ -20383,7 +20382,7 @@
       <c r="Y389" s="3"/>
       <c r="Z389" s="3"/>
     </row>
-    <row r="390" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
         <v>846</v>
       </c>
@@ -20425,7 +20424,7 @@
       <c r="Y390" s="3"/>
       <c r="Z390" s="3"/>
     </row>
-    <row r="391" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
         <v>848</v>
       </c>
@@ -20467,7 +20466,7 @@
       <c r="Y391" s="3"/>
       <c r="Z391" s="3"/>
     </row>
-    <row r="392" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
         <v>850</v>
       </c>
@@ -20509,7 +20508,7 @@
       <c r="Y392" s="3"/>
       <c r="Z392" s="3"/>
     </row>
-    <row r="393" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
         <v>853</v>
       </c>
@@ -20551,7 +20550,7 @@
       <c r="Y393" s="3"/>
       <c r="Z393" s="3"/>
     </row>
-    <row r="394" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
         <v>855</v>
       </c>
@@ -20593,7 +20592,7 @@
       <c r="Y394" s="3"/>
       <c r="Z394" s="3"/>
     </row>
-    <row r="395" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
         <v>857</v>
       </c>
@@ -20635,7 +20634,7 @@
       <c r="Y395" s="3"/>
       <c r="Z395" s="3"/>
     </row>
-    <row r="396" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
         <v>859</v>
       </c>
@@ -20671,7 +20670,7 @@
       <c r="Y396" s="3"/>
       <c r="Z396" s="3"/>
     </row>
-    <row r="397" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
         <v>861</v>
       </c>
@@ -20707,7 +20706,7 @@
       <c r="Y397" s="3"/>
       <c r="Z397" s="3"/>
     </row>
-    <row r="398" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
         <v>864</v>
       </c>
@@ -20743,7 +20742,7 @@
       <c r="Y398" s="3"/>
       <c r="Z398" s="3"/>
     </row>
-    <row r="399" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
         <v>866</v>
       </c>
@@ -20779,7 +20778,7 @@
       <c r="Y399" s="3"/>
       <c r="Z399" s="3"/>
     </row>
-    <row r="400" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
         <v>868</v>
       </c>
@@ -20815,7 +20814,7 @@
       <c r="Y400" s="3"/>
       <c r="Z400" s="3"/>
     </row>
-    <row r="401" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
         <v>870</v>
       </c>
@@ -20851,7 +20850,7 @@
       <c r="Y401" s="3"/>
       <c r="Z401" s="3"/>
     </row>
-    <row r="402" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
         <v>873</v>
       </c>
@@ -20887,7 +20886,7 @@
       <c r="Y402" s="3"/>
       <c r="Z402" s="3"/>
     </row>
-    <row r="403" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
         <v>875</v>
       </c>
@@ -20929,7 +20928,7 @@
       <c r="Y403" s="3"/>
       <c r="Z403" s="3"/>
     </row>
-    <row r="404" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
         <v>878</v>
       </c>
@@ -20971,7 +20970,7 @@
       <c r="Y404" s="3"/>
       <c r="Z404" s="3"/>
     </row>
-    <row r="405" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
         <v>880</v>
       </c>
@@ -21013,7 +21012,7 @@
       <c r="Y405" s="3"/>
       <c r="Z405" s="3"/>
     </row>
-    <row r="406" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
         <v>882</v>
       </c>
@@ -21055,7 +21054,7 @@
       <c r="Y406" s="3"/>
       <c r="Z406" s="3"/>
     </row>
-    <row r="407" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
         <v>884</v>
       </c>
@@ -21097,7 +21096,7 @@
       <c r="Y407" s="3"/>
       <c r="Z407" s="3"/>
     </row>
-    <row r="408" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
         <v>886</v>
       </c>
@@ -21139,7 +21138,7 @@
       <c r="Y408" s="3"/>
       <c r="Z408" s="3"/>
     </row>
-    <row r="409" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
         <v>888</v>
       </c>
@@ -21181,7 +21180,7 @@
       <c r="Y409" s="3"/>
       <c r="Z409" s="3"/>
     </row>
-    <row r="410" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
         <v>890</v>
       </c>
@@ -21223,7 +21222,7 @@
       <c r="Y410" s="3"/>
       <c r="Z410" s="3"/>
     </row>
-    <row r="411" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
         <v>892</v>
       </c>
@@ -21265,7 +21264,7 @@
       <c r="Y411" s="3"/>
       <c r="Z411" s="3"/>
     </row>
-    <row r="412" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
         <v>894</v>
       </c>
@@ -21307,7 +21306,7 @@
       <c r="Y412" s="3"/>
       <c r="Z412" s="3"/>
     </row>
-    <row r="413" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
         <v>896</v>
       </c>
@@ -21349,7 +21348,7 @@
       <c r="Y413" s="3"/>
       <c r="Z413" s="3"/>
     </row>
-    <row r="414" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
         <v>898</v>
       </c>
@@ -21391,7 +21390,7 @@
       <c r="Y414" s="3"/>
       <c r="Z414" s="3"/>
     </row>
-    <row r="415" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
         <v>901</v>
       </c>
@@ -21433,7 +21432,7 @@
       <c r="Y415" s="3"/>
       <c r="Z415" s="3"/>
     </row>
-    <row r="416" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
         <v>903</v>
       </c>
@@ -21475,7 +21474,7 @@
       <c r="Y416" s="3"/>
       <c r="Z416" s="3"/>
     </row>
-    <row r="417" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
         <v>905</v>
       </c>
@@ -21517,7 +21516,7 @@
       <c r="Y417" s="3"/>
       <c r="Z417" s="3"/>
     </row>
-    <row r="418" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
         <v>907</v>
       </c>
@@ -21559,7 +21558,7 @@
       <c r="Y418" s="3"/>
       <c r="Z418" s="3"/>
     </row>
-    <row r="419" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
         <v>909</v>
       </c>
@@ -21601,7 +21600,7 @@
       <c r="Y419" s="3"/>
       <c r="Z419" s="3"/>
     </row>
-    <row r="420" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
         <v>911</v>
       </c>
@@ -21643,7 +21642,7 @@
       <c r="Y420" s="3"/>
       <c r="Z420" s="3"/>
     </row>
-    <row r="421" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
         <v>913</v>
       </c>
@@ -21685,7 +21684,7 @@
       <c r="Y421" s="3"/>
       <c r="Z421" s="3"/>
     </row>
-    <row r="422" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
         <v>915</v>
       </c>
@@ -21727,7 +21726,7 @@
       <c r="Y422" s="3"/>
       <c r="Z422" s="3"/>
     </row>
-    <row r="423" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
         <v>917</v>
       </c>
@@ -21769,7 +21768,7 @@
       <c r="Y423" s="3"/>
       <c r="Z423" s="3"/>
     </row>
-    <row r="424" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
         <v>919</v>
       </c>
@@ -21811,7 +21810,7 @@
       <c r="Y424" s="3"/>
       <c r="Z424" s="3"/>
     </row>
-    <row r="425" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
         <v>921</v>
       </c>
@@ -21853,7 +21852,7 @@
       <c r="Y425" s="3"/>
       <c r="Z425" s="3"/>
     </row>
-    <row r="426" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
         <v>924</v>
       </c>
@@ -21895,7 +21894,7 @@
       <c r="Y426" s="3"/>
       <c r="Z426" s="3"/>
     </row>
-    <row r="427" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
         <v>926</v>
       </c>
@@ -21937,7 +21936,7 @@
       <c r="Y427" s="3"/>
       <c r="Z427" s="3"/>
     </row>
-    <row r="428" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="3" t="s">
         <v>928</v>
       </c>
@@ -21979,7 +21978,7 @@
       <c r="Y428" s="3"/>
       <c r="Z428" s="3"/>
     </row>
-    <row r="429" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="3" t="s">
         <v>930</v>
       </c>
@@ -22021,7 +22020,7 @@
       <c r="Y429" s="3"/>
       <c r="Z429" s="3"/>
     </row>
-    <row r="430" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="3" t="s">
         <v>932</v>
       </c>
@@ -22063,7 +22062,7 @@
       <c r="Y430" s="3"/>
       <c r="Z430" s="3"/>
     </row>
-    <row r="431" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="3" t="s">
         <v>934</v>
       </c>
@@ -22105,7 +22104,7 @@
       <c r="Y431" s="3"/>
       <c r="Z431" s="3"/>
     </row>
-    <row r="432" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="3" t="s">
         <v>936</v>
       </c>
@@ -22147,7 +22146,7 @@
       <c r="Y432" s="3"/>
       <c r="Z432" s="3"/>
     </row>
-    <row r="433" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
         <v>938</v>
       </c>
@@ -22189,7 +22188,7 @@
       <c r="Y433" s="3"/>
       <c r="Z433" s="3"/>
     </row>
-    <row r="434" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
         <v>940</v>
       </c>
@@ -22231,7 +22230,7 @@
       <c r="Y434" s="3"/>
       <c r="Z434" s="3"/>
     </row>
-    <row r="435" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
         <v>942</v>
       </c>
@@ -22273,7 +22272,7 @@
       <c r="Y435" s="3"/>
       <c r="Z435" s="3"/>
     </row>
-    <row r="436" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
         <v>944</v>
       </c>
@@ -22315,7 +22314,7 @@
       <c r="Y436" s="3"/>
       <c r="Z436" s="3"/>
     </row>
-    <row r="437" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
         <v>946</v>
       </c>
@@ -22357,7 +22356,7 @@
       <c r="Y437" s="3"/>
       <c r="Z437" s="3"/>
     </row>
-    <row r="438" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="3" t="s">
         <v>948</v>
       </c>
@@ -22399,7 +22398,7 @@
       <c r="Y438" s="3"/>
       <c r="Z438" s="3"/>
     </row>
-    <row r="439" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="3" t="s">
         <v>950</v>
       </c>
@@ -22441,7 +22440,7 @@
       <c r="Y439" s="3"/>
       <c r="Z439" s="3"/>
     </row>
-    <row r="440" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="3" t="s">
         <v>952</v>
       </c>
@@ -22483,7 +22482,7 @@
       <c r="Y440" s="3"/>
       <c r="Z440" s="3"/>
     </row>
-    <row r="441" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="3" t="s">
         <v>954</v>
       </c>
@@ -22525,7 +22524,7 @@
       <c r="Y441" s="3"/>
       <c r="Z441" s="3"/>
     </row>
-    <row r="442" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
         <v>956</v>
       </c>
@@ -22567,7 +22566,7 @@
       <c r="Y442" s="3"/>
       <c r="Z442" s="3"/>
     </row>
-    <row r="443" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
         <v>958</v>
       </c>
@@ -22609,7 +22608,7 @@
       <c r="Y443" s="3"/>
       <c r="Z443" s="3"/>
     </row>
-    <row r="444" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
         <v>960</v>
       </c>
@@ -22651,7 +22650,7 @@
       <c r="Y444" s="3"/>
       <c r="Z444" s="3"/>
     </row>
-    <row r="445" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
         <v>962</v>
       </c>
@@ -22693,7 +22692,7 @@
       <c r="Y445" s="3"/>
       <c r="Z445" s="3"/>
     </row>
-    <row r="446" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
         <v>964</v>
       </c>
@@ -22735,7 +22734,7 @@
       <c r="Y446" s="3"/>
       <c r="Z446" s="3"/>
     </row>
-    <row r="447" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
         <v>966</v>
       </c>
@@ -22771,7 +22770,7 @@
       <c r="Y447" s="3"/>
       <c r="Z447" s="3"/>
     </row>
-    <row r="448" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
         <v>968</v>
       </c>
@@ -22807,7 +22806,7 @@
       <c r="Y448" s="3"/>
       <c r="Z448" s="3"/>
     </row>
-    <row r="449" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
         <v>970</v>
       </c>
@@ -22843,7 +22842,7 @@
       <c r="Y449" s="3"/>
       <c r="Z449" s="3"/>
     </row>
-    <row r="450" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
         <v>972</v>
       </c>
@@ -22879,7 +22878,7 @@
       <c r="Y450" s="3"/>
       <c r="Z450" s="3"/>
     </row>
-    <row r="451" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="3" t="s">
         <v>974</v>
       </c>
@@ -22915,7 +22914,7 @@
       <c r="Y451" s="3"/>
       <c r="Z451" s="3"/>
     </row>
-    <row r="452" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
         <v>976</v>
       </c>
@@ -22951,7 +22950,7 @@
       <c r="Y452" s="3"/>
       <c r="Z452" s="3"/>
     </row>
-    <row r="453" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
         <v>978</v>
       </c>
@@ -22987,7 +22986,7 @@
       <c r="Y453" s="3"/>
       <c r="Z453" s="3"/>
     </row>
-    <row r="454" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
         <v>980</v>
       </c>
@@ -23023,7 +23022,7 @@
       <c r="Y454" s="3"/>
       <c r="Z454" s="3"/>
     </row>
-    <row r="455" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
         <v>982</v>
       </c>
@@ -23059,7 +23058,7 @@
       <c r="Y455" s="3"/>
       <c r="Z455" s="3"/>
     </row>
-    <row r="456" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
         <v>984</v>
       </c>
@@ -23095,7 +23094,7 @@
       <c r="Y456" s="3"/>
       <c r="Z456" s="3"/>
     </row>
-    <row r="457" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
         <v>986</v>
       </c>
@@ -23131,7 +23130,7 @@
       <c r="Y457" s="3"/>
       <c r="Z457" s="3"/>
     </row>
-    <row r="458" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
         <v>988</v>
       </c>
@@ -23173,7 +23172,7 @@
       <c r="Y458" s="3"/>
       <c r="Z458" s="3"/>
     </row>
-    <row r="459" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
         <v>993</v>
       </c>
@@ -23215,7 +23214,7 @@
       <c r="Y459" s="3"/>
       <c r="Z459" s="3"/>
     </row>
-    <row r="460" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
         <v>995</v>
       </c>
@@ -23257,7 +23256,7 @@
       <c r="Y460" s="3"/>
       <c r="Z460" s="3"/>
     </row>
-    <row r="461" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
         <v>997</v>
       </c>
@@ -23299,7 +23298,7 @@
       <c r="Y461" s="3"/>
       <c r="Z461" s="3"/>
     </row>
-    <row r="462" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
         <v>999</v>
       </c>
@@ -23341,7 +23340,7 @@
       <c r="Y462" s="3"/>
       <c r="Z462" s="3"/>
     </row>
-    <row r="463" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
         <v>1003</v>
       </c>
@@ -23383,7 +23382,7 @@
       <c r="Y463" s="3"/>
       <c r="Z463" s="3"/>
     </row>
-    <row r="464" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
         <v>1005</v>
       </c>
@@ -23425,7 +23424,7 @@
       <c r="Y464" s="3"/>
       <c r="Z464" s="3"/>
     </row>
-    <row r="465" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
         <v>1007</v>
       </c>
@@ -23467,7 +23466,7 @@
       <c r="Y465" s="3"/>
       <c r="Z465" s="3"/>
     </row>
-    <row r="466" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
         <v>1009</v>
       </c>
@@ -23509,7 +23508,7 @@
       <c r="Y466" s="3"/>
       <c r="Z466" s="3"/>
     </row>
-    <row r="467" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
         <v>1011</v>
       </c>
@@ -23551,7 +23550,7 @@
       <c r="Y467" s="3"/>
       <c r="Z467" s="3"/>
     </row>
-    <row r="468" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
         <v>1013</v>
       </c>
@@ -23593,7 +23592,7 @@
       <c r="Y468" s="3"/>
       <c r="Z468" s="3"/>
     </row>
-    <row r="469" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
         <v>1015</v>
       </c>
@@ -23635,7 +23634,7 @@
       <c r="Y469" s="3"/>
       <c r="Z469" s="3"/>
     </row>
-    <row r="470" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
         <v>1017</v>
       </c>
@@ -23677,7 +23676,7 @@
       <c r="Y470" s="3"/>
       <c r="Z470" s="3"/>
     </row>
-    <row r="471" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
         <v>1019</v>
       </c>
@@ -23719,7 +23718,7 @@
       <c r="Y471" s="3"/>
       <c r="Z471" s="3"/>
     </row>
-    <row r="472" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
         <v>1021</v>
       </c>
@@ -23761,7 +23760,7 @@
       <c r="Y472" s="3"/>
       <c r="Z472" s="3"/>
     </row>
-    <row r="473" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
         <v>1023</v>
       </c>
@@ -23803,7 +23802,7 @@
       <c r="Y473" s="3"/>
       <c r="Z473" s="3"/>
     </row>
-    <row r="474" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
         <v>1025</v>
       </c>
@@ -23845,7 +23844,7 @@
       <c r="Y474" s="3"/>
       <c r="Z474" s="3"/>
     </row>
-    <row r="475" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
         <v>1027</v>
       </c>
@@ -23887,7 +23886,7 @@
       <c r="Y475" s="3"/>
       <c r="Z475" s="3"/>
     </row>
-    <row r="476" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
         <v>1029</v>
       </c>
@@ -23929,7 +23928,7 @@
       <c r="Y476" s="3"/>
       <c r="Z476" s="3"/>
     </row>
-    <row r="477" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
         <v>1031</v>
       </c>
@@ -23971,7 +23970,7 @@
       <c r="Y477" s="3"/>
       <c r="Z477" s="3"/>
     </row>
-    <row r="478" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
         <v>1033</v>
       </c>
@@ -24013,7 +24012,7 @@
       <c r="Y478" s="3"/>
       <c r="Z478" s="3"/>
     </row>
-    <row r="479" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
         <v>1035</v>
       </c>
@@ -24055,7 +24054,7 @@
       <c r="Y479" s="3"/>
       <c r="Z479" s="3"/>
     </row>
-    <row r="480" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
         <v>1037</v>
       </c>
@@ -24097,7 +24096,7 @@
       <c r="Y480" s="3"/>
       <c r="Z480" s="3"/>
     </row>
-    <row r="481" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="3" t="s">
         <v>1039</v>
       </c>
@@ -24139,7 +24138,7 @@
       <c r="Y481" s="3"/>
       <c r="Z481" s="3"/>
     </row>
-    <row r="482" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
         <v>1041</v>
       </c>
@@ -24181,7 +24180,7 @@
       <c r="Y482" s="3"/>
       <c r="Z482" s="3"/>
     </row>
-    <row r="483" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
         <v>1045</v>
       </c>
@@ -24223,7 +24222,7 @@
       <c r="Y483" s="3"/>
       <c r="Z483" s="3"/>
     </row>
-    <row r="484" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
         <v>1047</v>
       </c>
@@ -24265,7 +24264,7 @@
       <c r="Y484" s="3"/>
       <c r="Z484" s="3"/>
     </row>
-    <row r="485" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
         <v>1049</v>
       </c>
@@ -24307,7 +24306,7 @@
       <c r="Y485" s="3"/>
       <c r="Z485" s="3"/>
     </row>
-    <row r="486" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
         <v>1051</v>
       </c>
@@ -24349,7 +24348,7 @@
       <c r="Y486" s="3"/>
       <c r="Z486" s="3"/>
     </row>
-    <row r="487" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
         <v>1053</v>
       </c>
@@ -24391,7 +24390,7 @@
       <c r="Y487" s="3"/>
       <c r="Z487" s="3"/>
     </row>
-    <row r="488" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
         <v>1055</v>
       </c>
@@ -24433,7 +24432,7 @@
       <c r="Y488" s="3"/>
       <c r="Z488" s="3"/>
     </row>
-    <row r="489" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
         <v>1057</v>
       </c>
@@ -24475,7 +24474,7 @@
       <c r="Y489" s="3"/>
       <c r="Z489" s="3"/>
     </row>
-    <row r="490" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
         <v>1059</v>
       </c>
@@ -24517,7 +24516,7 @@
       <c r="Y490" s="3"/>
       <c r="Z490" s="3"/>
     </row>
-    <row r="491" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
         <v>1061</v>
       </c>
@@ -24559,7 +24558,7 @@
       <c r="Y491" s="3"/>
       <c r="Z491" s="3"/>
     </row>
-    <row r="492" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
         <v>1063</v>
       </c>
@@ -24601,7 +24600,7 @@
       <c r="Y492" s="3"/>
       <c r="Z492" s="3"/>
     </row>
-    <row r="493" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
         <v>1065</v>
       </c>
@@ -24643,7 +24642,7 @@
       <c r="Y493" s="3"/>
       <c r="Z493" s="3"/>
     </row>
-    <row r="494" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
         <v>1067</v>
       </c>
@@ -24685,7 +24684,7 @@
       <c r="Y494" s="3"/>
       <c r="Z494" s="3"/>
     </row>
-    <row r="495" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
         <v>1070</v>
       </c>
@@ -24727,7 +24726,7 @@
       <c r="Y495" s="3"/>
       <c r="Z495" s="3"/>
     </row>
-    <row r="496" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
         <v>1072</v>
       </c>
@@ -24769,7 +24768,7 @@
       <c r="Y496" s="3"/>
       <c r="Z496" s="3"/>
     </row>
-    <row r="497" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
         <v>1074</v>
       </c>
@@ -24811,7 +24810,7 @@
       <c r="Y497" s="3"/>
       <c r="Z497" s="3"/>
     </row>
-    <row r="498" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
         <v>1078</v>
       </c>
@@ -24853,7 +24852,7 @@
       <c r="Y498" s="3"/>
       <c r="Z498" s="3"/>
     </row>
-    <row r="499" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="3" t="s">
         <v>1080</v>
       </c>
@@ -24895,7 +24894,7 @@
       <c r="Y499" s="3"/>
       <c r="Z499" s="3"/>
     </row>
-    <row r="500" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
         <v>1082</v>
       </c>
@@ -24937,7 +24936,7 @@
       <c r="Y500" s="3"/>
       <c r="Z500" s="3"/>
     </row>
-    <row r="501" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
         <v>1084</v>
       </c>
@@ -24979,7 +24978,7 @@
       <c r="Y501" s="3"/>
       <c r="Z501" s="3"/>
     </row>
-    <row r="502" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
         <v>1086</v>
       </c>
@@ -25021,7 +25020,7 @@
       <c r="Y502" s="3"/>
       <c r="Z502" s="3"/>
     </row>
-    <row r="503" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
         <v>1088</v>
       </c>
@@ -25063,7 +25062,7 @@
       <c r="Y503" s="3"/>
       <c r="Z503" s="3"/>
     </row>
-    <row r="504" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
         <v>1090</v>
       </c>
@@ -25105,7 +25104,7 @@
       <c r="Y504" s="3"/>
       <c r="Z504" s="3"/>
     </row>
-    <row r="505" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
         <v>1092</v>
       </c>
@@ -25147,7 +25146,7 @@
       <c r="Y505" s="3"/>
       <c r="Z505" s="3"/>
     </row>
-    <row r="506" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
         <v>1094</v>
       </c>
@@ -25189,7 +25188,7 @@
       <c r="Y506" s="3"/>
       <c r="Z506" s="3"/>
     </row>
-    <row r="507" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
         <v>1096</v>
       </c>
@@ -25231,7 +25230,7 @@
       <c r="Y507" s="3"/>
       <c r="Z507" s="3"/>
     </row>
-    <row r="508" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
         <v>1098</v>
       </c>
@@ -25273,7 +25272,7 @@
       <c r="Y508" s="3"/>
       <c r="Z508" s="3"/>
     </row>
-    <row r="509" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
         <v>1100</v>
       </c>
@@ -25315,7 +25314,7 @@
       <c r="Y509" s="3"/>
       <c r="Z509" s="3"/>
     </row>
-    <row r="510" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
         <v>1102</v>
       </c>
@@ -25357,7 +25356,7 @@
       <c r="Y510" s="3"/>
       <c r="Z510" s="3"/>
     </row>
-    <row r="511" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="3" t="s">
         <v>1104</v>
       </c>
@@ -25399,7 +25398,7 @@
       <c r="Y511" s="3"/>
       <c r="Z511" s="3"/>
     </row>
-    <row r="512" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
         <v>1106</v>
       </c>
@@ -25441,7 +25440,7 @@
       <c r="Y512" s="3"/>
       <c r="Z512" s="3"/>
     </row>
-    <row r="513" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
         <v>1108</v>
       </c>
@@ -25483,7 +25482,7 @@
       <c r="Y513" s="3"/>
       <c r="Z513" s="3"/>
     </row>
-    <row r="514" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
         <v>1110</v>
       </c>
@@ -25525,7 +25524,7 @@
       <c r="Y514" s="3"/>
       <c r="Z514" s="3"/>
     </row>
-    <row r="515" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
         <v>1112</v>
       </c>
@@ -25567,7 +25566,7 @@
       <c r="Y515" s="3"/>
       <c r="Z515" s="3"/>
     </row>
-    <row r="516" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
         <v>1114</v>
       </c>
@@ -25609,7 +25608,7 @@
       <c r="Y516" s="3"/>
       <c r="Z516" s="3"/>
     </row>
-    <row r="517" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="3" t="s">
         <v>1116</v>
       </c>
@@ -25651,7 +25650,7 @@
       <c r="Y517" s="3"/>
       <c r="Z517" s="3"/>
     </row>
-    <row r="518" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
         <v>1120</v>
       </c>
@@ -25693,7 +25692,7 @@
       <c r="Y518" s="3"/>
       <c r="Z518" s="3"/>
     </row>
-    <row r="519" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
         <v>1122</v>
       </c>
@@ -25735,7 +25734,7 @@
       <c r="Y519" s="3"/>
       <c r="Z519" s="3"/>
     </row>
-    <row r="520" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
         <v>1124</v>
       </c>
@@ -25777,7 +25776,7 @@
       <c r="Y520" s="3"/>
       <c r="Z520" s="3"/>
     </row>
-    <row r="521" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
         <v>1126</v>
       </c>
@@ -25819,7 +25818,7 @@
       <c r="Y521" s="3"/>
       <c r="Z521" s="3"/>
     </row>
-    <row r="522" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
         <v>1128</v>
       </c>
@@ -25861,7 +25860,7 @@
       <c r="Y522" s="3"/>
       <c r="Z522" s="3"/>
     </row>
-    <row r="523" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
         <v>1130</v>
       </c>
@@ -25903,7 +25902,7 @@
       <c r="Y523" s="3"/>
       <c r="Z523" s="3"/>
     </row>
-    <row r="524" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
         <v>1132</v>
       </c>
@@ -25945,7 +25944,7 @@
       <c r="Y524" s="3"/>
       <c r="Z524" s="3"/>
     </row>
-    <row r="525" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
         <v>1134</v>
       </c>
@@ -25987,7 +25986,7 @@
       <c r="Y525" s="3"/>
       <c r="Z525" s="3"/>
     </row>
-    <row r="526" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
         <v>1136</v>
       </c>
@@ -26029,7 +26028,7 @@
       <c r="Y526" s="3"/>
       <c r="Z526" s="3"/>
     </row>
-    <row r="527" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
         <v>1138</v>
       </c>
@@ -26071,7 +26070,7 @@
       <c r="Y527" s="3"/>
       <c r="Z527" s="3"/>
     </row>
-    <row r="528" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
         <v>1140</v>
       </c>
@@ -26113,7 +26112,7 @@
       <c r="Y528" s="3"/>
       <c r="Z528" s="3"/>
     </row>
-    <row r="529" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
         <v>1142</v>
       </c>
@@ -26155,7 +26154,7 @@
       <c r="Y529" s="3"/>
       <c r="Z529" s="3"/>
     </row>
-    <row r="530" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
         <v>1144</v>
       </c>
@@ -26197,7 +26196,7 @@
       <c r="Y530" s="3"/>
       <c r="Z530" s="3"/>
     </row>
-    <row r="531" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
         <v>1146</v>
       </c>
@@ -26239,7 +26238,7 @@
       <c r="Y531" s="3"/>
       <c r="Z531" s="3"/>
     </row>
-    <row r="532" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
         <v>1148</v>
       </c>
@@ -26281,7 +26280,7 @@
       <c r="Y532" s="3"/>
       <c r="Z532" s="3"/>
     </row>
-    <row r="533" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
         <v>1150</v>
       </c>
@@ -26323,7 +26322,7 @@
       <c r="Y533" s="3"/>
       <c r="Z533" s="3"/>
     </row>
-    <row r="534" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
         <v>1152</v>
       </c>
@@ -26365,7 +26364,7 @@
       <c r="Y534" s="3"/>
       <c r="Z534" s="3"/>
     </row>
-    <row r="535" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="3" t="s">
         <v>1154</v>
       </c>
@@ -26407,7 +26406,7 @@
       <c r="Y535" s="3"/>
       <c r="Z535" s="3"/>
     </row>
-    <row r="536" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
         <v>1156</v>
       </c>
@@ -26449,7 +26448,7 @@
       <c r="Y536" s="3"/>
       <c r="Z536" s="3"/>
     </row>
-    <row r="537" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
         <v>1158</v>
       </c>
@@ -26485,7 +26484,7 @@
       <c r="Y537" s="3"/>
       <c r="Z537" s="3"/>
     </row>
-    <row r="538" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
         <v>1160</v>
       </c>
@@ -26521,7 +26520,7 @@
       <c r="Y538" s="3"/>
       <c r="Z538" s="3"/>
     </row>
-    <row r="539" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="3" t="s">
         <v>1162</v>
       </c>
@@ -26565,7 +26564,7 @@
       <c r="Y539" s="3"/>
       <c r="Z539" s="3"/>
     </row>
-    <row r="540" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
         <v>1168</v>
       </c>
@@ -26609,7 +26608,7 @@
       <c r="Y540" s="3"/>
       <c r="Z540" s="3"/>
     </row>
-    <row r="541" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="3" t="s">
         <v>1170</v>
       </c>
@@ -26653,7 +26652,7 @@
       <c r="Y541" s="3"/>
       <c r="Z541" s="3"/>
     </row>
-    <row r="542" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
         <v>1172</v>
       </c>
@@ -26697,7 +26696,7 @@
       <c r="Y542" s="3"/>
       <c r="Z542" s="3"/>
     </row>
-    <row r="543" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="3" t="s">
         <v>1174</v>
       </c>
@@ -26741,7 +26740,7 @@
       <c r="Y543" s="3"/>
       <c r="Z543" s="3"/>
     </row>
-    <row r="544" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="3" t="s">
         <v>1176</v>
       </c>
@@ -26785,7 +26784,7 @@
       <c r="Y544" s="3"/>
       <c r="Z544" s="3"/>
     </row>
-    <row r="545" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
         <v>1178</v>
       </c>
@@ -26829,7 +26828,7 @@
       <c r="Y545" s="3"/>
       <c r="Z545" s="3"/>
     </row>
-    <row r="546" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
         <v>1180</v>
       </c>
@@ -26873,7 +26872,7 @@
       <c r="Y546" s="3"/>
       <c r="Z546" s="3"/>
     </row>
-    <row r="547" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="3" t="s">
         <v>1182</v>
       </c>
@@ -26917,7 +26916,7 @@
       <c r="Y547" s="3"/>
       <c r="Z547" s="3"/>
     </row>
-    <row r="548" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
         <v>1184</v>
       </c>
@@ -26961,7 +26960,7 @@
       <c r="Y548" s="3"/>
       <c r="Z548" s="3"/>
     </row>
-    <row r="549" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="3" t="s">
         <v>1186</v>
       </c>
@@ -27005,7 +27004,7 @@
       <c r="Y549" s="3"/>
       <c r="Z549" s="3"/>
     </row>
-    <row r="550" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
         <v>1188</v>
       </c>
@@ -27049,7 +27048,7 @@
       <c r="Y550" s="3"/>
       <c r="Z550" s="3"/>
     </row>
-    <row r="551" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="3" t="s">
         <v>1190</v>
       </c>
@@ -27093,7 +27092,7 @@
       <c r="Y551" s="3"/>
       <c r="Z551" s="3"/>
     </row>
-    <row r="552" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
         <v>1192</v>
       </c>
@@ -27137,7 +27136,7 @@
       <c r="Y552" s="3"/>
       <c r="Z552" s="3"/>
     </row>
-    <row r="553" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="3" t="s">
         <v>1194</v>
       </c>
@@ -27181,7 +27180,7 @@
       <c r="Y553" s="3"/>
       <c r="Z553" s="3"/>
     </row>
-    <row r="554" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
         <v>1197</v>
       </c>
@@ -27225,7 +27224,7 @@
       <c r="Y554" s="3"/>
       <c r="Z554" s="3"/>
     </row>
-    <row r="555" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="3" t="s">
         <v>1199</v>
       </c>
@@ -27269,7 +27268,7 @@
       <c r="Y555" s="3"/>
       <c r="Z555" s="3"/>
     </row>
-    <row r="556" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="3" t="s">
         <v>1201</v>
       </c>
@@ -27313,7 +27312,7 @@
       <c r="Y556" s="3"/>
       <c r="Z556" s="3"/>
     </row>
-    <row r="557" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="3" t="s">
         <v>1203</v>
       </c>
@@ -27357,7 +27356,7 @@
       <c r="Y557" s="3"/>
       <c r="Z557" s="3"/>
     </row>
-    <row r="558" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
         <v>1205</v>
       </c>
@@ -27401,7 +27400,7 @@
       <c r="Y558" s="3"/>
       <c r="Z558" s="3"/>
     </row>
-    <row r="559" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="3" t="s">
         <v>1207</v>
       </c>
@@ -27445,7 +27444,7 @@
       <c r="Y559" s="3"/>
       <c r="Z559" s="3"/>
     </row>
-    <row r="560" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
         <v>1209</v>
       </c>
@@ -27489,7 +27488,7 @@
       <c r="Y560" s="3"/>
       <c r="Z560" s="3"/>
     </row>
-    <row r="561" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="3" t="s">
         <v>1211</v>
       </c>
@@ -27533,7 +27532,7 @@
       <c r="Y561" s="3"/>
       <c r="Z561" s="3"/>
     </row>
-    <row r="562" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="3" t="s">
         <v>1213</v>
       </c>
@@ -27577,7 +27576,7 @@
       <c r="Y562" s="3"/>
       <c r="Z562" s="3"/>
     </row>
-    <row r="563" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="3" t="s">
         <v>1215</v>
       </c>
@@ -27621,7 +27620,7 @@
       <c r="Y563" s="3"/>
       <c r="Z563" s="3"/>
     </row>
-    <row r="564" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="3" t="s">
         <v>1217</v>
       </c>
@@ -27665,7 +27664,7 @@
       <c r="Y564" s="3"/>
       <c r="Z564" s="3"/>
     </row>
-    <row r="565" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="3" t="s">
         <v>1219</v>
       </c>
@@ -27709,7 +27708,7 @@
       <c r="Y565" s="3"/>
       <c r="Z565" s="3"/>
     </row>
-    <row r="566" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="3" t="s">
         <v>1221</v>
       </c>
@@ -27753,7 +27752,7 @@
       <c r="Y566" s="3"/>
       <c r="Z566" s="3"/>
     </row>
-    <row r="567" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="3" t="s">
         <v>1223</v>
       </c>
@@ -27797,7 +27796,7 @@
       <c r="Y567" s="3"/>
       <c r="Z567" s="3"/>
     </row>
-    <row r="568" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="3" t="s">
         <v>1225</v>
       </c>
@@ -27841,7 +27840,7 @@
       <c r="Y568" s="3"/>
       <c r="Z568" s="3"/>
     </row>
-    <row r="569" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
         <v>1227</v>
       </c>
@@ -27885,7 +27884,7 @@
       <c r="Y569" s="3"/>
       <c r="Z569" s="3"/>
     </row>
-    <row r="570" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
         <v>1229</v>
       </c>
@@ -27929,7 +27928,7 @@
       <c r="Y570" s="3"/>
       <c r="Z570" s="3"/>
     </row>
-    <row r="571" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="3" t="s">
         <v>1231</v>
       </c>
@@ -27973,7 +27972,7 @@
       <c r="Y571" s="3"/>
       <c r="Z571" s="3"/>
     </row>
-    <row r="572" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
         <v>1236</v>
       </c>
@@ -28017,7 +28016,7 @@
       <c r="Y572" s="3"/>
       <c r="Z572" s="3"/>
     </row>
-    <row r="573" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
         <v>1238</v>
       </c>
@@ -28061,7 +28060,7 @@
       <c r="Y573" s="3"/>
       <c r="Z573" s="3"/>
     </row>
-    <row r="574" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="3" t="s">
         <v>1240</v>
       </c>
@@ -28105,7 +28104,7 @@
       <c r="Y574" s="3"/>
       <c r="Z574" s="3"/>
     </row>
-    <row r="575" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
         <v>1242</v>
       </c>
@@ -28149,7 +28148,7 @@
       <c r="Y575" s="3"/>
       <c r="Z575" s="3"/>
     </row>
-    <row r="576" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
         <v>1245</v>
       </c>
@@ -28193,7 +28192,7 @@
       <c r="Y576" s="3"/>
       <c r="Z576" s="3"/>
     </row>
-    <row r="577" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="3" t="s">
         <v>1247</v>
       </c>
@@ -28237,7 +28236,7 @@
       <c r="Y577" s="3"/>
       <c r="Z577" s="3"/>
     </row>
-    <row r="578" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
         <v>1249</v>
       </c>
@@ -28281,7 +28280,7 @@
       <c r="Y578" s="3"/>
       <c r="Z578" s="3"/>
     </row>
-    <row r="579" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="3" t="s">
         <v>1251</v>
       </c>
@@ -28325,7 +28324,7 @@
       <c r="Y579" s="3"/>
       <c r="Z579" s="3"/>
     </row>
-    <row r="580" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="3" t="s">
         <v>1253</v>
       </c>
@@ -28369,7 +28368,7 @@
       <c r="Y580" s="3"/>
       <c r="Z580" s="3"/>
     </row>
-    <row r="581" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
         <v>1255</v>
       </c>
@@ -28413,7 +28412,7 @@
       <c r="Y581" s="3"/>
       <c r="Z581" s="3"/>
     </row>
-    <row r="582" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
         <v>1257</v>
       </c>
@@ -28457,7 +28456,7 @@
       <c r="Y582" s="3"/>
       <c r="Z582" s="3"/>
     </row>
-    <row r="583" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="3" t="s">
         <v>1259</v>
       </c>
@@ -28501,7 +28500,7 @@
       <c r="Y583" s="3"/>
       <c r="Z583" s="3"/>
     </row>
-    <row r="584" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
         <v>1262</v>
       </c>
@@ -28545,7 +28544,7 @@
       <c r="Y584" s="3"/>
       <c r="Z584" s="3"/>
     </row>
-    <row r="585" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
         <v>1264</v>
       </c>
@@ -28589,7 +28588,7 @@
       <c r="Y585" s="3"/>
       <c r="Z585" s="3"/>
     </row>
-    <row r="586" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
         <v>1266</v>
       </c>
@@ -28633,7 +28632,7 @@
       <c r="Y586" s="3"/>
       <c r="Z586" s="3"/>
     </row>
-    <row r="587" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="3" t="s">
         <v>1268</v>
       </c>
@@ -40242,13 +40241,7 @@
       <c r="Z1000" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H587" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Time Discrimination"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H587" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
